--- a/latest/job.xlsx
+++ b/latest/job.xlsx
@@ -257,7 +257,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="45">
     <fill>
       <patternFill/>
     </fill>
@@ -504,6 +504,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -960,7 +965,7 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -1135,6 +1140,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2219,7 +2225,7 @@
       </c>
       <c r="V4" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W4" s="48" t="inlineStr">
@@ -3084,7 +3090,7 @@
       </c>
       <c r="V9" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W9" s="48" t="inlineStr">
@@ -3257,7 +3263,7 @@
       </c>
       <c r="V10" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W10" s="47" t="inlineStr">
@@ -3430,7 +3436,7 @@
       </c>
       <c r="V11" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W11" s="48" t="inlineStr">
@@ -3476,17 +3482,17 @@
       </c>
       <c r="AF11" s="2" t="inlineStr">
         <is>
-          <t>A档，100分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1主攻。城市/薪资为香港、HK$22,000-28,000/月，薪资匹配为部分达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港本地Agentic AI平台公司，主打企业客服与销售流程自动化；JD与可信度为中高、中高，入池岗位。关键风险：英文/粤语/IANG；招聘状态不稳。</t>
+          <t>A档，100分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1主攻。城市/薪资为香港、HK$22,000-28,000/月，薪资匹配为部分达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港本地Agentic AI平台公司，主打企业客服与销售流程自动化；JD与可信度为中高、中高，入池岗位。关键风险：英文/粤语/IANG。</t>
         </is>
       </c>
       <c r="AG11" s="2" t="inlineStr">
         <is>
-          <t>先核验再投</t>
+          <t>重点准备后投</t>
         </is>
       </c>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>英文/粤语/IANG；招聘状态不稳</t>
+          <t>英文/粤语/IANG</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr">
@@ -4641,7 +4647,7 @@
       </c>
       <c r="V18" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；公开可见HR活跃状态：刚刚在线</t>
         </is>
       </c>
       <c r="W18" s="48" t="inlineStr">
@@ -4814,7 +4820,7 @@
       </c>
       <c r="V19" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="W19" s="48" t="inlineStr">
@@ -4987,7 +4993,7 @@
       </c>
       <c r="V20" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="W20" s="48" t="inlineStr">
@@ -5458,7 +5464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI47"/>
+  <dimension ref="A1:AI48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="4"/>
@@ -9762,7 +9768,7 @@
       </c>
       <c r="V25" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W25" s="47" t="inlineStr">
@@ -12530,7 +12536,7 @@
       </c>
       <c r="V41" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W41" s="48" t="inlineStr">
@@ -13548,7 +13554,7 @@
       </c>
       <c r="V47" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W47" s="47" t="inlineStr">
@@ -13613,7 +13619,179 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="42" customHeight="1"/>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="47" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B48" s="47" t="inlineStr">
+        <is>
+          <t>Engineering Project Manager Intern-Shanghai/ Shenzhen</t>
+        </is>
+      </c>
+      <c r="C48" s="47" t="inlineStr">
+        <is>
+          <t>深圳/上海</t>
+        </is>
+      </c>
+      <c r="D48" s="47" t="inlineStr">
+        <is>
+          <t>Apple官网未公开</t>
+        </is>
+      </c>
+      <c r="E48" s="47" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F48" s="47" t="inlineStr">
+        <is>
+          <t>实习薪资未公开；Apple平台价值高</t>
+        </is>
+      </c>
+      <c r="G48" s="47" t="inlineStr">
+        <is>
+          <t>主线A-AI终端/智能硬件/TPM/软硬件协同项目</t>
+        </is>
+      </c>
+      <c r="H48" s="47" t="inlineStr">
+        <is>
+          <t>P2今日可投</t>
+        </is>
+      </c>
+      <c r="I48" s="47" t="inlineStr">
+        <is>
+          <t>中高</t>
+        </is>
+      </c>
+      <c r="J48" s="47" t="inlineStr">
+        <is>
+          <t>实习/硬件项目管理/EPM/外企</t>
+        </is>
+      </c>
+      <c r="K48" s="47" t="inlineStr">
+        <is>
+          <t>学生岗位，具体年级与专业以Apple JD为准</t>
+        </is>
+      </c>
+      <c r="L48" s="47" t="inlineStr">
+        <is>
+          <t>Apple官网显示Intern岗位；完整JD为JS页面，需投前二次确认每周到岗、实习周期和技术要求</t>
+        </is>
+      </c>
+      <c r="M48" s="47" t="inlineStr">
+        <is>
+          <t>2026-06-11发布；2026-06-17官方搜索页可见</t>
+        </is>
+      </c>
+      <c r="N48" s="47" t="inlineStr">
+        <is>
+          <t>Apple Jobs</t>
+        </is>
+      </c>
+      <c r="O48" s="47" t="inlineStr">
+        <is>
+          <t>全球消费电子与软硬件一体化顶级外企，AI终端、硬件工程、供应链和产品体验平台价值极高</t>
+        </is>
+      </c>
+      <c r="P48" s="47" t="inlineStr">
+        <is>
+          <t>做iPhone、iPad、Mac、AirPods、Apple Watch、Vision Pro及软硬件生态。</t>
+        </is>
+      </c>
+      <c r="Q48" s="47" t="inlineStr">
+        <is>
+          <t>硬件工程项目管理实习，预计围绕跨职能协作、项目节奏、工程问题跟进、样机/量产节点沟通和供应链协同。</t>
+        </is>
+      </c>
+      <c r="R48" s="47" t="inlineStr">
+        <is>
+          <t>Apple官网未披露该岗位单独福利；以offer和当地政策为准。</t>
+        </is>
+      </c>
+      <c r="S48" s="47" t="inlineStr">
+        <is>
+          <t>外企英文沟通与硬件工程语境；可能偏EPM/执行协同而非产品定义；完整JD需二次确认。</t>
+        </is>
+      </c>
+      <c r="T48" s="47" t="inlineStr">
+        <is>
+          <t>英文风险中；代码风险低；算法风险低；驻厂/供应链沟通风险中。</t>
+        </is>
+      </c>
+      <c r="U48" s="47" t="inlineStr">
+        <is>
+          <t>Apple官方搜索页可核验标题、发布时间、地点和Role Number；详情页JS渲染，职责需二次确认</t>
+        </is>
+      </c>
+      <c r="V48" s="47" t="inlineStr">
+        <is>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+        </is>
+      </c>
+      <c r="W48" s="47" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="X48" s="47" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Y48" s="47" t="inlineStr">
+        <is>
+          <t>Apple智能硬件/TPM版：突出工业设计、硬件产品、CMF、AI硕士、跨团队项目协作、英文沟通和软硬件结合项目。</t>
+        </is>
+      </c>
+      <c r="Z48" s="47" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AA48" s="17" t="inlineStr">
+        <is>
+          <t>https://jobs.apple.com/en-us/details/200494847-3435/engineering-project-manager-intern-shanghai-shenzhen?team=HRDWR</t>
+        </is>
+      </c>
+      <c r="AB48" s="47" t="n">
+        <v>47</v>
+      </c>
+      <c r="AC48" s="47" t="inlineStr">
+        <is>
+          <t>2026-06-17 Apple miss correction: official Jobs link grade fixed; promoted from expanded to internship.</t>
+        </is>
+      </c>
+      <c r="AD48" s="60" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AE48" s="47" t="n">
+        <v>79</v>
+      </c>
+      <c r="AF48" s="47" t="inlineStr">
+        <is>
+          <t>B档，79分；字段显示主线为主线A-AI终端/智能硬件/TPM/软硬件协同项目，匹配度高，原申请优先级P2今日可投。城市/薪资为深圳/上海、Apple官网未公开，薪资匹配为实习薪资未公开；Apple平台价值高，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球消费电子与软硬件一体化顶级外企，AI终端、硬件工程、供应链和产品体验平台价值极高；JD与可信度为Apple官方搜索页可核验标题、发…、中高，扩源入口需后置核验。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳。</t>
+        </is>
+      </c>
+      <c r="AG48" s="47" t="inlineStr">
+        <is>
+          <t>作为主投池，持续监控</t>
+        </is>
+      </c>
+      <c r="AH48" s="47" t="inlineStr">
+        <is>
+          <t>薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳</t>
+        </is>
+      </c>
+      <c r="AI48" s="47" t="inlineStr">
+        <is>
+          <t>Apple智能硬件/TPM版：突出工业设计、硬件产品、CMF、AI硕士、跨团队项目协作、英文沟通和软硬件结合项目。</t>
+        </is>
+      </c>
+    </row>
     <row r="49" ht="42" customHeight="1"/>
     <row r="50" ht="42" customHeight="1"/>
     <row r="51" ht="42" customHeight="1"/>
@@ -13669,6 +13847,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13680,7 +13859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13885,12 +14064,340 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="56" customHeight="1"/>
-    <row r="3" ht="56" customHeight="1"/>
+    <row r="2" ht="56" customHeight="1">
+      <c r="A2" s="64" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B2" s="64" t="inlineStr">
+        <is>
+          <t>实习岗</t>
+        </is>
+      </c>
+      <c r="C2" s="64" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D2" s="64" t="inlineStr">
+        <is>
+          <t>Engineering Project Manager Intern-Shanghai/ Shenzhen</t>
+        </is>
+      </c>
+      <c r="E2" s="64" t="inlineStr">
+        <is>
+          <t>深圳/上海</t>
+        </is>
+      </c>
+      <c r="F2" s="64" t="inlineStr">
+        <is>
+          <t>Apple官网未公开</t>
+        </is>
+      </c>
+      <c r="G2" s="64" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H2" s="64" t="inlineStr">
+        <is>
+          <t>实习薪资未公开；Apple平台价值高</t>
+        </is>
+      </c>
+      <c r="I2" s="64" t="inlineStr">
+        <is>
+          <t>主线A-AI终端/智能硬件/TPM/软硬件协同项目</t>
+        </is>
+      </c>
+      <c r="J2" s="64" t="inlineStr">
+        <is>
+          <t>P2今日可投</t>
+        </is>
+      </c>
+      <c r="K2" s="64" t="inlineStr">
+        <is>
+          <t>中高</t>
+        </is>
+      </c>
+      <c r="L2" s="64" t="inlineStr">
+        <is>
+          <t>实习/硬件项目管理/EPM/外企</t>
+        </is>
+      </c>
+      <c r="M2" s="64" t="inlineStr">
+        <is>
+          <t>学生岗位，具体年级与专业以Apple JD为准</t>
+        </is>
+      </c>
+      <c r="N2" s="64" t="inlineStr">
+        <is>
+          <t>Apple官网显示Intern岗位；完整JD为JS页面，需投前二次确认每周到岗、实习周期和技术要求</t>
+        </is>
+      </c>
+      <c r="O2" s="64" t="inlineStr">
+        <is>
+          <t>2026-06-11发布；2026-06-17官方搜索页可见</t>
+        </is>
+      </c>
+      <c r="P2" s="64" t="inlineStr">
+        <is>
+          <t>Apple Jobs</t>
+        </is>
+      </c>
+      <c r="Q2" s="64" t="inlineStr">
+        <is>
+          <t>全球消费电子与软硬件一体化顶级外企，AI终端、硬件工程、供应链和产品体验平台价值极高</t>
+        </is>
+      </c>
+      <c r="R2" s="64" t="inlineStr">
+        <is>
+          <t>硬件工程项目管理实习，预计围绕跨职能协作、项目节奏、工程问题跟进、样机/量产节点沟通和供应链协同。</t>
+        </is>
+      </c>
+      <c r="S2" s="64" t="inlineStr">
+        <is>
+          <t>外企英文沟通与硬件工程语境；可能偏EPM/执行协同而非产品定义；完整JD需二次确认。</t>
+        </is>
+      </c>
+      <c r="T2" s="64" t="inlineStr">
+        <is>
+          <t>英文风险中；代码风险低；算法风险低；驻厂/供应链沟通风险中。</t>
+        </is>
+      </c>
+      <c r="U2" s="64" t="inlineStr">
+        <is>
+          <t>Apple官方搜索页可核验标题、发布时间、地点和Role Number；详情页JS渲染，职责需二次确认</t>
+        </is>
+      </c>
+      <c r="V2" s="64" t="inlineStr">
+        <is>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+        </is>
+      </c>
+      <c r="W2" s="64" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="X2" s="64" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Y2" s="64" t="inlineStr">
+        <is>
+          <t>Apple智能硬件/TPM版：突出工业设计、硬件产品、CMF、AI硕士、跨团队项目协作、英文沟通和软硬件结合项目。</t>
+        </is>
+      </c>
+      <c r="Z2" s="64" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AA2" s="17" t="inlineStr">
+        <is>
+          <t>https://jobs.apple.com/en-us/details/200494847-3435/engineering-project-manager-intern-shanghai-shenzhen?team=HRDWR</t>
+        </is>
+      </c>
+      <c r="AB2" s="64" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AC2" s="64" t="n">
+        <v>79</v>
+      </c>
+      <c r="AD2" s="64" t="inlineStr">
+        <is>
+          <t>B档，79分；字段显示主线为主线A-AI终端/智能硬件/TPM/软硬件协同项目，匹配度高，原申请优先级P2今日可投。城市/薪资为深圳/上海、Apple官网未公开，薪资匹配为实习薪资未公开；Apple平台价值高，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球消费电子与软硬件一体化顶级外企，AI终端、硬件工程、供应链和产品体验平台价值极高；JD与可信度为Apple官方搜索页可核验标题、发…、中高，扩源入口需后置核验。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳。</t>
+        </is>
+      </c>
+      <c r="AE2" s="64" t="inlineStr">
+        <is>
+          <t>作为主投池，持续监控</t>
+        </is>
+      </c>
+      <c r="AF2" s="64" t="inlineStr">
+        <is>
+          <t>薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳</t>
+        </is>
+      </c>
+      <c r="AG2" s="64" t="inlineStr">
+        <is>
+          <t>Apple智能硬件/TPM版：突出工业设计、硬件产品、CMF、AI硕士、跨团队项目协作、英文沟通和软硬件结合项目。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="A3" s="64" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B3" s="64" t="inlineStr">
+        <is>
+          <t>次选_条件不完全符合</t>
+        </is>
+      </c>
+      <c r="C3" s="64" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="D3" s="64" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, iPad</t>
+        </is>
+      </c>
+      <c r="E3" s="64" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="F3" s="64" t="inlineStr">
+        <is>
+          <t>Apple官网未公开</t>
+        </is>
+      </c>
+      <c r="G3" s="64" t="inlineStr">
+        <is>
+          <t>中高</t>
+        </is>
+      </c>
+      <c r="H3" s="64" t="inlineStr">
+        <is>
+          <t>薪资未知；Apple平台价值高</t>
+        </is>
+      </c>
+      <c r="I3" s="64" t="inlineStr">
+        <is>
+          <t>主线A-AI终端/智能硬件/TPM/NPI</t>
+        </is>
+      </c>
+      <c r="J3" s="64" t="inlineStr">
+        <is>
+          <t>P3二次确认后投递</t>
+        </is>
+      </c>
+      <c r="K3" s="64" t="inlineStr">
+        <is>
+          <t>中高</t>
+        </is>
+      </c>
+      <c r="L3" s="64" t="inlineStr">
+        <is>
+          <t>正式/TPM/智能硬件/外企</t>
+        </is>
+      </c>
+      <c r="M3" s="64" t="inlineStr">
+        <is>
+          <t>未完整核验</t>
+        </is>
+      </c>
+      <c r="N3" s="64" t="n"/>
+      <c r="O3" s="64" t="inlineStr">
+        <is>
+          <t>Apple官方岗位页，2026-06-12发布</t>
+        </is>
+      </c>
+      <c r="P3" s="64" t="inlineStr">
+        <is>
+          <t>Apple Jobs 官方</t>
+        </is>
+      </c>
+      <c r="Q3" s="64" t="inlineStr">
+        <is>
+          <t>全球消费电子与软硬件一体化顶级外企，iPad硬件与供应链平台价值高</t>
+        </is>
+      </c>
+      <c r="R3" s="64" t="inlineStr">
+        <is>
+          <t>iPad硬件/运营链路的技术项目管理，预计涉及跨职能工程协作、供应链/制造节点、风险跟踪和项目推进。</t>
+        </is>
+      </c>
+      <c r="S3" s="64" t="inlineStr">
+        <is>
+          <t>正式TPM可能要求多年经验；非纯产品经理；英文和硬件工程语境要求高，需二次确认。</t>
+        </is>
+      </c>
+      <c r="T3" s="64" t="inlineStr">
+        <is>
+          <t>英文风险中高；代码风险低；驻厂/供应链沟通风险中。</t>
+        </is>
+      </c>
+      <c r="U3" s="64" t="inlineStr">
+        <is>
+          <t>Apple官方搜索页可核验标题、发布时间、地点和Role Number；详情页JS渲染，职责需二次确认</t>
+        </is>
+      </c>
+      <c r="V3" s="64" t="inlineStr">
+        <is>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+        </is>
+      </c>
+      <c r="W3" s="64" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="X3" s="64" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Y3" s="64" t="inlineStr">
+        <is>
+          <t>Apple智能硬件/TPM版：突出硬件产品、项目协作、NPI/供应链理解、CMF与软硬件结合项目。</t>
+        </is>
+      </c>
+      <c r="Z3" s="64" t="inlineStr">
+        <is>
+          <t>中高</t>
+        </is>
+      </c>
+      <c r="AA3" s="17" t="inlineStr">
+        <is>
+          <t>https://jobs.apple.com/en-us/details/200666248-3435/technical-program-manager-ipad?team=OPMFG</t>
+        </is>
+      </c>
+      <c r="AB3" s="64" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AC3" s="64" t="n">
+        <v>79</v>
+      </c>
+      <c r="AD3" s="64" t="inlineStr">
+        <is>
+          <t>B档，79分；字段显示主线为主线A-AI终端/智能硬件/TPM/NPI，匹配度中高，原申请优先级P3二次确认后投递。城市/薪资为深圳、Apple官网未公开，薪资匹配为薪资未知；Apple平台价值高，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球消费电子与软硬件一体化顶级外企，iPad硬件与供应链平台价值高；JD与可信度为Apple官方搜索页可核验标题、发…、中高，次选表但仍按平台和方向重新排序。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳。</t>
+        </is>
+      </c>
+      <c r="AE3" s="64" t="inlineStr">
+        <is>
+          <t>二次核验后投</t>
+        </is>
+      </c>
+      <c r="AF3" s="64" t="inlineStr">
+        <is>
+          <t>薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳</t>
+        </is>
+      </c>
+      <c r="AG3" s="64" t="inlineStr">
+        <is>
+          <t>Apple智能硬件/TPM版：突出硬件产品、项目协作、NPI/供应链理解、CMF与软硬件结合项目。</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="56" customHeight="1"/>
     <row r="5" ht="56" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:AG1"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13901,7 +14408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ87"/>
+  <dimension ref="A1:AJ88"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="3"/>
@@ -15300,7 +15807,7 @@
       </c>
       <c r="V8" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W8" s="48" t="inlineStr">
@@ -15351,7 +15858,7 @@
       </c>
       <c r="AG8" s="2" t="inlineStr">
         <is>
-          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球大型德系药企；JD与可信度为精确JD、高，次选表但仍按平台和方向重新排序。关键风险：薪资待确认；英文/粤语/IANG；出差/驻厂。</t>
+          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球大型德系药企；JD与可信度为精确JD、高，次选表但仍按平台和方向重新排序。关键风险：薪资待确认；英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AH8" s="2" t="inlineStr">
@@ -15361,7 +15868,7 @@
       </c>
       <c r="AI8" s="2" t="inlineStr">
         <is>
-          <t>薪资待确认；英文/粤语/IANG；出差/驻厂</t>
+          <t>薪资待确认；英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="inlineStr">
@@ -16190,7 +16697,7 @@
       </c>
       <c r="V13" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W13" s="47" t="inlineStr">
@@ -16241,7 +16748,7 @@
       </c>
       <c r="AG13" s="2" t="inlineStr">
         <is>
-          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港跨境物流与电商服务知名公司；JD与可信度为精确JD、高，次选表但仍按平台和方向重新排序。关键风险：薪资待确认；英文/粤语/IANG；出差/驻厂。</t>
+          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港跨境物流与电商服务知名公司；JD与可信度为精确JD、高，次选表但仍按平台和方向重新排序。关键风险：薪资待确认；英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AH13" s="2" t="inlineStr">
@@ -16251,7 +16758,7 @@
       </c>
       <c r="AI13" s="2" t="inlineStr">
         <is>
-          <t>薪资待确认；英文/粤语/IANG；出差/驻厂</t>
+          <t>薪资待确认；英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
         </is>
       </c>
       <c r="AJ13" s="2" t="inlineStr">
@@ -22242,7 +22749,7 @@
       </c>
       <c r="V47" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W47" s="48" t="inlineStr">
@@ -22293,7 +22800,7 @@
       </c>
       <c r="AG47" s="2" t="inlineStr">
         <is>
-          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中高，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为不适用，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：AI 产品创业公司；JD与可信度为精确JD、高，次选表但仍按平台和方向重新排序。关键风险：英文/粤语/IANG；出差/驻厂。</t>
+          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中高，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为不适用，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：AI 产品创业公司；JD与可信度为精确JD、高，次选表但仍按平台和方向重新排序。关键风险：英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AH47" s="2" t="inlineStr">
@@ -22303,7 +22810,7 @@
       </c>
       <c r="AI47" s="2" t="inlineStr">
         <is>
-          <t>英文/粤语/IANG；出差/驻厂</t>
+          <t>英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
         </is>
       </c>
       <c r="AJ47" s="2" t="inlineStr">
@@ -22420,7 +22927,7 @@
       </c>
       <c r="V48" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W48" s="47" t="inlineStr">
@@ -22471,7 +22978,7 @@
       </c>
       <c r="AG48" s="2" t="inlineStr">
         <is>
-          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为不适用，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港 AI 创业团队；JD与可信度为精确JD、高，次选表但仍按平台和方向重新排序。关键风险：英文/粤语/IANG；出差/驻厂。</t>
+          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为不适用，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港 AI 创业团队；JD与可信度为精确JD、高，次选表但仍按平台和方向重新排序。关键风险：英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AH48" s="2" t="inlineStr">
@@ -22481,7 +22988,7 @@
       </c>
       <c r="AI48" s="2" t="inlineStr">
         <is>
-          <t>英文/粤语/IANG；出差/驻厂</t>
+          <t>英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
         </is>
       </c>
       <c r="AJ48" s="2" t="inlineStr">
@@ -23511,7 +24018,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="AA54" s="62" t="inlineStr">
+      <c r="AA54" s="17" t="inlineStr">
         <is>
           <t>https://jobs.apple.com/en-us/details/200658508-3435/product-design-engineer-mechanical?team=HRDWR</t>
         </is>
@@ -23689,7 +24196,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="AA55" s="62" t="inlineStr">
+      <c r="AA55" s="17" t="inlineStr">
         <is>
           <t>https://jobs.apple.com/en-us/details/200644919-3435/manufacturing-design-engineer-intern-shenzhen-changsha?team=STDNT</t>
         </is>
@@ -25438,7 +25945,7 @@
       </c>
       <c r="V65" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W65" s="48" t="inlineStr">
@@ -25794,7 +26301,7 @@
       </c>
       <c r="V67" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="W67" s="48" t="inlineStr">
@@ -28343,42 +28850,42 @@
     <row r="82" ht="56" customHeight="1">
       <c r="A82" s="47" t="inlineStr">
         <is>
-          <t>美团</t>
+          <t>智子芯元（深圳）科技有限责任公司</t>
         </is>
       </c>
       <c r="B82" s="47" t="inlineStr">
         <is>
-          <t>AI硬件产品专员/工程师</t>
+          <t>产品经理（Agent方向）</t>
         </is>
       </c>
       <c r="C82" s="47" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>深圳-龙岗区</t>
         </is>
       </c>
       <c r="D82" s="47" t="inlineStr">
         <is>
-          <t>30-60万/年</t>
+          <t>20-40k·16薪</t>
         </is>
       </c>
       <c r="E82" s="47" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中高</t>
         </is>
       </c>
       <c r="F82" s="47" t="inlineStr">
         <is>
-          <t>达标</t>
+          <t>正式岗薪资达标</t>
         </is>
       </c>
       <c r="G82" s="47" t="inlineStr">
         <is>
-          <t>主线A-AIoT/AI终端/软硬件产品</t>
+          <t>主线B-AI Agent/AI产品/国产算力应用</t>
         </is>
       </c>
       <c r="H82" s="47" t="inlineStr">
         <is>
-          <t>P1主攻</t>
+          <t>P3二次确认后投递</t>
         </is>
       </c>
       <c r="I82" s="47" t="inlineStr">
@@ -28388,67 +28895,63 @@
       </c>
       <c r="J82" s="47" t="inlineStr">
         <is>
-          <t>正式岗/社招低年限</t>
+          <t>社招/AI产品/Agent方向/创业公司</t>
         </is>
       </c>
       <c r="K82" s="47" t="inlineStr">
         <is>
-          <t>本科</t>
-        </is>
-      </c>
-      <c r="L82" s="47" t="inlineStr">
-        <is>
-          <t>1年以下/1-3年AI产品或智能硬件经验优先</t>
-        </is>
-      </c>
+          <t>统招本科</t>
+        </is>
+      </c>
+      <c r="L82" s="47" t="inlineStr"/>
       <c r="M82" s="47" t="inlineStr">
         <is>
-          <t>2026-04-17刷新；2026-05-10检索在线</t>
+          <t>2026-06-17猎聘搜索结果核验</t>
         </is>
       </c>
       <c r="N82" s="47" t="inlineStr">
         <is>
-          <t>好猎头/美团职位页</t>
+          <t>猎聘搜索结果/深圳新闻网公司线索</t>
         </is>
       </c>
       <c r="O82" s="47" t="inlineStr">
         <is>
-          <t>港股上市本地生活与科技零售头部公司，持续投入AI与硬件场景</t>
+          <t>深圳新锐AI公司，公开报道称由深圳市大数据研究院孵化，方向为高性能算子自动发现与优化平台</t>
         </is>
       </c>
       <c r="P82" s="47" t="inlineStr">
         <is>
-          <t>做本地生活、即时零售、无人配送、智能硬件和AI技术落地</t>
+          <t>围绕AI+数学和国产算力生态，研发KernelCAT等高性能算子自动化工具，服务模型在不同算力平台上的部署和优化。</t>
         </is>
       </c>
       <c r="Q82" s="47" t="inlineStr">
         <is>
-          <t>负责AI技术与硬件产品融合落地，输出PRD/功能说明书，协同硬件、算法、嵌入式团队推进研发、联调、测试、量产支持和上市落地。</t>
+          <t>标题为产品经理（Agent方向），预计围绕Agent产品定义、需求转化和AI工具/算子平台场景落地；完整职责需二次确认。</t>
         </is>
       </c>
       <c r="R82" s="47" t="inlineStr">
         <is>
-          <t>页面未列完整福利；投前重点确认五险一金基数、年终/绩效、餐补交通、加班调休和硬件团队工作强度。</t>
+          <t>未核验</t>
         </is>
       </c>
       <c r="S82" s="47" t="inlineStr">
         <is>
-          <t>量产/供应链协同风险；可能涉及硬件技术理解；详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核</t>
+          <t>完整JD未抓取；技术底层偏算子/国产算力，代码和算法理解风险可能偏高；1-3年经验对用户是次选挑战。</t>
         </is>
       </c>
       <c r="T82" s="47" t="inlineStr">
         <is>
-          <t>可能考AI芯片、传感器、嵌入式基础逻辑；非纯代码岗</t>
+          <t>代码/算法风险中高；销售/驻场风险待确认；语言/签证风险低。</t>
         </is>
       </c>
       <c r="U82" s="47" t="inlineStr">
         <is>
-          <t>精确JD</t>
+          <t>猎聘搜索结果/公司岗位列表片段，详情页触发安全验证，需二次确认</t>
         </is>
       </c>
       <c r="V82" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W82" s="47" t="inlineStr">
@@ -28463,17 +28966,17 @@
       </c>
       <c r="Y82" s="47" t="inlineStr">
         <is>
-          <t>AIoT/智能硬件产品版：突出耳机CMF、AI硬件/传感器理解、PRD和跨团队推进</t>
+          <t>AI产品/Agent版：突出AI硕士、Agent/RAG/Prompt、技术抽象到产品需求、原型和跨团队协作。</t>
         </is>
       </c>
       <c r="Z82" s="47" t="inlineStr">
         <is>
-          <t>中高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="AA82" s="62" t="inlineStr">
         <is>
-          <t>https://www.haolietou.com/j_335735</t>
+          <t>https://m.liepin.com/job/1980980707.shtml</t>
         </is>
       </c>
       <c r="AB82" s="47" t="n">
@@ -28481,48 +28984,48 @@
       </c>
       <c r="AC82" s="47" t="inlineStr">
         <is>
-          <t>首次入库日期=2026-05-10</t>
+          <t>首次入库日期=2026-06-17</t>
         </is>
       </c>
       <c r="AD82" s="47" t="inlineStr"/>
-      <c r="AE82" s="61" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="AE82" s="59" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="AF82" s="47" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="AG82" s="47" t="inlineStr">
         <is>
-          <t>C档，50分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度高，原申请优先级P1主攻。城市/薪资为深圳、30-60万/年，薪资匹配为达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：港股上市本地生活与科技零售头部公司，持续投入AI与硬件场景；JD与可信度为精确JD、中高，次选表但仍按平台和方向重新排序。关键风险：资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛。</t>
+          <t>B档，79分；字段显示主线为主线B-AI Agent/AI产品/国产算力应用，匹配度中高，原申请优先级P3二次确认后投递。城市/薪资为深圳-龙岗区、20-40k·16薪，薪资匹配为正式岗薪资达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：深圳新锐AI公司，公开报道称由深圳市大数据研究院孵化，方向为高性能算子自动发现与优…；JD与可信度为猎聘搜索结果/公司岗位列表片段，详…、中，次选表但仍按平台和方向重新排序。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；JD不精确；英文/粤语/IANG；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AH82" s="47" t="inlineStr">
         <is>
-          <t>练手投/暂缓</t>
+          <t>二次核验后投</t>
         </is>
       </c>
       <c r="AI82" s="47" t="inlineStr">
         <is>
-          <t>资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛</t>
+          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；JD不精确；英文/粤语/IANG；招聘状态不稳</t>
         </is>
       </c>
       <c r="AJ82" s="47" t="inlineStr">
         <is>
-          <t>AIoT/智能硬件产品版：突出耳机CMF、AI硬件/传感器理解、PRD和跨团队推进</t>
+          <t>AI产品/Agent版：突出AI硕士、Agent/RAG/Prompt、技术抽象到产品需求、原型和跨团队协作。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="56" customHeight="1">
       <c r="A83" s="47" t="inlineStr">
         <is>
-          <t>深圳欣盛商科技有限公司</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="B83" s="47" t="inlineStr">
         <is>
-          <t>企业AI应用工程师</t>
+          <t>Technical Program Manager, iPad</t>
         </is>
       </c>
       <c r="C83" s="47" t="inlineStr">
@@ -28532,97 +29035,93 @@
       </c>
       <c r="D83" s="47" t="inlineStr">
         <is>
-          <t>1.5-3万</t>
+          <t>Apple官网未公开</t>
         </is>
       </c>
       <c r="E83" s="47" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中高</t>
         </is>
       </c>
       <c r="F83" s="47" t="inlineStr">
         <is>
-          <t>区间上沿达标</t>
+          <t>薪资未知；Apple平台价值高</t>
         </is>
       </c>
       <c r="G83" s="47" t="inlineStr">
         <is>
-          <t>主线B-AI应用落地/AI产品工程师</t>
+          <t>主线A-AI终端/智能硬件/TPM/NPI</t>
         </is>
       </c>
       <c r="H83" s="47" t="inlineStr">
         <is>
-          <t>P1主攻</t>
+          <t>P3二次确认后投递</t>
         </is>
       </c>
       <c r="I83" s="47" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中高</t>
         </is>
       </c>
       <c r="J83" s="47" t="inlineStr">
         <is>
-          <t>正式岗/社招低年限</t>
+          <t>正式/TPM/智能硬件/外企</t>
         </is>
       </c>
       <c r="K83" s="47" t="inlineStr">
         <is>
-          <t>本科</t>
-        </is>
-      </c>
-      <c r="L83" s="47" t="inlineStr">
-        <is>
-          <t>1-3年；懂跨境电商业务与AI工具落地优先</t>
-        </is>
-      </c>
+          <t>未完整核验</t>
+        </is>
+      </c>
+      <c r="L83" s="47" t="inlineStr"/>
       <c r="M83" s="47" t="inlineStr">
         <is>
-          <t>2026-04-15发布；2026-05-16检索在线</t>
+          <t>Apple官方岗位页，2026-06-12发布</t>
         </is>
       </c>
       <c r="N83" s="47" t="inlineStr">
         <is>
-          <t>智联招聘</t>
+          <t>Apple Jobs 官方</t>
         </is>
       </c>
       <c r="O83" s="47" t="inlineStr">
         <is>
-          <t>跨境电商公司，正在把AI能力嵌入运营、客服、物流、合规等业务流程</t>
+          <t>全球消费电子与软硬件一体化顶级外企，iPad硬件与供应链平台价值高</t>
         </is>
       </c>
       <c r="P83" s="47" t="inlineStr">
         <is>
-          <t>做跨境电商经营与供应链运营，推动AI在电商全链路降本增效</t>
+          <t>做iPhone、iPad、Mac、AirPods、Apple Watch、Vision Pro及软硬件生态。</t>
         </is>
       </c>
       <c r="Q83" s="47" t="inlineStr">
         <is>
-          <t>负责模型选型、智能体落地、Prompt/RAG调优、ERP/CRM/电商平台接口打通，并把AI流程真正接入业务环境持续运维。</t>
+          <t>iPad硬件/运营链路的技术项目管理，预计涉及跨职能工程协作、供应链/制造节点、风险跟踪和项目推进。</t>
         </is>
       </c>
       <c r="R83" s="47" t="inlineStr">
         <is>
-          <t>五险一金、带薪年假、法定节假日、节日福利、团建、AI培训。</t>
+          <t>Apple官网未披露该岗位单独福利；以offer和当地政策为准。</t>
         </is>
       </c>
       <c r="S83" s="47" t="inlineStr">
         <is>
-          <t>跨境电商业务节奏快；需要自己扛落地闭环；详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核</t>
+          <t>正式TPM可能要求多年经验；非纯产品经理；英文和硬件工程语境要求高，需二次确认。</t>
         </is>
       </c>
       <c r="T83" s="47" t="inlineStr">
         <is>
-          <t>允许弱代码和系统集成；不是纯算法岗，但需要能和研发/API对接</t>
+          <t>英文风险中高；代码风险低；驻厂/供应链沟通风险中。</t>
         </is>
       </c>
       <c r="U83" s="47" t="inlineStr">
         <is>
-          <t>精确JD</t>
+          <t>Apple官方搜索页可核验标题、发布时间、地点和Role Number；详情页JS渲染，职责需二次确认</t>
         </is>
       </c>
       <c r="V83" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="W83" s="47" t="inlineStr">
@@ -28637,17 +29136,17 @@
       </c>
       <c r="Y83" s="47" t="inlineStr">
         <is>
-          <t>AI业务落地版：突出业务流程梳理、原型/PRD、AI工具选型、跨团队推进和低代码集成</t>
+          <t>Apple智能硬件/TPM版：突出硬件产品、项目协作、NPI/供应链理解、CMF与软硬件结合项目。</t>
         </is>
       </c>
       <c r="Z83" s="47" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="AA83" s="62" t="inlineStr">
-        <is>
-          <t>https://m.zhaopin.com/jobs/CC514239920J40924516115.htm</t>
+          <t>中高</t>
+        </is>
+      </c>
+      <c r="AA83" s="17" t="inlineStr">
+        <is>
+          <t>https://jobs.apple.com/en-us/details/200666248-3435/technical-program-manager-ipad?team=OPMFG</t>
         </is>
       </c>
       <c r="AB83" s="47" t="n">
@@ -28655,48 +29154,48 @@
       </c>
       <c r="AC83" s="47" t="inlineStr">
         <is>
-          <t>首次入库日期=2026-05-16</t>
+          <t>首次入库日期=2026-06-17</t>
         </is>
       </c>
       <c r="AD83" s="47" t="inlineStr"/>
-      <c r="AE83" s="61" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="AE83" s="59" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="AF83" s="47" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="AG83" s="47" t="inlineStr">
         <is>
-          <t>C档，50分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1主攻。城市/薪资为深圳、1.5-3万，薪资匹配为区间上沿达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：跨境电商公司，正在把AI能力嵌入运营、客服、物流、合规等业务流程；JD与可信度为精确JD、高，次选表但仍按平台和方向重新排序。关键风险：资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛；正式岗薪资低于18k新门槛。</t>
+          <t>B档，79分；字段显示主线为主线A-AI终端/智能硬件/TPM/NPI，匹配度中高，原申请优先级P3二次确认后投递。城市/薪资为深圳、Apple官网未公开，薪资匹配为薪资未知；Apple平台价值高，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球消费电子与软硬件一体化顶级外企，iPad硬件与供应链平台价值高；JD与可信度为Apple官方搜索页可核验标题、发…、中高，次选表但仍按平台和方向重新排序。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AH83" s="47" t="inlineStr">
         <is>
-          <t>练手投/暂缓</t>
+          <t>二次核验后投</t>
         </is>
       </c>
       <c r="AI83" s="47" t="inlineStr">
         <is>
-          <t>资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛；正式岗薪资低于18k新门槛</t>
+          <t>薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳</t>
         </is>
       </c>
       <c r="AJ83" s="47" t="inlineStr">
         <is>
-          <t>AI业务落地版：突出业务流程梳理、原型/PRD、AI工具选型、跨团队推进和低代码集成</t>
+          <t>Apple智能硬件/TPM版：突出硬件产品、项目协作、NPI/供应链理解、CMF与软硬件结合项目。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="56" customHeight="1">
       <c r="A84" s="47" t="inlineStr">
         <is>
-          <t>Seeed 矽递科技</t>
+          <t>美团</t>
         </is>
       </c>
       <c r="B84" s="47" t="inlineStr">
         <is>
-          <t>AI产品经理</t>
+          <t>AI硬件产品专员/工程师</t>
         </is>
       </c>
       <c r="C84" s="47" t="inlineStr">
@@ -28706,7 +29205,7 @@
       </c>
       <c r="D84" s="47" t="inlineStr">
         <is>
-          <t>18-26K·13薪</t>
+          <t>30-60万/年</t>
         </is>
       </c>
       <c r="E84" s="47" t="inlineStr">
@@ -28716,7 +29215,7 @@
       </c>
       <c r="F84" s="47" t="inlineStr">
         <is>
-          <t>基本达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="G84" s="47" t="inlineStr">
@@ -28731,7 +29230,7 @@
       </c>
       <c r="I84" s="47" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中高</t>
         </is>
       </c>
       <c r="J84" s="47" t="inlineStr">
@@ -28741,62 +29240,62 @@
       </c>
       <c r="K84" s="47" t="inlineStr">
         <is>
-          <t>本科及以上</t>
+          <t>本科</t>
         </is>
       </c>
       <c r="L84" s="47" t="inlineStr">
         <is>
-          <t>1-3年；AI产品或智能硬件/跨境业务经验优先</t>
+          <t>1年以下/1-3年AI产品或智能硬件经验优先</t>
         </is>
       </c>
       <c r="M84" s="47" t="inlineStr">
         <is>
-          <t>2026-05-16检索到BOSS列表在招</t>
+          <t>2026-04-17刷新；2026-05-10检索在线</t>
         </is>
       </c>
       <c r="N84" s="47" t="inlineStr">
         <is>
-          <t>BOSS直聘列表页 + Seeed公开资料</t>
+          <t>好猎头/美团职位页</t>
         </is>
       </c>
       <c r="O84" s="47" t="inlineStr">
         <is>
-          <t>深圳开源硬件与AI硬件生态头部平台，海外开发者品牌认知强</t>
+          <t>港股上市本地生活与科技零售头部公司，持续投入AI与硬件场景</t>
         </is>
       </c>
       <c r="P84" s="47" t="inlineStr">
         <is>
-          <t>做开源硬件、AI硬件模组、开发板和软硬件生态产品，并服务全球开发者与企业客户</t>
+          <t>做本地生活、即时零售、无人配送、智能硬件和AI技术落地</t>
         </is>
       </c>
       <c r="Q84" s="47" t="inlineStr">
         <is>
-          <t>围绕AI硬件与业务场景设计产品方案，推动AIGC/Agent能力与硬件、内容、电商和开发者生态结合落地。</t>
+          <t>负责AI技术与硬件产品融合落地，输出PRD/功能说明书，协同硬件、算法、嵌入式团队推进研发、联调、测试、量产支持和上市落地。</t>
         </is>
       </c>
       <c r="R84" s="47" t="inlineStr">
         <is>
-          <t>BOSS列表未展示完整福利；投前确认13薪、社保公积金基数、出海业务加班节奏。</t>
+          <t>页面未列完整福利；投前重点确认五险一金基数、年终/绩效、餐补交通、加班调休和硬件团队工作强度。</t>
         </is>
       </c>
       <c r="S84" s="47" t="inlineStr">
         <is>
-          <t>BOSS详情触发安全验证；薪资下沿略低于深圳目标；详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核</t>
+          <t>量产/供应链协同风险；可能涉及硬件技术理解；详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核</t>
         </is>
       </c>
       <c r="T84" s="47" t="inlineStr">
         <is>
-          <t>可能偏英文/出海协作；需理解AI硬件与产品逻辑，非纯代码岗</t>
+          <t>可能考AI芯片、传感器、嵌入式基础逻辑；非纯代码岗</t>
         </is>
       </c>
       <c r="U84" s="47" t="inlineStr">
         <is>
-          <t>列表页核验，需二次确认</t>
+          <t>精确JD</t>
         </is>
       </c>
       <c r="V84" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="W84" s="47" t="inlineStr">
@@ -28811,17 +29310,17 @@
       </c>
       <c r="Y84" s="47" t="inlineStr">
         <is>
-          <t>AI硬件/出海产品版：突出AIoT、硬件理解、用户场景、PRD、跨团队推进和英文资料处理</t>
+          <t>AIoT/智能硬件产品版：突出耳机CMF、AI硬件/传感器理解、PRD和跨团队推进</t>
         </is>
       </c>
       <c r="Z84" s="47" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中高</t>
         </is>
       </c>
       <c r="AA84" s="62" t="inlineStr">
         <is>
-          <t>https://www.zhipin.com/zhaopin/bbec0fec2ff0682003R509i5Ew~~/</t>
+          <t>https://www.haolietou.com/j_335735</t>
         </is>
       </c>
       <c r="AB84" s="47" t="n">
@@ -28829,7 +29328,7 @@
       </c>
       <c r="AC84" s="47" t="inlineStr">
         <is>
-          <t>首次入库日期=2026-05-16</t>
+          <t>首次入库日期=2026-05-10</t>
         </is>
       </c>
       <c r="AD84" s="47" t="inlineStr"/>
@@ -28843,44 +29342,44 @@
       </c>
       <c r="AG84" s="47" t="inlineStr">
         <is>
-          <t>C档，50分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度高，原申请优先级P1主攻。城市/薪资为深圳、18-26K·13薪，薪资匹配为基本达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：深圳开源硬件与AI硬件生态头部平台，海外开发者品牌认知强；JD与可信度为列表页核验，需二次确认、中，次选表但仍按平台和方向重新排序。关键风险：资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛；JD不精确；英文/粤语/IANG；招聘状态不稳。</t>
+          <t>C档，50分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度高，原申请优先级P1主攻。城市/薪资为深圳、30-60万/年，薪资匹配为达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：港股上市本地生活与科技零售头部公司，持续投入AI与硬件场景；JD与可信度为精确JD、中高，次选表但仍按平台和方向重新排序。关键风险：资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛。</t>
         </is>
       </c>
       <c r="AH84" s="47" t="inlineStr">
         <is>
-          <t>观察</t>
+          <t>练手投/暂缓</t>
         </is>
       </c>
       <c r="AI84" s="47" t="inlineStr">
         <is>
-          <t>资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛；JD不精确；英文/粤语/IANG；招聘状态不稳</t>
+          <t>资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛</t>
         </is>
       </c>
       <c r="AJ84" s="47" t="inlineStr">
         <is>
-          <t>AI硬件/出海产品版：突出AIoT、硬件理解、用户场景、PRD、跨团队推进和英文资料处理</t>
+          <t>AIoT/智能硬件产品版：突出耳机CMF、AI硬件/传感器理解、PRD和跨团队推进</t>
         </is>
       </c>
     </row>
     <row r="85" ht="56" customHeight="1">
       <c r="A85" s="47" t="inlineStr">
         <is>
-          <t>玖龙纸业（控股）有限公司</t>
+          <t>深圳欣盛商科技有限公司</t>
         </is>
       </c>
       <c r="B85" s="47" t="inlineStr">
         <is>
-          <t>AI产品经理</t>
+          <t>企业AI应用工程师</t>
         </is>
       </c>
       <c r="C85" s="47" t="inlineStr">
         <is>
-          <t>东莞-麻涌镇</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D85" s="47" t="inlineStr">
         <is>
-          <t>20-40K·14薪</t>
+          <t>1.5-3万</t>
         </is>
       </c>
       <c r="E85" s="47" t="inlineStr">
@@ -28890,7 +29389,7 @@
       </c>
       <c r="F85" s="47" t="inlineStr">
         <is>
-          <t>达标</t>
+          <t>区间上沿达标</t>
         </is>
       </c>
       <c r="G85" s="47" t="inlineStr">
@@ -28915,57 +29414,57 @@
       </c>
       <c r="K85" s="47" t="inlineStr">
         <is>
-          <t>本科及以上</t>
+          <t>本科</t>
         </is>
       </c>
       <c r="L85" s="47" t="inlineStr">
         <is>
-          <t>1-3年；制造业数字化/AI产品经验优先</t>
+          <t>1-3年；懂跨境电商业务与AI工具落地优先</t>
         </is>
       </c>
       <c r="M85" s="47" t="inlineStr">
         <is>
-          <t>2026-05-16检索到智联/聚合页在线</t>
+          <t>2026-04-15发布；2026-05-16检索在线</t>
         </is>
       </c>
       <c r="N85" s="47" t="inlineStr">
         <is>
-          <t>智联招聘搜索结果 + 玖龙纸业公开地址资料</t>
+          <t>智联招聘</t>
         </is>
       </c>
       <c r="O85" s="47" t="inlineStr">
         <is>
-          <t>大型造纸制造集团，适合做生产、仓储、供应链和经营流程的AI应用落地</t>
+          <t>跨境电商公司，正在把AI能力嵌入运营、客服、物流、合规等业务流程</t>
         </is>
       </c>
       <c r="P85" s="47" t="inlineStr">
         <is>
-          <t>做包装纸、文化纸、再生资源和大型制造基地运营，业务流程和数据场景丰富。</t>
+          <t>做跨境电商经营与供应链运营，推动AI在电商全链路降本增效</t>
         </is>
       </c>
       <c r="Q85" s="47" t="inlineStr">
         <is>
-          <t>围绕制造、仓储、计划、财务或运营流程定义AI产品需求，推动AI能力嵌入业务系统并形成可持续闭环。</t>
+          <t>负责模型选型、智能体落地、Prompt/RAG调优、ERP/CRM/电商平台接口打通，并把AI流程真正接入业务环境持续运维。</t>
         </is>
       </c>
       <c r="R85" s="47" t="inlineStr">
         <is>
-          <t>搜索结果显示20-40K·14薪；其他福利需投前确认。</t>
+          <t>五险一金、带薪年假、法定节假日、节日福利、团建、AI培训。</t>
         </is>
       </c>
       <c r="S85" s="47" t="inlineStr">
         <is>
-          <t>制造业现场业务理解要求高；可能需要跨基地协作；详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核</t>
+          <t>跨境电商业务节奏快；需要自己扛落地闭环；详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核</t>
         </is>
       </c>
       <c r="T85" s="47" t="inlineStr">
         <is>
-          <t>偏业务流程产品与AI落地；需和IT/数据团队协作，非纯算法岗</t>
+          <t>允许弱代码和系统集成；不是纯算法岗，但需要能和研发/API对接</t>
         </is>
       </c>
       <c r="U85" s="47" t="inlineStr">
         <is>
-          <t>搜索结果核验，需二次确认</t>
+          <t>精确JD</t>
         </is>
       </c>
       <c r="V85" s="47" t="inlineStr">
@@ -28985,17 +29484,17 @@
       </c>
       <c r="Y85" s="47" t="inlineStr">
         <is>
-          <t>AI业务Agent版：突出流程梳理、制造/供应链场景理解、AI工具落地和跨部门推进</t>
+          <t>AI业务落地版：突出业务流程梳理、原型/PRD、AI工具选型、跨团队推进和低代码集成</t>
         </is>
       </c>
       <c r="Z85" s="47" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="AA85" s="62" t="inlineStr">
         <is>
-          <t>https://www.zhaopin.com/sou/jl765/kw%E7%8E%96%E9%BE%99%E7%BA%B8%E4%B8%9A%20AI%E4%BA%A7%E5%93%81%E7%BB%8F%E7%90%86</t>
+          <t>https://m.zhaopin.com/jobs/CC514239920J40924516115.htm</t>
         </is>
       </c>
       <c r="AB85" s="47" t="n">
@@ -29017,64 +29516,64 @@
       </c>
       <c r="AG85" s="47" t="inlineStr">
         <is>
-          <t>C档，50分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1主攻。城市/薪资为东莞-麻涌镇、20-40K·14薪，薪资匹配为达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：大型造纸制造集团，适合做生产、仓储、供应链和经营流程的AI应用落地；JD与可信度为搜索结果核验，需二次确认、中，次选表但仍按平台和方向重新排序。关键风险：资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛；招聘状态不稳。</t>
+          <t>C档，50分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1主攻。城市/薪资为深圳、1.5-3万，薪资匹配为区间上沿达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：跨境电商公司，正在把AI能力嵌入运营、客服、物流、合规等业务流程；JD与可信度为精确JD、高，次选表但仍按平台和方向重新排序。关键风险：资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛；正式岗薪资低于18k新门槛。</t>
         </is>
       </c>
       <c r="AH85" s="47" t="inlineStr">
         <is>
-          <t>观察</t>
+          <t>练手投/暂缓</t>
         </is>
       </c>
       <c r="AI85" s="47" t="inlineStr">
         <is>
-          <t>资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛；招聘状态不稳</t>
+          <t>资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛；正式岗薪资低于18k新门槛</t>
         </is>
       </c>
       <c r="AJ85" s="47" t="inlineStr">
         <is>
-          <t>AI业务Agent版：突出流程梳理、制造/供应链场景理解、AI工具落地和跨部门推进</t>
+          <t>AI业务落地版：突出业务流程梳理、原型/PRD、AI工具选型、跨团队推进和低代码集成</t>
         </is>
       </c>
     </row>
     <row r="86" ht="56" customHeight="1">
       <c r="A86" s="47" t="inlineStr">
         <is>
-          <t>新明珠集团</t>
+          <t>Seeed 矽递科技</t>
         </is>
       </c>
       <c r="B86" s="47" t="inlineStr">
         <is>
-          <t>AI智能体产品设计师</t>
+          <t>AI产品经理</t>
         </is>
       </c>
       <c r="C86" s="47" t="inlineStr">
         <is>
-          <t>佛山</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D86" s="47" t="inlineStr">
         <is>
-          <t>20-25K</t>
+          <t>18-26K·13薪</t>
         </is>
       </c>
       <c r="E86" s="47" t="inlineStr">
         <is>
-          <t>中高</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F86" s="47" t="inlineStr">
         <is>
-          <t>达标</t>
+          <t>基本达标</t>
         </is>
       </c>
       <c r="G86" s="47" t="inlineStr">
         <is>
-          <t>主线B-AI应用落地/AI产品工程师</t>
+          <t>主线A-AIoT/AI终端/软硬件产品</t>
         </is>
       </c>
       <c r="H86" s="47" t="inlineStr">
         <is>
-          <t>P2验证</t>
+          <t>P1主攻</t>
         </is>
       </c>
       <c r="I86" s="47" t="inlineStr">
@@ -29094,57 +29593,57 @@
       </c>
       <c r="L86" s="47" t="inlineStr">
         <is>
-          <t>1-3年；AI智能体/数字化产品经验优先</t>
+          <t>1-3年；AI产品或智能硬件/跨境业务经验优先</t>
         </is>
       </c>
       <c r="M86" s="47" t="inlineStr">
         <is>
-          <t>2026-05-16检索到鱼泡/聚合页在线</t>
+          <t>2026-05-16检索到BOSS列表在招</t>
         </is>
       </c>
       <c r="N86" s="47" t="inlineStr">
         <is>
-          <t>鱼泡/公开招聘聚合页</t>
+          <t>BOSS直聘列表页 + Seeed公开资料</t>
         </is>
       </c>
       <c r="O86" s="47" t="inlineStr">
         <is>
-          <t>佛山陶瓷与大家居头部集团，正在推进AI智能体和数字化经营工具</t>
+          <t>深圳开源硬件与AI硬件生态头部平台，海外开发者品牌认知强</t>
         </is>
       </c>
       <c r="P86" s="47" t="inlineStr">
         <is>
-          <t>做建筑陶瓷、家居建材和数字化零售/经营系统。</t>
+          <t>做开源硬件、AI硬件模组、开发板和软硬件生态产品，并服务全球开发者与企业客户</t>
         </is>
       </c>
       <c r="Q86" s="47" t="inlineStr">
         <is>
-          <t>负责AI智能体产品设计、业务场景抽象、需求文档、原型和跨部门推进，偏业务流程AI落地。</t>
+          <t>围绕AI硬件与业务场景设计产品方案，推动AIGC/Agent能力与硬件、内容、电商和开发者生态结合落地。</t>
         </is>
       </c>
       <c r="R86" s="47" t="inlineStr">
         <is>
-          <t>聚合页仅展示薪资；投前确认社保公积金、年终、加班和岗位归属。</t>
+          <t>BOSS列表未展示完整福利；投前确认13薪、社保公积金基数、出海业务加班节奏。</t>
         </is>
       </c>
       <c r="S86" s="47" t="inlineStr">
         <is>
-          <t>聚合源可信度有限；传统行业数字化推进节奏需确认；详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核</t>
+          <t>BOSS详情触发安全验证；薪资下沿略低于深圳目标；详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核</t>
         </is>
       </c>
       <c r="T86" s="47" t="inlineStr">
         <is>
-          <t>可能需要理解智能体/知识库/业务系统对接，代码风险中低</t>
+          <t>可能偏英文/出海协作；需理解AI硬件与产品逻辑，非纯代码岗</t>
         </is>
       </c>
       <c r="U86" s="47" t="inlineStr">
         <is>
-          <t>搜索结果核验，需二次确认</t>
+          <t>列表页核验，需二次确认</t>
         </is>
       </c>
       <c r="V86" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W86" s="47" t="inlineStr">
@@ -29159,7 +29658,7 @@
       </c>
       <c r="Y86" s="47" t="inlineStr">
         <is>
-          <t>AI业务Agent版：突出业务流程拆解、智能体场景、原型/PRD和传统行业数字化沟通</t>
+          <t>AI硬件/出海产品版：突出AIoT、硬件理解、用户场景、PRD、跨团队推进和英文资料处理</t>
         </is>
       </c>
       <c r="Z86" s="47" t="inlineStr">
@@ -29169,7 +29668,7 @@
       </c>
       <c r="AA86" s="62" t="inlineStr">
         <is>
-          <t>https://www.yupao.com/s/yp43658691/</t>
+          <t>https://www.zhipin.com/zhaopin/bbec0fec2ff0682003R509i5Ew~~/</t>
         </is>
       </c>
       <c r="AB86" s="47" t="n">
@@ -29191,7 +29690,7 @@
       </c>
       <c r="AG86" s="47" t="inlineStr">
         <is>
-          <t>C档，50分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度中高，原申请优先级P2验证。城市/薪资为佛山、20-25K，薪资匹配为达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：佛山陶瓷与大家居头部集团，正在推进AI智能体和数字化经营工具；JD与可信度为搜索结果核验，需二次确认、中，次选表但仍按平台和方向重新排序。关键风险：资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛；招聘状态不稳。</t>
+          <t>C档，50分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度高，原申请优先级P1主攻。城市/薪资为深圳、18-26K·13薪，薪资匹配为基本达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：深圳开源硬件与AI硬件生态头部平台，海外开发者品牌认知强；JD与可信度为列表页核验，需二次确认、中，次选表但仍按平台和方向重新排序。关键风险：资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛；JD不精确；英文/粤语/IANG；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AH86" s="47" t="inlineStr">
@@ -29201,115 +29700,119 @@
       </c>
       <c r="AI86" s="47" t="inlineStr">
         <is>
-          <t>资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛；招聘状态不稳</t>
+          <t>资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛；JD不精确；英文/粤语/IANG；招聘状态不稳</t>
         </is>
       </c>
       <c r="AJ86" s="47" t="inlineStr">
         <is>
-          <t>AI业务Agent版：突出业务流程拆解、智能体场景、原型/PRD和传统行业数字化沟通</t>
+          <t>AI硬件/出海产品版：突出AIoT、硬件理解、用户场景、PRD、跨团队推进和英文资料处理</t>
         </is>
       </c>
     </row>
     <row r="87" ht="56" customHeight="1">
       <c r="A87" s="47" t="inlineStr">
         <is>
-          <t>智子芯元（深圳）科技有限责任公司</t>
+          <t>玖龙纸业（控股）有限公司</t>
         </is>
       </c>
       <c r="B87" s="47" t="inlineStr">
         <is>
-          <t>产品经理（Agent方向）</t>
+          <t>AI产品经理</t>
         </is>
       </c>
       <c r="C87" s="47" t="inlineStr">
         <is>
-          <t>深圳-龙岗区</t>
+          <t>东莞-麻涌镇</t>
         </is>
       </c>
       <c r="D87" s="47" t="inlineStr">
         <is>
-          <t>20-40k·16薪</t>
+          <t>20-40K·14薪</t>
         </is>
       </c>
       <c r="E87" s="47" t="inlineStr">
         <is>
-          <t>中高</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F87" s="47" t="inlineStr">
         <is>
-          <t>正式岗薪资达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="G87" s="47" t="inlineStr">
         <is>
-          <t>主线B-AI Agent/AI产品/国产算力应用</t>
+          <t>主线B-AI应用落地/AI产品工程师</t>
         </is>
       </c>
       <c r="H87" s="47" t="inlineStr">
         <is>
-          <t>P3二次确认后投递</t>
+          <t>P1主攻</t>
         </is>
       </c>
       <c r="I87" s="47" t="inlineStr">
         <is>
-          <t>中高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="J87" s="47" t="inlineStr">
         <is>
-          <t>社招/AI产品/Agent方向/创业公司</t>
+          <t>正式岗/社招低年限</t>
         </is>
       </c>
       <c r="K87" s="47" t="inlineStr">
         <is>
-          <t>统招本科</t>
-        </is>
-      </c>
-      <c r="L87" s="47" t="inlineStr"/>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="L87" s="47" t="inlineStr">
+        <is>
+          <t>1-3年；制造业数字化/AI产品经验优先</t>
+        </is>
+      </c>
       <c r="M87" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17猎聘搜索结果核验</t>
+          <t>2026-05-16检索到智联/聚合页在线</t>
         </is>
       </c>
       <c r="N87" s="47" t="inlineStr">
         <is>
-          <t>猎聘搜索结果/深圳新闻网公司线索</t>
+          <t>智联招聘搜索结果 + 玖龙纸业公开地址资料</t>
         </is>
       </c>
       <c r="O87" s="47" t="inlineStr">
         <is>
-          <t>深圳新锐AI公司，公开报道称由深圳市大数据研究院孵化，方向为高性能算子自动发现与优化平台</t>
+          <t>大型造纸制造集团，适合做生产、仓储、供应链和经营流程的AI应用落地</t>
         </is>
       </c>
       <c r="P87" s="47" t="inlineStr">
         <is>
-          <t>围绕AI+数学和国产算力生态，研发KernelCAT等高性能算子自动化工具，服务模型在不同算力平台上的部署和优化。</t>
+          <t>做包装纸、文化纸、再生资源和大型制造基地运营，业务流程和数据场景丰富。</t>
         </is>
       </c>
       <c r="Q87" s="47" t="inlineStr">
         <is>
-          <t>标题为产品经理（Agent方向），预计围绕Agent产品定义、需求转化和AI工具/算子平台场景落地；完整职责需二次确认。</t>
+          <t>围绕制造、仓储、计划、财务或运营流程定义AI产品需求，推动AI能力嵌入业务系统并形成可持续闭环。</t>
         </is>
       </c>
       <c r="R87" s="47" t="inlineStr">
         <is>
-          <t>未核验</t>
+          <t>搜索结果显示20-40K·14薪；其他福利需投前确认。</t>
         </is>
       </c>
       <c r="S87" s="47" t="inlineStr">
         <is>
-          <t>完整JD未抓取；技术底层偏算子/国产算力，代码和算法理解风险可能偏高；1-3年经验对用户是次选挑战。</t>
+          <t>制造业现场业务理解要求高；可能需要跨基地协作；详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核</t>
         </is>
       </c>
       <c r="T87" s="47" t="inlineStr">
         <is>
-          <t>代码/算法风险中高；销售/驻场风险待确认；语言/签证风险低。</t>
+          <t>偏业务流程产品与AI落地；需和IT/数据团队协作，非纯算法岗</t>
         </is>
       </c>
       <c r="U87" s="47" t="inlineStr">
         <is>
-          <t>猎聘搜索结果/公司岗位列表片段，详情页触发安全验证，需二次确认</t>
+          <t>搜索结果核验，需二次确认</t>
         </is>
       </c>
       <c r="V87" s="47" t="inlineStr">
@@ -29329,7 +29832,7 @@
       </c>
       <c r="Y87" s="47" t="inlineStr">
         <is>
-          <t>AI产品/Agent版：突出AI硕士、Agent/RAG/Prompt、技术抽象到产品需求、原型和跨团队协作。</t>
+          <t>AI业务Agent版：突出流程梳理、制造/供应链场景理解、AI工具落地和跨部门推进</t>
         </is>
       </c>
       <c r="Z87" s="47" t="inlineStr">
@@ -29339,7 +29842,7 @@
       </c>
       <c r="AA87" s="62" t="inlineStr">
         <is>
-          <t>https://m.liepin.com/job/1980980707.shtml</t>
+          <t>https://www.zhaopin.com/sou/jl765/kw%E7%8E%96%E9%BE%99%E7%BA%B8%E4%B8%9A%20AI%E4%BA%A7%E5%93%81%E7%BB%8F%E7%90%86</t>
         </is>
       </c>
       <c r="AB87" s="47" t="n">
@@ -29347,40 +29850,213 @@
       </c>
       <c r="AC87" s="47" t="inlineStr">
         <is>
-          <t>首次入库日期=2026-06-17</t>
+          <t>首次入库日期=2026-05-16</t>
         </is>
       </c>
       <c r="AD87" s="47" t="inlineStr"/>
-      <c r="AE87" s="59" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="AE87" s="61" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="AF87" s="47" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="AG87" s="47" t="inlineStr">
         <is>
-          <t>B档，79分；字段显示主线为主线B-AI Agent/AI产品/国产算力应用，匹配度中高，原申请优先级P3二次确认后投递。城市/薪资为深圳-龙岗区、20-40k·16薪，薪资匹配为正式岗薪资达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：深圳新锐AI公司，公开报道称由深圳市大数据研究院孵化，方向为高性能算子自动发现与优…；JD与可信度为猎聘搜索结果/公司岗位列表片段，详…、中，次选表但仍按平台和方向重新排序。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；JD不精确；英文/粤语/IANG；招聘状态不稳。</t>
+          <t>C档，50分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1主攻。城市/薪资为东莞-麻涌镇、20-40K·14薪，薪资匹配为达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：大型造纸制造集团，适合做生产、仓储、供应链和经营流程的AI应用落地；JD与可信度为搜索结果核验，需二次确认、中，次选表但仍按平台和方向重新排序。关键风险：资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AH87" s="47" t="inlineStr">
         <is>
-          <t>二次核验后投</t>
+          <t>观察</t>
         </is>
       </c>
       <c r="AI87" s="47" t="inlineStr">
         <is>
-          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；JD不精确；英文/粤语/IANG；招聘状态不稳</t>
+          <t>资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛；招聘状态不稳</t>
         </is>
       </c>
       <c r="AJ87" s="47" t="inlineStr">
         <is>
-          <t>AI产品/Agent版：突出AI硕士、Agent/RAG/Prompt、技术抽象到产品需求、原型和跨团队协作。</t>
+          <t>AI业务Agent版：突出流程梳理、制造/供应链场景理解、AI工具落地和跨部门推进</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="56" customHeight="1"/>
+    <row r="88" ht="56" customHeight="1">
+      <c r="A88" s="47" t="inlineStr">
+        <is>
+          <t>新明珠集团</t>
+        </is>
+      </c>
+      <c r="B88" s="47" t="inlineStr">
+        <is>
+          <t>AI智能体产品设计师</t>
+        </is>
+      </c>
+      <c r="C88" s="47" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="D88" s="47" t="inlineStr">
+        <is>
+          <t>20-25K</t>
+        </is>
+      </c>
+      <c r="E88" s="47" t="inlineStr">
+        <is>
+          <t>中高</t>
+        </is>
+      </c>
+      <c r="F88" s="47" t="inlineStr">
+        <is>
+          <t>达标</t>
+        </is>
+      </c>
+      <c r="G88" s="47" t="inlineStr">
+        <is>
+          <t>主线B-AI应用落地/AI产品工程师</t>
+        </is>
+      </c>
+      <c r="H88" s="47" t="inlineStr">
+        <is>
+          <t>P2验证</t>
+        </is>
+      </c>
+      <c r="I88" s="47" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J88" s="47" t="inlineStr">
+        <is>
+          <t>正式岗/社招低年限</t>
+        </is>
+      </c>
+      <c r="K88" s="47" t="inlineStr">
+        <is>
+          <t>本科及以上</t>
+        </is>
+      </c>
+      <c r="L88" s="47" t="inlineStr">
+        <is>
+          <t>1-3年；AI智能体/数字化产品经验优先</t>
+        </is>
+      </c>
+      <c r="M88" s="47" t="inlineStr">
+        <is>
+          <t>2026-05-16检索到鱼泡/聚合页在线</t>
+        </is>
+      </c>
+      <c r="N88" s="47" t="inlineStr">
+        <is>
+          <t>鱼泡/公开招聘聚合页</t>
+        </is>
+      </c>
+      <c r="O88" s="47" t="inlineStr">
+        <is>
+          <t>佛山陶瓷与大家居头部集团，正在推进AI智能体和数字化经营工具</t>
+        </is>
+      </c>
+      <c r="P88" s="47" t="inlineStr">
+        <is>
+          <t>做建筑陶瓷、家居建材和数字化零售/经营系统。</t>
+        </is>
+      </c>
+      <c r="Q88" s="47" t="inlineStr">
+        <is>
+          <t>负责AI智能体产品设计、业务场景抽象、需求文档、原型和跨部门推进，偏业务流程AI落地。</t>
+        </is>
+      </c>
+      <c r="R88" s="47" t="inlineStr">
+        <is>
+          <t>聚合页仅展示薪资；投前确认社保公积金、年终、加班和岗位归属。</t>
+        </is>
+      </c>
+      <c r="S88" s="47" t="inlineStr">
+        <is>
+          <t>聚合源可信度有限；传统行业数字化推进节奏需确认；详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核</t>
+        </is>
+      </c>
+      <c r="T88" s="47" t="inlineStr">
+        <is>
+          <t>可能需要理解智能体/知识库/业务系统对接，代码风险中低</t>
+        </is>
+      </c>
+      <c r="U88" s="47" t="inlineStr">
+        <is>
+          <t>搜索结果核验，需二次确认</t>
+        </is>
+      </c>
+      <c r="V88" s="47" t="inlineStr">
+        <is>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+        </is>
+      </c>
+      <c r="W88" s="47" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="X88" s="47" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Y88" s="47" t="inlineStr">
+        <is>
+          <t>AI业务Agent版：突出业务流程拆解、智能体场景、原型/PRD和传统行业数字化沟通</t>
+        </is>
+      </c>
+      <c r="Z88" s="47" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AA88" s="62" t="inlineStr">
+        <is>
+          <t>https://www.yupao.com/s/yp43658691/</t>
+        </is>
+      </c>
+      <c r="AB88" s="47" t="n">
+        <v>87</v>
+      </c>
+      <c r="AC88" s="47" t="inlineStr">
+        <is>
+          <t>首次入库日期=2026-05-16</t>
+        </is>
+      </c>
+      <c r="AD88" s="47" t="inlineStr"/>
+      <c r="AE88" s="61" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AF88" s="47" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG88" s="47" t="inlineStr">
+        <is>
+          <t>C档，50分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度中高，原申请优先级P2验证。城市/薪资为佛山、20-25K，薪资匹配为达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：佛山陶瓷与大家居头部集团，正在推进AI智能体和数字化经营工具；JD与可信度为搜索结果核验，需二次确认、中，次选表但仍按平台和方向重新排序。关键风险：资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛；招聘状态不稳。</t>
+        </is>
+      </c>
+      <c r="AH88" s="47" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+      <c r="AI88" s="47" t="inlineStr">
+        <is>
+          <t>资深/高年限硬门槛：详情或任职要求含5年及以上/5+ years硬经验门槛；招聘状态不稳</t>
+        </is>
+      </c>
+      <c r="AJ88" s="47" t="inlineStr">
+        <is>
+          <t>AI业务Agent版：突出业务流程拆解、智能体场景、原型/PRD和传统行业数字化沟通</t>
+        </is>
+      </c>
+    </row>
     <row r="89" ht="56" customHeight="1"/>
     <row r="90" ht="56" customHeight="1"/>
     <row r="91" ht="56" customHeight="1"/>
@@ -29515,6 +30191,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA86" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA88" r:id="rId87"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29526,7 +30203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG161"/>
+  <dimension ref="A1:AG162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -32949,7 +33626,7 @@
       </c>
       <c r="Q21" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R21" s="48" t="inlineStr">
@@ -34434,7 +35111,7 @@
       </c>
       <c r="Q30" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R30" s="47" t="inlineStr">
@@ -34599,7 +35276,7 @@
       </c>
       <c r="Q31" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R31" s="47" t="inlineStr">
@@ -34662,17 +35339,17 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>C档，50分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度高，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球外设龙头与瑞士国际品牌；JD与可信度为精确JD、高，入池岗位。关键风险：资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；薪资待确认；英文/粤语/IANG；出差/驻厂。</t>
+          <t>C档，50分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度高，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球外设龙头与瑞士国际品牌；JD与可信度为精确JD、高，入池岗位。关键风险：资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；薪资待确认；英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AE31" s="2" t="inlineStr">
         <is>
-          <t>练手投/暂缓</t>
+          <t>观察</t>
         </is>
       </c>
       <c r="AF31" s="2" t="inlineStr">
         <is>
-          <t>资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；薪资待确认；英文/粤语/IANG；出差/驻厂</t>
+          <t>资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；薪资待确认；英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
         </is>
       </c>
       <c r="AG31" s="2" t="inlineStr">
@@ -35754,7 +36431,7 @@
       </c>
       <c r="Q38" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R38" s="48" t="inlineStr">
@@ -37404,7 +38081,7 @@
       </c>
       <c r="Q48" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R48" s="48" t="inlineStr">
@@ -38064,7 +38741,7 @@
       </c>
       <c r="Q52" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R52" s="47" t="inlineStr">
@@ -39384,7 +40061,7 @@
       </c>
       <c r="Q60" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R60" s="47" t="inlineStr">
@@ -44825,7 +45502,7 @@
       </c>
       <c r="Q93" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R93" s="48" t="inlineStr">
@@ -45469,7 +46146,7 @@
       </c>
       <c r="Q97" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R97" s="48" t="inlineStr">
@@ -45528,17 +46205,17 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>A档，100分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1主攻。城市/薪资为香港、HK$22,000-28,000/月，薪资匹配为部分达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港本地Agentic AI平台公司，主打企业客服与销售流程自动化；JD与可信度为中高、中高，入池岗位。关键风险：英文/粤语/IANG；招聘状态不稳。</t>
+          <t>A档，100分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1主攻。城市/薪资为香港、HK$22,000-28,000/月，薪资匹配为部分达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港本地Agentic AI平台公司，主打企业客服与销售流程自动化；JD与可信度为中高、中高，入池岗位。关键风险：英文/粤语/IANG。</t>
         </is>
       </c>
       <c r="AE97" s="2" t="inlineStr">
         <is>
-          <t>先核验再投</t>
+          <t>重点准备后投</t>
         </is>
       </c>
       <c r="AF97" s="2" t="inlineStr">
         <is>
-          <t>英文/粤语/IANG；招聘状态不稳</t>
+          <t>英文/粤语/IANG</t>
         </is>
       </c>
       <c r="AG97" s="2" t="inlineStr">
@@ -45630,7 +46307,7 @@
       </c>
       <c r="Q98" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R98" s="48" t="inlineStr">
@@ -45685,7 +46362,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>B档，79分；字段显示主线为主线B-AI应用落地/GenAI业务分析，匹配度中高，原申请优先级P2验证（FDE相邻低代码落地）。城市/薪资为香港、官方未公开，薪资匹配为待确认；香港正式岗需投前问curr…，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：亚洲大型餐饮与零售集团，香港本地业务体量大，公开JD称集团约40,000员工、2,…；JD与可信度为精确JD（LinkedIn公共页完…、高，扩源入口需后置核验。关键风险：薪资待确认；英文/粤语/IANG；代码/技术面。</t>
+          <t>B档，79分；字段显示主线为主线B-AI应用落地/GenAI业务分析，匹配度中高，原申请优先级P2验证（FDE相邻低代码落地）。城市/薪资为香港、官方未公开，薪资匹配为待确认；香港正式岗需投前问curr…，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：亚洲大型餐饮与零售集团，香港本地业务体量大，公开JD称集团约40,000员工、2,…；JD与可信度为精确JD（LinkedIn公共页完…、高，扩源入口需后置核验。关键风险：薪资待确认；英文/粤语/IANG；代码/技术面；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AE98" s="2" t="inlineStr">
@@ -45695,7 +46372,7 @@
       </c>
       <c r="AF98" s="2" t="inlineStr">
         <is>
-          <t>薪资待确认；英文/粤语/IANG；代码/技术面</t>
+          <t>薪资待确认；英文/粤语/IANG；代码/技术面；招聘状态不稳</t>
         </is>
       </c>
       <c r="AG98" s="2" t="inlineStr">
@@ -47554,7 +48231,7 @@
       </c>
       <c r="Q110" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R110" s="48" t="inlineStr">
@@ -47613,7 +48290,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>A档，100分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1。城市/薪资为香港-Kowloon Bay、未公开，薪资匹配为薪资未公开，需投递前问区间，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港AI基础设施/云与数据中心服务公司，方向覆盖异构AI计算与安全Agent工作流。；JD与可信度为岗位卡片核验、中高，扩源入口需后置核验。关键风险：薪资待确认；英文/粤语/IANG。</t>
+          <t>A档，100分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1。城市/薪资为香港-Kowloon Bay、未公开，薪资匹配为薪资未公开，需投递前问区间，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港AI基础设施/云与数据中心服务公司，方向覆盖异构AI计算与安全Agent工作流。；JD与可信度为岗位卡片核验、中高，扩源入口需后置核验。关键风险：薪资待确认；英文/粤语/IANG；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AE110" s="2" t="inlineStr">
@@ -47623,7 +48300,7 @@
       </c>
       <c r="AF110" s="2" t="inlineStr">
         <is>
-          <t>薪资待确认；英文/粤语/IANG</t>
+          <t>薪资待确认；英文/粤语/IANG；招聘状态不稳</t>
         </is>
       </c>
       <c r="AG110" s="2" t="inlineStr">
@@ -47715,7 +48392,7 @@
       </c>
       <c r="Q111" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R111" s="48" t="inlineStr">
@@ -47774,17 +48451,17 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>C档，50分；字段显示主线为备线-AI解决方案/数字化产品/医疗科技产品，匹配度中高，原申请优先级P2。城市/薪资为香港-Science Park、未公开，薪资匹配为薪资未公开，需投递前问区间，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港科学园医疗科技初创，聚焦老龄健康、认知/心理健康评估和干预产品。；JD与可信度为岗位卡片核验、中高，扩源入口需后置核验。关键风险：资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；薪资待确认；英文/粤语/IANG；代码/技术面；招聘状态不稳。</t>
+          <t>C档，50分；字段显示主线为备线-AI解决方案/数字化产品/医疗科技产品，匹配度中高，原申请优先级P2。城市/薪资为香港-Science Park、未公开，薪资匹配为薪资未公开，需投递前问区间，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港科学园医疗科技初创，聚焦老龄健康、认知/心理健康评估和干预产品。；JD与可信度为岗位卡片核验、中高，扩源入口需后置核验。关键风险：资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；薪资待确认；英文/粤语/IANG；代码/技术面。</t>
         </is>
       </c>
       <c r="AE111" s="2" t="inlineStr">
         <is>
-          <t>观察</t>
+          <t>练手投/暂缓</t>
         </is>
       </c>
       <c r="AF111" s="2" t="inlineStr">
         <is>
-          <t>资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；薪资待确认；英文/粤语/IANG；代码/技术面；招聘状态不稳</t>
+          <t>资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；薪资待确认；英文/粤语/IANG；代码/技术面</t>
         </is>
       </c>
       <c r="AG111" s="2" t="inlineStr">
@@ -48198,7 +48875,7 @@
       </c>
       <c r="Q114" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R114" s="48" t="inlineStr">
@@ -48253,21 +48930,21 @@
         </is>
       </c>
       <c r="AC114" s="2" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>A档，96分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1。城市/薪资为香港-Lai Chi Kok、HK$33K-40K/月（公开聚合…，薪资匹配为达标：香港区间高于HKD 25K-…，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：Oursky为香港软件产品工作室，FormX.ai为其AI文档/数据抽取产品，AI…；JD与可信度为岗位卡片核验、中高，扩源入口需后置核验。关键风险：英文/粤语/IANG；销售化；招聘状态不稳。</t>
+          <t>A档，100分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1。城市/薪资为香港-Lai Chi Kok、HK$33K-40K/月（公开聚合…，薪资匹配为达标：香港区间高于HKD 25K-…，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：Oursky为香港软件产品工作室，FormX.ai为其AI文档/数据抽取产品，AI…；JD与可信度为岗位卡片核验、中高，扩源入口需后置核验。关键风险：英文/粤语/IANG；销售化。</t>
         </is>
       </c>
       <c r="AE114" s="2" t="inlineStr">
         <is>
-          <t>先核验再投</t>
+          <t>重点准备后投</t>
         </is>
       </c>
       <c r="AF114" s="2" t="inlineStr">
         <is>
-          <t>英文/粤语/IANG；销售化；招聘状态不稳</t>
+          <t>英文/粤语/IANG；销售化</t>
         </is>
       </c>
       <c r="AG114" s="2" t="inlineStr">
@@ -50979,7 +51656,7 @@
       </c>
       <c r="Q131" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R131" s="47" t="inlineStr">
@@ -51305,7 +51982,7 @@
       </c>
       <c r="Q133" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；公开可见HR活跃状态：刚刚在线</t>
         </is>
       </c>
       <c r="R133" s="47" t="inlineStr">
@@ -51468,7 +52145,7 @@
       </c>
       <c r="Q134" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="R134" s="47" t="inlineStr">
@@ -51631,7 +52308,7 @@
       </c>
       <c r="Q135" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="R135" s="47" t="inlineStr">
@@ -51957,7 +52634,7 @@
       </c>
       <c r="Q137" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="R137" s="47" t="inlineStr">
@@ -52120,7 +52797,7 @@
       </c>
       <c r="Q138" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="R138" s="47" t="inlineStr">
@@ -55682,7 +56359,7 @@
       </c>
       <c r="Q160" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R160" s="47" t="inlineStr">
@@ -55913,7 +56590,163 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="56" customHeight="1"/>
+    <row r="162" ht="56" customHeight="1">
+      <c r="A162" s="47" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B162" s="47" t="inlineStr">
+        <is>
+          <t>Engineering Project Manager Intern-Shanghai/ Shenzhen</t>
+        </is>
+      </c>
+      <c r="C162" s="47" t="inlineStr">
+        <is>
+          <t>深圳/上海</t>
+        </is>
+      </c>
+      <c r="D162" s="47" t="inlineStr">
+        <is>
+          <t>Apple官网未公开</t>
+        </is>
+      </c>
+      <c r="E162" s="47" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F162" s="47" t="inlineStr">
+        <is>
+          <t>实习薪资未公开；Apple平台价值高</t>
+        </is>
+      </c>
+      <c r="G162" s="47" t="inlineStr">
+        <is>
+          <t>主线A-AI终端/智能硬件/TPM/软硬件协同项目</t>
+        </is>
+      </c>
+      <c r="H162" s="47" t="inlineStr">
+        <is>
+          <t>P2今日可投</t>
+        </is>
+      </c>
+      <c r="I162" s="47" t="inlineStr">
+        <is>
+          <t>中高</t>
+        </is>
+      </c>
+      <c r="J162" s="47" t="inlineStr">
+        <is>
+          <t>全球消费电子与软硬件一体化顶级外企，AI终端、硬件工程、供应链和产品体验平台价值极高</t>
+        </is>
+      </c>
+      <c r="K162" s="47" t="inlineStr">
+        <is>
+          <t>做iPhone、iPad、Mac、AirPods、Apple Watch、Vision Pro及软硬件生态。</t>
+        </is>
+      </c>
+      <c r="L162" s="47" t="inlineStr">
+        <is>
+          <t>硬件工程项目管理实习，预计围绕跨职能协作、项目节奏、工程问题跟进、样机/量产节点沟通和供应链协同。</t>
+        </is>
+      </c>
+      <c r="M162" s="47" t="inlineStr">
+        <is>
+          <t>Apple官网未披露该岗位单独福利；以offer和当地政策为准。</t>
+        </is>
+      </c>
+      <c r="N162" s="47" t="inlineStr">
+        <is>
+          <t>外企英文沟通与硬件工程语境；可能偏EPM/执行协同而非产品定义；完整JD需二次确认。</t>
+        </is>
+      </c>
+      <c r="O162" s="47" t="inlineStr">
+        <is>
+          <t>英文风险中；代码风险低；算法风险低；驻厂/供应链沟通风险中。</t>
+        </is>
+      </c>
+      <c r="P162" s="47" t="inlineStr">
+        <is>
+          <t>Apple官方搜索页可核验标题、发布时间、地点和Role Number；详情页JS渲染，职责需二次确认</t>
+        </is>
+      </c>
+      <c r="Q162" s="47" t="inlineStr">
+        <is>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+        </is>
+      </c>
+      <c r="R162" s="47" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="S162" s="47" t="inlineStr">
+        <is>
+          <t>Apple智能硬件/TPM版：突出工业设计、硬件产品、CMF、AI硕士、跨团队项目协作、英文沟通和软硬件结合项目。</t>
+        </is>
+      </c>
+      <c r="T162" s="47" t="inlineStr">
+        <is>
+          <t>中高</t>
+        </is>
+      </c>
+      <c r="U162" s="17" t="inlineStr">
+        <is>
+          <t>https://jobs.apple.com/en-us/details/200494847-3435/engineering-project-manager-intern-shanghai-shenzhen?team=HRDWR</t>
+        </is>
+      </c>
+      <c r="V162" s="47" t="inlineStr">
+        <is>
+          <t>过渡</t>
+        </is>
+      </c>
+      <c r="W162" s="47" t="inlineStr">
+        <is>
+          <t>实习岗</t>
+        </is>
+      </c>
+      <c r="X162" s="47" t="inlineStr"/>
+      <c r="Y162" s="47" t="inlineStr"/>
+      <c r="Z162" s="47" t="inlineStr">
+        <is>
+          <t>今日新增，方向与用户AIoT/AI应用主线相关，建议优先完成投前复核。</t>
+        </is>
+      </c>
+      <c r="AA162" s="47" t="inlineStr">
+        <is>
+          <t>投递前确认薪资、转正/HC、是否强代码、是否驻场出差；按对应简历版本准备项目证据。</t>
+        </is>
+      </c>
+      <c r="AB162" s="59" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AC162" s="47" t="n">
+        <v>79</v>
+      </c>
+      <c r="AD162" s="47" t="inlineStr">
+        <is>
+          <t>B档，79分；字段显示主线为主线A-AI终端/智能硬件/TPM/软硬件协同项目，匹配度高，原申请优先级P2今日可投。城市/薪资为深圳/上海、Apple官网未公开，薪资匹配为实习薪资未公开；Apple平台价值高，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球消费电子与软硬件一体化顶级外企，AI终端、硬件工程、供应链和产品体验平台价值极高；JD与可信度为Apple官方搜索页可核验标题、发…、中高，扩源入口需后置核验。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳。</t>
+        </is>
+      </c>
+      <c r="AE162" s="47" t="inlineStr">
+        <is>
+          <t>作为主投池，持续监控</t>
+        </is>
+      </c>
+      <c r="AF162" s="47" t="inlineStr">
+        <is>
+          <t>薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳</t>
+        </is>
+      </c>
+      <c r="AG162" s="47" t="inlineStr">
+        <is>
+          <t>Apple智能硬件/TPM版：突出工业设计、硬件产品、CMF、AI硕士、跨团队项目协作、英文沟通和软硬件结合项目。</t>
+        </is>
+      </c>
+    </row>
     <row r="163" ht="56" customHeight="1"/>
     <row r="164" ht="56" customHeight="1"/>
     <row r="165" ht="56" customHeight="1"/>
@@ -56084,6 +56917,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U159" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U160" r:id="rId159"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U162" r:id="rId161"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57175,7 +58009,7 @@
       </c>
       <c r="S6" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="T6" s="47" t="inlineStr">
@@ -57251,7 +58085,7 @@
       </c>
       <c r="AI6" s="2" t="inlineStr">
         <is>
-          <t>B档，79分；字段显示主线为主线B-AI应用落地/GenAI业务分析，匹配度中高，原申请优先级P2验证（FDE相邻低代码落地）。城市/薪资为香港、官方未公开，薪资匹配为待确认；香港正式岗需投前问curr…，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：亚洲大型餐饮与零售集团，香港本地业务体量大，公开JD称集团约40,000员工、2,…；JD与可信度为精确JD（LinkedIn公共页完…、高，扩源入口需后置核验。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；英文/粤语/IANG；代码/技术面。</t>
+          <t>B档，79分；字段显示主线为主线B-AI应用落地/GenAI业务分析，匹配度中高，原申请优先级P2验证（FDE相邻低代码落地）。城市/薪资为香港、官方未公开，薪资匹配为待确认；香港正式岗需投前问curr…，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：亚洲大型餐饮与零售集团，香港本地业务体量大，公开JD称集团约40,000员工、2,…；JD与可信度为精确JD（LinkedIn公共页完…、高，扩源入口需后置核验。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；英文/粤语/IANG；代码/技术面；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="inlineStr">
@@ -57261,7 +58095,7 @@
       </c>
       <c r="AK6" s="2" t="inlineStr">
         <is>
-          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；英文/粤语/IANG；代码/技术面</t>
+          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；英文/粤语/IANG；代码/技术面；招聘状态不稳</t>
         </is>
       </c>
       <c r="AL6" s="2" t="inlineStr">
@@ -58771,7 +59605,7 @@
       </c>
       <c r="S15" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="T15" s="47" t="inlineStr">
@@ -59115,7 +59949,7 @@
       </c>
       <c r="S17" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="T17" s="47" t="inlineStr">
@@ -59175,17 +60009,17 @@
       </c>
       <c r="AI17" s="2" t="inlineStr">
         <is>
-          <t>C档，50分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度高，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球外设龙头与瑞士国际品牌；JD与可信度为精确JD、高，扩源入口需后置核验。关键风险：资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；详情或任职要求含5年及以上/5+ years硬经验门槛；薪资待确认；经验偏高；英文/粤语/IANG；出差/驻厂。</t>
+          <t>C档，50分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度高，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球外设龙头与瑞士国际品牌；JD与可信度为精确JD、高，扩源入口需后置核验。关键风险：资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；详情或任职要求含5年及以上/5+ years硬经验门槛；薪资待确认；经验偏高；英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AJ17" s="2" t="inlineStr">
         <is>
-          <t>练手投/暂缓</t>
+          <t>观察</t>
         </is>
       </c>
       <c r="AK17" s="2" t="inlineStr">
         <is>
-          <t>资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；详情或任职要求含5年及以上/5+ years硬经验门槛；薪资待确认；经验偏高；英文/粤语/IANG；出差/驻厂</t>
+          <t>资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；详情或任职要求含5年及以上/5+ years硬经验门槛；薪资待确认；经验偏高；英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
         </is>
       </c>
       <c r="AL17" s="2" t="inlineStr">
@@ -59287,7 +60121,7 @@
       </c>
       <c r="S18" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="T18" s="47" t="inlineStr">
@@ -59363,7 +60197,7 @@
       </c>
       <c r="AI18" s="2" t="inlineStr">
         <is>
-          <t>A档，100分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1。城市/薪资为香港-Kowloon Bay、未公开，薪资匹配为薪资未公开，需投递前问区间，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港AI基础设施/云与数据中心服务公司，方向覆盖异构AI计算与安全Agent工作流。；JD与可信度为岗位卡片核验、中高，扩源入口需后置核验。关键风险：薪资待确认；英文/粤语/IANG。</t>
+          <t>A档，100分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1。城市/薪资为香港-Kowloon Bay、未公开，薪资匹配为薪资未公开，需投递前问区间，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港AI基础设施/云与数据中心服务公司，方向覆盖异构AI计算与安全Agent工作流。；JD与可信度为岗位卡片核验、中高，扩源入口需后置核验。关键风险：薪资待确认；英文/粤语/IANG；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AJ18" s="2" t="inlineStr">
@@ -59373,7 +60207,7 @@
       </c>
       <c r="AK18" s="2" t="inlineStr">
         <is>
-          <t>薪资待确认；英文/粤语/IANG</t>
+          <t>薪资待确认；英文/粤语/IANG；招聘状态不稳</t>
         </is>
       </c>
       <c r="AL18" s="2" t="inlineStr">
@@ -59475,7 +60309,7 @@
       </c>
       <c r="S19" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="T19" s="47" t="inlineStr">
@@ -59551,17 +60385,17 @@
       </c>
       <c r="AI19" s="2" t="inlineStr">
         <is>
-          <t>C档，50分；字段显示主线为备线-AI解决方案/数字化产品/医疗科技产品，匹配度中高，原申请优先级P2。城市/薪资为香港-Science Park、未公开，薪资匹配为薪资未公开，需投递前问区间，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港科学园医疗科技初创，聚焦老龄健康、认知/心理健康评估和干预产品。；JD与可信度为岗位卡片核验、中高，扩源入口需后置核验。关键风险：资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；薪资待确认；英文/粤语/IANG；代码/技术面；招聘状态不稳。</t>
+          <t>C档，50分；字段显示主线为备线-AI解决方案/数字化产品/医疗科技产品，匹配度中高，原申请优先级P2。城市/薪资为香港-Science Park、未公开，薪资匹配为薪资未公开，需投递前问区间，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港科学园医疗科技初创，聚焦老龄健康、认知/心理健康评估和干预产品。；JD与可信度为岗位卡片核验、中高，扩源入口需后置核验。关键风险：资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；薪资待确认；英文/粤语/IANG；代码/技术面。</t>
         </is>
       </c>
       <c r="AJ19" s="2" t="inlineStr">
         <is>
-          <t>观察</t>
+          <t>练手投/暂缓</t>
         </is>
       </c>
       <c r="AK19" s="2" t="inlineStr">
         <is>
-          <t>资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；薪资待确认；英文/粤语/IANG；代码/技术面；招聘状态不稳</t>
+          <t>资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；薪资待确认；英文/粤语/IANG；代码/技术面</t>
         </is>
       </c>
       <c r="AL19" s="2" t="inlineStr">
@@ -60039,7 +60873,7 @@
       </c>
       <c r="S22" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="T22" s="47" t="inlineStr">
@@ -60111,21 +60945,21 @@
         </is>
       </c>
       <c r="AH22" s="2" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AI22" s="2" t="inlineStr">
         <is>
-          <t>A档，96分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1。城市/薪资为香港-Lai Chi Kok、HK$33K-40K/月（公开聚合…，薪资匹配为达标：香港区间高于HKD 25K-…，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：Oursky为香港软件产品工作室，FormX.ai为其AI文档/数据抽取产品，AI…；JD与可信度为岗位卡片核验、中高，扩源入口需后置核验。关键风险：英文/粤语/IANG；销售化；招聘状态不稳。</t>
+          <t>A档，100分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1。城市/薪资为香港-Lai Chi Kok、HK$33K-40K/月（公开聚合…，薪资匹配为达标：香港区间高于HKD 25K-…，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：Oursky为香港软件产品工作室，FormX.ai为其AI文档/数据抽取产品，AI…；JD与可信度为岗位卡片核验、中高，扩源入口需后置核验。关键风险：英文/粤语/IANG；销售化。</t>
         </is>
       </c>
       <c r="AJ22" s="2" t="inlineStr">
         <is>
-          <t>先核验再投</t>
+          <t>重点准备后投</t>
         </is>
       </c>
       <c r="AK22" s="2" t="inlineStr">
         <is>
-          <t>英文/粤语/IANG；销售化；招聘状态不稳</t>
+          <t>英文/粤语/IANG；销售化</t>
         </is>
       </c>
       <c r="AL22" s="2" t="inlineStr">
@@ -60761,7 +61595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E179"/>
+  <dimension ref="A1:E211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -61062,7 +61896,7 @@
           <t>5-10年经验要求明显偏高，聚焦智能运维/AIOps场景，云计算/运维产品深度要求强，不适合当前转型主投。</t>
         </is>
       </c>
-      <c r="E11" s="48" t="inlineStr"/>
+      <c r="E11" s="48" t="n"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="48" t="inlineStr">
@@ -61202,9 +62036,9 @@
           <t>产品经理(AI)(J17248)</t>
         </is>
       </c>
-      <c r="C17" s="48" t="inlineStr"/>
-      <c r="D17" s="48" t="inlineStr"/>
-      <c r="E17" s="48" t="inlineStr"/>
+      <c r="C17" s="48" t="n"/>
+      <c r="D17" s="48" t="n"/>
+      <c r="E17" s="48" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="48" t="inlineStr">
@@ -61217,9 +62051,9 @@
           <t>产品经理</t>
         </is>
       </c>
-      <c r="C18" s="48" t="inlineStr"/>
-      <c r="D18" s="48" t="inlineStr"/>
-      <c r="E18" s="48" t="inlineStr"/>
+      <c r="C18" s="48" t="n"/>
+      <c r="D18" s="48" t="n"/>
+      <c r="E18" s="48" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="48" t="inlineStr">
@@ -61232,9 +62066,9 @@
           <t>高级产品经理（品牌优先）</t>
         </is>
       </c>
-      <c r="C19" s="48" t="inlineStr"/>
-      <c r="D19" s="48" t="inlineStr"/>
-      <c r="E19" s="48" t="inlineStr"/>
+      <c r="C19" s="48" t="n"/>
+      <c r="D19" s="48" t="n"/>
+      <c r="E19" s="48" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="48" t="inlineStr">
@@ -61247,9 +62081,9 @@
           <t>运营商-高阶硬件产品经理-深圳</t>
         </is>
       </c>
-      <c r="C20" s="48" t="inlineStr"/>
-      <c r="D20" s="48" t="inlineStr"/>
-      <c r="E20" s="48" t="inlineStr"/>
+      <c r="C20" s="48" t="n"/>
+      <c r="D20" s="48" t="n"/>
+      <c r="E20" s="48" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="48" t="inlineStr">
@@ -61262,9 +62096,9 @@
           <t>高级产品经理（AI/研发IT平台/制造MES/QMS/项目管理PM）</t>
         </is>
       </c>
-      <c r="C21" s="48" t="inlineStr"/>
-      <c r="D21" s="48" t="inlineStr"/>
-      <c r="E21" s="48" t="inlineStr"/>
+      <c r="C21" s="48" t="n"/>
+      <c r="D21" s="48" t="n"/>
+      <c r="E21" s="48" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="48" t="inlineStr">
@@ -61277,9 +62111,9 @@
           <t>AI产品经理（NAS）</t>
         </is>
       </c>
-      <c r="C22" s="48" t="inlineStr"/>
-      <c r="D22" s="48" t="inlineStr"/>
-      <c r="E22" s="48" t="inlineStr"/>
+      <c r="C22" s="48" t="n"/>
+      <c r="D22" s="48" t="n"/>
+      <c r="E22" s="48" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="48" t="inlineStr">
@@ -61292,9 +62126,9 @@
           <t>APP 产品经理（智能安防）</t>
         </is>
       </c>
-      <c r="C23" s="48" t="inlineStr"/>
-      <c r="D23" s="48" t="inlineStr"/>
-      <c r="E23" s="48" t="inlineStr"/>
+      <c r="C23" s="48" t="n"/>
+      <c r="D23" s="48" t="n"/>
+      <c r="E23" s="48" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="48" t="inlineStr">
@@ -61307,9 +62141,9 @@
           <t>产品策划经理（儿童智能产品深圳）</t>
         </is>
       </c>
-      <c r="C24" s="48" t="inlineStr"/>
-      <c r="D24" s="48" t="inlineStr"/>
-      <c r="E24" s="48" t="inlineStr"/>
+      <c r="C24" s="48" t="n"/>
+      <c r="D24" s="48" t="n"/>
+      <c r="E24" s="48" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="48" t="inlineStr">
@@ -61322,9 +62156,9 @@
           <t>高阶硬件产品经理-深圳</t>
         </is>
       </c>
-      <c r="C25" s="48" t="inlineStr"/>
-      <c r="D25" s="48" t="inlineStr"/>
-      <c r="E25" s="48" t="inlineStr"/>
+      <c r="C25" s="48" t="n"/>
+      <c r="D25" s="48" t="n"/>
+      <c r="E25" s="48" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="48" t="inlineStr">
@@ -61337,9 +62171,9 @@
           <t>智能硬件产品经理</t>
         </is>
       </c>
-      <c r="C26" s="48" t="inlineStr"/>
-      <c r="D26" s="48" t="inlineStr"/>
-      <c r="E26" s="48" t="inlineStr"/>
+      <c r="C26" s="48" t="n"/>
+      <c r="D26" s="48" t="n"/>
+      <c r="E26" s="48" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="48" t="inlineStr">
@@ -61352,9 +62186,9 @@
           <t>高级产品经理（小家电/厨电类/环境类）</t>
         </is>
       </c>
-      <c r="C27" s="48" t="inlineStr"/>
-      <c r="D27" s="48" t="inlineStr"/>
-      <c r="E27" s="48" t="inlineStr"/>
+      <c r="C27" s="48" t="n"/>
+      <c r="D27" s="48" t="n"/>
+      <c r="E27" s="48" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="48" t="inlineStr">
@@ -61367,9 +62201,9 @@
           <t>智能硬件产品经理（医疗设备）深圳</t>
         </is>
       </c>
-      <c r="C28" s="48" t="inlineStr"/>
-      <c r="D28" s="48" t="inlineStr"/>
-      <c r="E28" s="48" t="inlineStr"/>
+      <c r="C28" s="48" t="n"/>
+      <c r="D28" s="48" t="n"/>
+      <c r="E28" s="48" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="48" t="inlineStr">
@@ -61382,9 +62216,9 @@
           <t>手机整机产品经理（智能硬件知名企业）</t>
         </is>
       </c>
-      <c r="C29" s="48" t="inlineStr"/>
-      <c r="D29" s="48" t="inlineStr"/>
-      <c r="E29" s="48" t="inlineStr"/>
+      <c r="C29" s="48" t="n"/>
+      <c r="D29" s="48" t="n"/>
+      <c r="E29" s="48" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="48" t="inlineStr">
@@ -61397,9 +62231,9 @@
           <t>智能硬件产品经理-深圳/杭州</t>
         </is>
       </c>
-      <c r="C30" s="48" t="inlineStr"/>
-      <c r="D30" s="48" t="inlineStr"/>
-      <c r="E30" s="48" t="inlineStr"/>
+      <c r="C30" s="48" t="n"/>
+      <c r="D30" s="48" t="n"/>
+      <c r="E30" s="48" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="48" t="inlineStr">
@@ -61412,9 +62246,9 @@
           <t>产品经理（智能玩具与游戏产品/智能硬件方向/深圳或佛山）</t>
         </is>
       </c>
-      <c r="C31" s="48" t="inlineStr"/>
-      <c r="D31" s="48" t="inlineStr"/>
-      <c r="E31" s="48" t="inlineStr"/>
+      <c r="C31" s="48" t="n"/>
+      <c r="D31" s="48" t="n"/>
+      <c r="E31" s="48" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="48" t="inlineStr">
@@ -61427,9 +62261,9 @@
           <t>产品经理</t>
         </is>
       </c>
-      <c r="C32" s="48" t="inlineStr"/>
-      <c r="D32" s="48" t="inlineStr"/>
-      <c r="E32" s="48" t="inlineStr"/>
+      <c r="C32" s="48" t="n"/>
+      <c r="D32" s="48" t="n"/>
+      <c r="E32" s="48" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="48" t="inlineStr">
@@ -61442,9 +62276,9 @@
           <t>产品企划高级工程师/产品经理-AI（库卡）</t>
         </is>
       </c>
-      <c r="C33" s="48" t="inlineStr"/>
-      <c r="D33" s="48" t="inlineStr"/>
-      <c r="E33" s="48" t="inlineStr"/>
+      <c r="C33" s="48" t="n"/>
+      <c r="D33" s="48" t="n"/>
+      <c r="E33" s="48" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="48" t="inlineStr">
@@ -61457,9 +62291,9 @@
           <t>工业高级产品经理</t>
         </is>
       </c>
-      <c r="C34" s="48" t="inlineStr"/>
-      <c r="D34" s="48" t="inlineStr"/>
-      <c r="E34" s="48" t="inlineStr"/>
+      <c r="C34" s="48" t="n"/>
+      <c r="D34" s="48" t="n"/>
+      <c r="E34" s="48" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="48" t="inlineStr">
@@ -61472,9 +62306,9 @@
           <t>PM项目经理/高级经理（精密制造/机器人/AI终端）</t>
         </is>
       </c>
-      <c r="C35" s="48" t="inlineStr"/>
-      <c r="D35" s="48" t="inlineStr"/>
-      <c r="E35" s="48" t="inlineStr"/>
+      <c r="C35" s="48" t="n"/>
+      <c r="D35" s="48" t="n"/>
+      <c r="E35" s="48" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="48" t="inlineStr">
@@ -61487,9 +62321,9 @@
           <t>PM项目经理/高级经理（精密制造/机器人/AI终端）</t>
         </is>
       </c>
-      <c r="C36" s="48" t="inlineStr"/>
-      <c r="D36" s="48" t="inlineStr"/>
-      <c r="E36" s="48" t="inlineStr"/>
+      <c r="C36" s="48" t="n"/>
+      <c r="D36" s="48" t="n"/>
+      <c r="E36" s="48" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="48" t="inlineStr">
@@ -61502,9 +62336,9 @@
           <t>智能硬件产品经理</t>
         </is>
       </c>
-      <c r="C37" s="48" t="inlineStr"/>
-      <c r="D37" s="48" t="inlineStr"/>
-      <c r="E37" s="48" t="inlineStr"/>
+      <c r="C37" s="48" t="n"/>
+      <c r="D37" s="48" t="n"/>
+      <c r="E37" s="48" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="48" t="inlineStr">
@@ -61517,9 +62351,9 @@
           <t>产品经理（人机交互方向）-广州或杭州</t>
         </is>
       </c>
-      <c r="C38" s="48" t="inlineStr"/>
-      <c r="D38" s="48" t="inlineStr"/>
-      <c r="E38" s="48" t="inlineStr"/>
+      <c r="C38" s="48" t="n"/>
+      <c r="D38" s="48" t="n"/>
+      <c r="E38" s="48" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="48" t="inlineStr">
@@ -61532,9 +62366,9 @@
           <t>机器人产品经理（软件）（Leader）AI智能硬件</t>
         </is>
       </c>
-      <c r="C39" s="48" t="inlineStr"/>
-      <c r="D39" s="48" t="inlineStr"/>
-      <c r="E39" s="48" t="inlineStr"/>
+      <c r="C39" s="48" t="n"/>
+      <c r="D39" s="48" t="n"/>
+      <c r="E39" s="48" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="48" t="inlineStr">
@@ -61547,9 +62381,9 @@
           <t>高级智能硬件产品经理 (爆品体系构建者)</t>
         </is>
       </c>
-      <c r="C40" s="48" t="inlineStr"/>
-      <c r="D40" s="48" t="inlineStr"/>
-      <c r="E40" s="48" t="inlineStr"/>
+      <c r="C40" s="48" t="n"/>
+      <c r="D40" s="48" t="n"/>
+      <c r="E40" s="48" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="48" t="inlineStr">
@@ -61562,9 +62396,9 @@
           <t>智能硬件产品经理</t>
         </is>
       </c>
-      <c r="C41" s="48" t="inlineStr"/>
-      <c r="D41" s="48" t="inlineStr"/>
-      <c r="E41" s="48" t="inlineStr"/>
+      <c r="C41" s="48" t="n"/>
+      <c r="D41" s="48" t="n"/>
+      <c r="E41" s="48" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="48" t="inlineStr">
@@ -61577,9 +62411,9 @@
           <t>智能硬件产品经理</t>
         </is>
       </c>
-      <c r="C42" s="48" t="inlineStr"/>
-      <c r="D42" s="48" t="inlineStr"/>
-      <c r="E42" s="48" t="inlineStr"/>
+      <c r="C42" s="48" t="n"/>
+      <c r="D42" s="48" t="n"/>
+      <c r="E42" s="48" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="48" t="inlineStr">
@@ -61592,9 +62426,9 @@
           <t>AI 产品经理 智能硬件行业</t>
         </is>
       </c>
-      <c r="C43" s="48" t="inlineStr"/>
-      <c r="D43" s="48" t="inlineStr"/>
-      <c r="E43" s="48" t="inlineStr"/>
+      <c r="C43" s="48" t="n"/>
+      <c r="D43" s="48" t="n"/>
+      <c r="E43" s="48" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="48" t="inlineStr">
@@ -61607,9 +62441,9 @@
           <t>宠物智能产品经理</t>
         </is>
       </c>
-      <c r="C44" s="48" t="inlineStr"/>
-      <c r="D44" s="48" t="inlineStr"/>
-      <c r="E44" s="48" t="inlineStr"/>
+      <c r="C44" s="48" t="n"/>
+      <c r="D44" s="48" t="n"/>
+      <c r="E44" s="48" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="48" t="inlineStr">
@@ -61622,9 +62456,9 @@
           <t>储能软件产品负责人</t>
         </is>
       </c>
-      <c r="C45" s="48" t="inlineStr"/>
-      <c r="D45" s="48" t="inlineStr"/>
-      <c r="E45" s="48" t="inlineStr"/>
+      <c r="C45" s="48" t="n"/>
+      <c r="D45" s="48" t="n"/>
+      <c r="E45" s="48" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="48" t="inlineStr">
@@ -61637,9 +62471,9 @@
           <t>高级数据产品经理（Data Agent方向）</t>
         </is>
       </c>
-      <c r="C46" s="48" t="inlineStr"/>
-      <c r="D46" s="48" t="inlineStr"/>
-      <c r="E46" s="48" t="inlineStr"/>
+      <c r="C46" s="48" t="n"/>
+      <c r="D46" s="48" t="n"/>
+      <c r="E46" s="48" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="48" t="inlineStr">
@@ -61652,9 +62486,9 @@
           <t>AI增值应用产品经理</t>
         </is>
       </c>
-      <c r="C47" s="48" t="inlineStr"/>
-      <c r="D47" s="48" t="inlineStr"/>
-      <c r="E47" s="48" t="inlineStr"/>
+      <c r="C47" s="48" t="n"/>
+      <c r="D47" s="48" t="n"/>
+      <c r="E47" s="48" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="48" t="inlineStr">
@@ -61667,9 +62501,9 @@
           <t>AI智能硬件产品专家</t>
         </is>
       </c>
-      <c r="C48" s="48" t="inlineStr"/>
-      <c r="D48" s="48" t="inlineStr"/>
-      <c r="E48" s="48" t="inlineStr"/>
+      <c r="C48" s="48" t="n"/>
+      <c r="D48" s="48" t="n"/>
+      <c r="E48" s="48" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="48" t="inlineStr">
@@ -61682,9 +62516,9 @@
           <t>AI应用研发校招实习生（阿里27年校招）</t>
         </is>
       </c>
-      <c r="C49" s="48" t="inlineStr"/>
-      <c r="D49" s="48" t="inlineStr"/>
-      <c r="E49" s="48" t="inlineStr"/>
+      <c r="C49" s="48" t="n"/>
+      <c r="D49" s="48" t="n"/>
+      <c r="E49" s="48" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="48" t="inlineStr">
@@ -61697,9 +62531,9 @@
           <t>AI应用研发实习生（27年阿里校招）</t>
         </is>
       </c>
-      <c r="C50" s="48" t="inlineStr"/>
-      <c r="D50" s="48" t="inlineStr"/>
-      <c r="E50" s="48" t="inlineStr"/>
+      <c r="C50" s="48" t="n"/>
+      <c r="D50" s="48" t="n"/>
+      <c r="E50" s="48" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="48" t="inlineStr">
@@ -61712,9 +62546,9 @@
           <t>AI 产品经理</t>
         </is>
       </c>
-      <c r="C51" s="48" t="inlineStr"/>
-      <c r="D51" s="48" t="inlineStr"/>
-      <c r="E51" s="48" t="inlineStr"/>
+      <c r="C51" s="48" t="n"/>
+      <c r="D51" s="48" t="n"/>
+      <c r="E51" s="48" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="48" t="inlineStr">
@@ -61727,9 +62561,9 @@
           <t>智慧屏显产品经理</t>
         </is>
       </c>
-      <c r="C52" s="48" t="inlineStr"/>
-      <c r="D52" s="48" t="inlineStr"/>
-      <c r="E52" s="48" t="inlineStr"/>
+      <c r="C52" s="48" t="n"/>
+      <c r="D52" s="48" t="n"/>
+      <c r="E52" s="48" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="48" t="inlineStr">
@@ -61742,9 +62576,9 @@
           <t>AI 产品经理 AI 应用方向</t>
         </is>
       </c>
-      <c r="C53" s="48" t="inlineStr"/>
-      <c r="D53" s="48" t="inlineStr"/>
-      <c r="E53" s="48" t="inlineStr"/>
+      <c r="C53" s="48" t="n"/>
+      <c r="D53" s="48" t="n"/>
+      <c r="E53" s="48" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="48" t="inlineStr">
@@ -61757,9 +62591,9 @@
           <t>AI 产品经理</t>
         </is>
       </c>
-      <c r="C54" s="48" t="inlineStr"/>
-      <c r="D54" s="48" t="inlineStr"/>
-      <c r="E54" s="48" t="inlineStr"/>
+      <c r="C54" s="48" t="n"/>
+      <c r="D54" s="48" t="n"/>
+      <c r="E54" s="48" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="48" t="inlineStr">
@@ -61772,9 +62606,9 @@
           <t>新能源生态产品经理</t>
         </is>
       </c>
-      <c r="C55" s="48" t="inlineStr"/>
-      <c r="D55" s="48" t="inlineStr"/>
-      <c r="E55" s="48" t="inlineStr"/>
+      <c r="C55" s="48" t="n"/>
+      <c r="D55" s="48" t="n"/>
+      <c r="E55" s="48" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="48" t="inlineStr">
@@ -61787,9 +62621,9 @@
           <t>电工能源产品经理</t>
         </is>
       </c>
-      <c r="C56" s="48" t="inlineStr"/>
-      <c r="D56" s="48" t="inlineStr"/>
-      <c r="E56" s="48" t="inlineStr"/>
+      <c r="C56" s="48" t="n"/>
+      <c r="D56" s="48" t="n"/>
+      <c r="E56" s="48" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="48" t="inlineStr">
@@ -61802,9 +62636,9 @@
           <t>智能硬件产品经理</t>
         </is>
       </c>
-      <c r="C57" s="48" t="inlineStr"/>
-      <c r="D57" s="48" t="inlineStr"/>
-      <c r="E57" s="48" t="inlineStr"/>
+      <c r="C57" s="48" t="n"/>
+      <c r="D57" s="48" t="n"/>
+      <c r="E57" s="48" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="48" t="inlineStr">
@@ -61817,9 +62651,9 @@
           <t>智能硬件产品经理</t>
         </is>
       </c>
-      <c r="C58" s="48" t="inlineStr"/>
-      <c r="D58" s="48" t="inlineStr"/>
-      <c r="E58" s="48" t="inlineStr"/>
+      <c r="C58" s="48" t="n"/>
+      <c r="D58" s="48" t="n"/>
+      <c r="E58" s="48" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="48" t="inlineStr">
@@ -61832,9 +62666,9 @@
           <t>AI产品经理</t>
         </is>
       </c>
-      <c r="C59" s="48" t="inlineStr"/>
-      <c r="D59" s="48" t="inlineStr"/>
-      <c r="E59" s="48" t="inlineStr"/>
+      <c r="C59" s="48" t="n"/>
+      <c r="D59" s="48" t="n"/>
+      <c r="E59" s="48" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="48" t="inlineStr">
@@ -61847,9 +62681,9 @@
           <t>AI产品经理</t>
         </is>
       </c>
-      <c r="C60" s="48" t="inlineStr"/>
-      <c r="D60" s="48" t="inlineStr"/>
-      <c r="E60" s="48" t="inlineStr"/>
+      <c r="C60" s="48" t="n"/>
+      <c r="D60" s="48" t="n"/>
+      <c r="E60" s="48" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="48" t="inlineStr">
@@ -61862,9 +62696,9 @@
           <t>AI智能体产品设计师</t>
         </is>
       </c>
-      <c r="C61" s="48" t="inlineStr"/>
-      <c r="D61" s="48" t="inlineStr"/>
-      <c r="E61" s="48" t="inlineStr"/>
+      <c r="C61" s="48" t="n"/>
+      <c r="D61" s="48" t="n"/>
+      <c r="E61" s="48" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="48" t="inlineStr">
@@ -61877,9 +62711,9 @@
           <t>大模型产品经理</t>
         </is>
       </c>
-      <c r="C62" s="48" t="inlineStr"/>
-      <c r="D62" s="48" t="inlineStr"/>
-      <c r="E62" s="48" t="inlineStr"/>
+      <c r="C62" s="48" t="n"/>
+      <c r="D62" s="48" t="n"/>
+      <c r="E62" s="48" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="48" t="inlineStr">
@@ -61892,9 +62726,9 @@
           <t>企业AI应用工程师</t>
         </is>
       </c>
-      <c r="C63" s="48" t="inlineStr"/>
-      <c r="D63" s="48" t="inlineStr"/>
-      <c r="E63" s="48" t="inlineStr"/>
+      <c r="C63" s="48" t="n"/>
+      <c r="D63" s="48" t="n"/>
+      <c r="E63" s="48" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="48" t="inlineStr">
@@ -61907,9 +62741,9 @@
           <t>用户产品经理（AI方向）</t>
         </is>
       </c>
-      <c r="C64" s="48" t="inlineStr"/>
-      <c r="D64" s="48" t="inlineStr"/>
-      <c r="E64" s="48" t="inlineStr"/>
+      <c r="C64" s="48" t="n"/>
+      <c r="D64" s="48" t="n"/>
+      <c r="E64" s="48" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="48" t="inlineStr">
@@ -61922,9 +62756,9 @@
           <t>AI产品经理（银行AI Agent平台）</t>
         </is>
       </c>
-      <c r="C65" s="48" t="inlineStr"/>
-      <c r="D65" s="48" t="inlineStr"/>
-      <c r="E65" s="48" t="inlineStr"/>
+      <c r="C65" s="48" t="n"/>
+      <c r="D65" s="48" t="n"/>
+      <c r="E65" s="48" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="48" t="inlineStr">
@@ -61937,9 +62771,9 @@
           <t>AI产品经理（日语/海外AI-IDP方向）</t>
         </is>
       </c>
-      <c r="C66" s="48" t="inlineStr"/>
-      <c r="D66" s="48" t="inlineStr"/>
-      <c r="E66" s="48" t="inlineStr"/>
+      <c r="C66" s="48" t="n"/>
+      <c r="D66" s="48" t="n"/>
+      <c r="E66" s="48" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="48" t="inlineStr">
@@ -61952,9 +62786,9 @@
           <t>AI智能体（Agent）产品经理 J17413</t>
         </is>
       </c>
-      <c r="C67" s="48" t="inlineStr"/>
-      <c r="D67" s="48" t="inlineStr"/>
-      <c r="E67" s="48" t="inlineStr"/>
+      <c r="C67" s="48" t="n"/>
+      <c r="D67" s="48" t="n"/>
+      <c r="E67" s="48" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="48" t="inlineStr">
@@ -61967,9 +62801,9 @@
           <t>AI产品经理（AI学习/画像方向）</t>
         </is>
       </c>
-      <c r="C68" s="48" t="inlineStr"/>
-      <c r="D68" s="48" t="inlineStr"/>
-      <c r="E68" s="48" t="inlineStr"/>
+      <c r="C68" s="48" t="n"/>
+      <c r="D68" s="48" t="n"/>
+      <c r="E68" s="48" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="48" t="inlineStr">
@@ -61982,9 +62816,9 @@
           <t>AI Application Product Manager</t>
         </is>
       </c>
-      <c r="C69" s="48" t="inlineStr"/>
-      <c r="D69" s="48" t="inlineStr"/>
-      <c r="E69" s="48" t="inlineStr"/>
+      <c r="C69" s="48" t="n"/>
+      <c r="D69" s="48" t="n"/>
+      <c r="E69" s="48" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="48" t="inlineStr">
@@ -61997,9 +62831,9 @@
           <t>AI Product Manager / Owner (ERP project)</t>
         </is>
       </c>
-      <c r="C70" s="48" t="inlineStr"/>
-      <c r="D70" s="48" t="inlineStr"/>
-      <c r="E70" s="48" t="inlineStr"/>
+      <c r="C70" s="48" t="n"/>
+      <c r="D70" s="48" t="n"/>
+      <c r="E70" s="48" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="48" t="inlineStr">
@@ -62012,9 +62846,9 @@
           <t>Product Manager - AI Rich Media Solution</t>
         </is>
       </c>
-      <c r="C71" s="48" t="inlineStr"/>
-      <c r="D71" s="48" t="inlineStr"/>
-      <c r="E71" s="48" t="inlineStr"/>
+      <c r="C71" s="48" t="n"/>
+      <c r="D71" s="48" t="n"/>
+      <c r="E71" s="48" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="48" t="inlineStr">
@@ -62027,9 +62861,9 @@
           <t>智能组网产品经理</t>
         </is>
       </c>
-      <c r="C72" s="48" t="inlineStr"/>
-      <c r="D72" s="48" t="inlineStr"/>
-      <c r="E72" s="48" t="inlineStr"/>
+      <c r="C72" s="48" t="n"/>
+      <c r="D72" s="48" t="n"/>
+      <c r="E72" s="48" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="48" t="inlineStr">
@@ -62042,9 +62876,9 @@
           <t>高级平台硬件产品经理（机器人）</t>
         </is>
       </c>
-      <c r="C73" s="48" t="inlineStr"/>
-      <c r="D73" s="48" t="inlineStr"/>
-      <c r="E73" s="48" t="inlineStr"/>
+      <c r="C73" s="48" t="n"/>
+      <c r="D73" s="48" t="n"/>
+      <c r="E73" s="48" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="48" t="inlineStr">
@@ -62057,9 +62891,9 @@
           <t>Product Owner (AI Solution, Cantonese Required)</t>
         </is>
       </c>
-      <c r="C74" s="48" t="inlineStr"/>
-      <c r="D74" s="48" t="inlineStr"/>
-      <c r="E74" s="48" t="inlineStr"/>
+      <c r="C74" s="48" t="n"/>
+      <c r="D74" s="48" t="n"/>
+      <c r="E74" s="48" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="48" t="inlineStr">
@@ -62072,9 +62906,9 @@
           <t>Business Analyst / Project Manager / Product Owner (Bank, AI Transformation)</t>
         </is>
       </c>
-      <c r="C75" s="48" t="inlineStr"/>
-      <c r="D75" s="48" t="inlineStr"/>
-      <c r="E75" s="48" t="inlineStr"/>
+      <c r="C75" s="48" t="n"/>
+      <c r="D75" s="48" t="n"/>
+      <c r="E75" s="48" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="48" t="inlineStr">
@@ -62087,9 +62921,9 @@
           <t>AIGC产品经理</t>
         </is>
       </c>
-      <c r="C76" s="48" t="inlineStr"/>
-      <c r="D76" s="48" t="inlineStr"/>
-      <c r="E76" s="48" t="inlineStr"/>
+      <c r="C76" s="48" t="n"/>
+      <c r="D76" s="48" t="n"/>
+      <c r="E76" s="48" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="48" t="inlineStr">
@@ -62102,9 +62936,9 @@
           <t>AI应用工程师</t>
         </is>
       </c>
-      <c r="C77" s="48" t="inlineStr"/>
-      <c r="D77" s="48" t="inlineStr"/>
-      <c r="E77" s="48" t="inlineStr"/>
+      <c r="C77" s="48" t="n"/>
+      <c r="D77" s="48" t="n"/>
+      <c r="E77" s="48" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="48" t="inlineStr">
@@ -62117,9 +62951,9 @@
           <t>高级AI应用工程师（可在广州/长沙）</t>
         </is>
       </c>
-      <c r="C78" s="48" t="inlineStr"/>
-      <c r="D78" s="48" t="inlineStr"/>
-      <c r="E78" s="48" t="inlineStr"/>
+      <c r="C78" s="48" t="n"/>
+      <c r="D78" s="48" t="n"/>
+      <c r="E78" s="48" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="48" t="inlineStr">
@@ -62132,9 +62966,9 @@
           <t>AI应用工程师（广州）</t>
         </is>
       </c>
-      <c r="C79" s="48" t="inlineStr"/>
-      <c r="D79" s="48" t="inlineStr"/>
-      <c r="E79" s="48" t="inlineStr"/>
+      <c r="C79" s="48" t="n"/>
+      <c r="D79" s="48" t="n"/>
+      <c r="E79" s="48" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="48" t="inlineStr">
@@ -62147,9 +62981,9 @@
           <t>AI应用开发工程师</t>
         </is>
       </c>
-      <c r="C80" s="48" t="inlineStr"/>
-      <c r="D80" s="48" t="inlineStr"/>
-      <c r="E80" s="48" t="inlineStr"/>
+      <c r="C80" s="48" t="n"/>
+      <c r="D80" s="48" t="n"/>
+      <c r="E80" s="48" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="48" t="inlineStr">
@@ -62162,9 +62996,9 @@
           <t>AI应用工程师（RAG/Agent）</t>
         </is>
       </c>
-      <c r="C81" s="48" t="inlineStr"/>
-      <c r="D81" s="48" t="inlineStr"/>
-      <c r="E81" s="48" t="inlineStr"/>
+      <c r="C81" s="48" t="n"/>
+      <c r="D81" s="48" t="n"/>
+      <c r="E81" s="48" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="48" t="inlineStr">
@@ -62177,9 +63011,9 @@
           <t>智能硬件产品经理</t>
         </is>
       </c>
-      <c r="C82" s="48" t="inlineStr"/>
-      <c r="D82" s="48" t="inlineStr"/>
-      <c r="E82" s="48" t="inlineStr"/>
+      <c r="C82" s="48" t="n"/>
+      <c r="D82" s="48" t="n"/>
+      <c r="E82" s="48" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="48" t="inlineStr">
@@ -62192,9 +63026,9 @@
           <t>智能硬件产品经理</t>
         </is>
       </c>
-      <c r="C83" s="48" t="inlineStr"/>
-      <c r="D83" s="48" t="inlineStr"/>
-      <c r="E83" s="48" t="inlineStr"/>
+      <c r="C83" s="48" t="n"/>
+      <c r="D83" s="48" t="n"/>
+      <c r="E83" s="48" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="48" t="inlineStr">
@@ -62207,9 +63041,9 @@
           <t>智能硬件产品经理</t>
         </is>
       </c>
-      <c r="C84" s="48" t="inlineStr"/>
-      <c r="D84" s="48" t="inlineStr"/>
-      <c r="E84" s="48" t="inlineStr"/>
+      <c r="C84" s="48" t="n"/>
+      <c r="D84" s="48" t="n"/>
+      <c r="E84" s="48" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="48" t="inlineStr">
@@ -62222,9 +63056,9 @@
           <t>智能硬件产品经理</t>
         </is>
       </c>
-      <c r="C85" s="48" t="inlineStr"/>
-      <c r="D85" s="48" t="inlineStr"/>
-      <c r="E85" s="48" t="inlineStr"/>
+      <c r="C85" s="48" t="n"/>
+      <c r="D85" s="48" t="n"/>
+      <c r="E85" s="48" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="48" t="inlineStr">
@@ -62237,9 +63071,9 @@
           <t>产品经理 IoT 智能硬件</t>
         </is>
       </c>
-      <c r="C86" s="48" t="inlineStr"/>
-      <c r="D86" s="48" t="inlineStr"/>
-      <c r="E86" s="48" t="inlineStr"/>
+      <c r="C86" s="48" t="n"/>
+      <c r="D86" s="48" t="n"/>
+      <c r="E86" s="48" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="48" t="inlineStr">
@@ -62252,9 +63086,9 @@
           <t>移动端产品经理 智能硬件方向</t>
         </is>
       </c>
-      <c r="C87" s="48" t="inlineStr"/>
-      <c r="D87" s="48" t="inlineStr"/>
-      <c r="E87" s="48" t="inlineStr"/>
+      <c r="C87" s="48" t="n"/>
+      <c r="D87" s="48" t="n"/>
+      <c r="E87" s="48" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="48" t="inlineStr">
@@ -62267,9 +63101,9 @@
           <t>Assistant Product Development Manager Innovation and Payment</t>
         </is>
       </c>
-      <c r="C88" s="48" t="inlineStr"/>
-      <c r="D88" s="48" t="inlineStr"/>
-      <c r="E88" s="48" t="inlineStr"/>
+      <c r="C88" s="48" t="n"/>
+      <c r="D88" s="48" t="n"/>
+      <c r="E88" s="48" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="48" t="inlineStr">
@@ -62282,9 +63116,9 @@
           <t>Assistant Manager Retail Banking Product</t>
         </is>
       </c>
-      <c r="C89" s="48" t="inlineStr"/>
-      <c r="D89" s="48" t="inlineStr"/>
-      <c r="E89" s="48" t="inlineStr"/>
+      <c r="C89" s="48" t="n"/>
+      <c r="D89" s="48" t="n"/>
+      <c r="E89" s="48" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="48" t="inlineStr">
@@ -62297,9 +63131,9 @@
           <t>Product Manager App and Card</t>
         </is>
       </c>
-      <c r="C90" s="48" t="inlineStr"/>
-      <c r="D90" s="48" t="inlineStr"/>
-      <c r="E90" s="48" t="inlineStr"/>
+      <c r="C90" s="48" t="n"/>
+      <c r="D90" s="48" t="n"/>
+      <c r="E90" s="48" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="48" t="inlineStr">
@@ -62312,9 +63146,9 @@
           <t>Senior Associate Product Manager Deposit Payment and Card</t>
         </is>
       </c>
-      <c r="C91" s="48" t="inlineStr"/>
-      <c r="D91" s="48" t="inlineStr"/>
-      <c r="E91" s="48" t="inlineStr"/>
+      <c r="C91" s="48" t="n"/>
+      <c r="D91" s="48" t="n"/>
+      <c r="E91" s="48" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="48" t="inlineStr">
@@ -62327,9 +63161,9 @@
           <t>(Assistant) Product Manager Cloud Product</t>
         </is>
       </c>
-      <c r="C92" s="48" t="inlineStr"/>
-      <c r="D92" s="48" t="inlineStr"/>
-      <c r="E92" s="48" t="inlineStr"/>
+      <c r="C92" s="48" t="n"/>
+      <c r="D92" s="48" t="n"/>
+      <c r="E92" s="48" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="48" t="inlineStr">
@@ -62342,9 +63176,9 @@
           <t>Senior Product Manager Digital Solution</t>
         </is>
       </c>
-      <c r="C93" s="48" t="inlineStr"/>
-      <c r="D93" s="48" t="inlineStr"/>
-      <c r="E93" s="48" t="inlineStr"/>
+      <c r="C93" s="48" t="n"/>
+      <c r="D93" s="48" t="n"/>
+      <c r="E93" s="48" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="48" t="inlineStr">
@@ -62357,9 +63191,9 @@
           <t>Senior Product Manager 或 Product Manager Mobile Payment</t>
         </is>
       </c>
-      <c r="C94" s="48" t="inlineStr"/>
-      <c r="D94" s="48" t="inlineStr"/>
-      <c r="E94" s="48" t="inlineStr"/>
+      <c r="C94" s="48" t="n"/>
+      <c r="D94" s="48" t="n"/>
+      <c r="E94" s="48" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="48" t="inlineStr">
@@ -62372,9 +63206,9 @@
           <t>产品经理</t>
         </is>
       </c>
-      <c r="C95" s="48" t="inlineStr"/>
-      <c r="D95" s="48" t="inlineStr"/>
-      <c r="E95" s="48" t="inlineStr"/>
+      <c r="C95" s="48" t="n"/>
+      <c r="D95" s="48" t="n"/>
+      <c r="E95" s="48" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="48" t="inlineStr">
@@ -62387,9 +63221,9 @@
           <t>大模型产品经理</t>
         </is>
       </c>
-      <c r="C96" s="48" t="inlineStr"/>
-      <c r="D96" s="48" t="inlineStr"/>
-      <c r="E96" s="48" t="inlineStr"/>
+      <c r="C96" s="48" t="n"/>
+      <c r="D96" s="48" t="n"/>
+      <c r="E96" s="48" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="48" t="inlineStr">
@@ -62402,9 +63236,9 @@
           <t>高级平台硬件产品经理（机器人）</t>
         </is>
       </c>
-      <c r="C97" s="48" t="inlineStr"/>
-      <c r="D97" s="48" t="inlineStr"/>
-      <c r="E97" s="48" t="inlineStr"/>
+      <c r="C97" s="48" t="n"/>
+      <c r="D97" s="48" t="n"/>
+      <c r="E97" s="48" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="48" t="inlineStr">
@@ -62417,9 +63251,9 @@
           <t>智能组网产品经理</t>
         </is>
       </c>
-      <c r="C98" s="48" t="inlineStr"/>
-      <c r="D98" s="48" t="inlineStr"/>
-      <c r="E98" s="48" t="inlineStr"/>
+      <c r="C98" s="48" t="n"/>
+      <c r="D98" s="48" t="n"/>
+      <c r="E98" s="48" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="48" t="inlineStr">
@@ -62432,9 +63266,9 @@
           <t>Product Manager - AI Rich Media Solution</t>
         </is>
       </c>
-      <c r="C99" s="48" t="inlineStr"/>
-      <c r="D99" s="48" t="inlineStr"/>
-      <c r="E99" s="48" t="inlineStr"/>
+      <c r="C99" s="48" t="n"/>
+      <c r="D99" s="48" t="n"/>
+      <c r="E99" s="48" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="48" t="inlineStr">
@@ -62447,9 +63281,9 @@
           <t>AI Product Manager / Owner (ERP project)</t>
         </is>
       </c>
-      <c r="C100" s="48" t="inlineStr"/>
-      <c r="D100" s="48" t="inlineStr"/>
-      <c r="E100" s="48" t="inlineStr"/>
+      <c r="C100" s="48" t="n"/>
+      <c r="D100" s="48" t="n"/>
+      <c r="E100" s="48" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="48" t="inlineStr">
@@ -62462,9 +63296,9 @@
           <t>AI Application Product Manager</t>
         </is>
       </c>
-      <c r="C101" s="48" t="inlineStr"/>
-      <c r="D101" s="48" t="inlineStr"/>
-      <c r="E101" s="48" t="inlineStr"/>
+      <c r="C101" s="48" t="n"/>
+      <c r="D101" s="48" t="n"/>
+      <c r="E101" s="48" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="48" t="inlineStr">
@@ -62477,9 +63311,9 @@
           <t>AI智能体产品设计师</t>
         </is>
       </c>
-      <c r="C102" s="48" t="inlineStr"/>
-      <c r="D102" s="48" t="inlineStr"/>
-      <c r="E102" s="48" t="inlineStr"/>
+      <c r="C102" s="48" t="n"/>
+      <c r="D102" s="48" t="n"/>
+      <c r="E102" s="48" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="48" t="inlineStr">
@@ -62492,9 +63326,9 @@
           <t>AI产品经理</t>
         </is>
       </c>
-      <c r="C103" s="48" t="inlineStr"/>
-      <c r="D103" s="48" t="inlineStr"/>
-      <c r="E103" s="48" t="inlineStr"/>
+      <c r="C103" s="48" t="n"/>
+      <c r="D103" s="48" t="n"/>
+      <c r="E103" s="48" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="48" t="inlineStr">
@@ -62507,9 +63341,9 @@
           <t>AI产品经理</t>
         </is>
       </c>
-      <c r="C104" s="48" t="inlineStr"/>
-      <c r="D104" s="48" t="inlineStr"/>
-      <c r="E104" s="48" t="inlineStr"/>
+      <c r="C104" s="48" t="n"/>
+      <c r="D104" s="48" t="n"/>
+      <c r="E104" s="48" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="48" t="inlineStr">
@@ -62522,9 +63356,9 @@
           <t>企业AI应用工程师</t>
         </is>
       </c>
-      <c r="C105" s="48" t="inlineStr"/>
-      <c r="D105" s="48" t="inlineStr"/>
-      <c r="E105" s="48" t="inlineStr"/>
+      <c r="C105" s="48" t="n"/>
+      <c r="D105" s="48" t="n"/>
+      <c r="E105" s="48" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="48" t="inlineStr">
@@ -62537,9 +63371,9 @@
           <t>AI硬件产品专员/工程师</t>
         </is>
       </c>
-      <c r="C106" s="48" t="inlineStr"/>
-      <c r="D106" s="48" t="inlineStr"/>
-      <c r="E106" s="48" t="inlineStr"/>
+      <c r="C106" s="48" t="n"/>
+      <c r="D106" s="48" t="n"/>
+      <c r="E106" s="48" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="48" t="inlineStr">
@@ -62552,9 +63386,9 @@
           <t>产品经理</t>
         </is>
       </c>
-      <c r="C107" s="48" t="inlineStr"/>
-      <c r="D107" s="48" t="inlineStr"/>
-      <c r="E107" s="48" t="inlineStr"/>
+      <c r="C107" s="48" t="n"/>
+      <c r="D107" s="48" t="n"/>
+      <c r="E107" s="48" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="48" t="inlineStr">
@@ -62567,9 +63401,9 @@
           <t>大模型产品经理</t>
         </is>
       </c>
-      <c r="C108" s="48" t="inlineStr"/>
-      <c r="D108" s="48" t="inlineStr"/>
-      <c r="E108" s="48" t="inlineStr"/>
+      <c r="C108" s="48" t="n"/>
+      <c r="D108" s="48" t="n"/>
+      <c r="E108" s="48" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="48" t="inlineStr">
@@ -62582,9 +63416,9 @@
           <t>高级平台硬件产品经理（机器人）</t>
         </is>
       </c>
-      <c r="C109" s="48" t="inlineStr"/>
-      <c r="D109" s="48" t="inlineStr"/>
-      <c r="E109" s="48" t="inlineStr"/>
+      <c r="C109" s="48" t="n"/>
+      <c r="D109" s="48" t="n"/>
+      <c r="E109" s="48" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="48" t="inlineStr">
@@ -62597,9 +63431,9 @@
           <t>智能组网产品经理</t>
         </is>
       </c>
-      <c r="C110" s="48" t="inlineStr"/>
-      <c r="D110" s="48" t="inlineStr"/>
-      <c r="E110" s="48" t="inlineStr"/>
+      <c r="C110" s="48" t="n"/>
+      <c r="D110" s="48" t="n"/>
+      <c r="E110" s="48" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="48" t="inlineStr">
@@ -62612,9 +63446,9 @@
           <t>Product Manager - AI Rich Media Solution</t>
         </is>
       </c>
-      <c r="C111" s="48" t="inlineStr"/>
-      <c r="D111" s="48" t="inlineStr"/>
-      <c r="E111" s="48" t="inlineStr"/>
+      <c r="C111" s="48" t="n"/>
+      <c r="D111" s="48" t="n"/>
+      <c r="E111" s="48" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="48" t="inlineStr">
@@ -62627,9 +63461,9 @@
           <t>AI Product Manager / Owner (ERP project)</t>
         </is>
       </c>
-      <c r="C112" s="48" t="inlineStr"/>
-      <c r="D112" s="48" t="inlineStr"/>
-      <c r="E112" s="48" t="inlineStr"/>
+      <c r="C112" s="48" t="n"/>
+      <c r="D112" s="48" t="n"/>
+      <c r="E112" s="48" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="48" t="inlineStr">
@@ -62642,9 +63476,9 @@
           <t>AI Application Product Manager</t>
         </is>
       </c>
-      <c r="C113" s="48" t="inlineStr"/>
-      <c r="D113" s="48" t="inlineStr"/>
-      <c r="E113" s="48" t="inlineStr"/>
+      <c r="C113" s="48" t="n"/>
+      <c r="D113" s="48" t="n"/>
+      <c r="E113" s="48" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="48" t="inlineStr">
@@ -62657,9 +63491,9 @@
           <t>AI智能体产品设计师</t>
         </is>
       </c>
-      <c r="C114" s="48" t="inlineStr"/>
-      <c r="D114" s="48" t="inlineStr"/>
-      <c r="E114" s="48" t="inlineStr"/>
+      <c r="C114" s="48" t="n"/>
+      <c r="D114" s="48" t="n"/>
+      <c r="E114" s="48" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="48" t="inlineStr">
@@ -62672,9 +63506,9 @@
           <t>AI产品经理</t>
         </is>
       </c>
-      <c r="C115" s="48" t="inlineStr"/>
-      <c r="D115" s="48" t="inlineStr"/>
-      <c r="E115" s="48" t="inlineStr"/>
+      <c r="C115" s="48" t="n"/>
+      <c r="D115" s="48" t="n"/>
+      <c r="E115" s="48" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="48" t="inlineStr">
@@ -62687,9 +63521,9 @@
           <t>AI产品经理</t>
         </is>
       </c>
-      <c r="C116" s="48" t="inlineStr"/>
-      <c r="D116" s="48" t="inlineStr"/>
-      <c r="E116" s="48" t="inlineStr"/>
+      <c r="C116" s="48" t="n"/>
+      <c r="D116" s="48" t="n"/>
+      <c r="E116" s="48" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="48" t="inlineStr">
@@ -62702,9 +63536,9 @@
           <t>企业AI应用工程师</t>
         </is>
       </c>
-      <c r="C117" s="48" t="inlineStr"/>
-      <c r="D117" s="48" t="inlineStr"/>
-      <c r="E117" s="48" t="inlineStr"/>
+      <c r="C117" s="48" t="n"/>
+      <c r="D117" s="48" t="n"/>
+      <c r="E117" s="48" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="48" t="inlineStr">
@@ -62717,9 +63551,9 @@
           <t>AI硬件产品专员/工程师</t>
         </is>
       </c>
-      <c r="C118" s="48" t="inlineStr"/>
-      <c r="D118" s="48" t="inlineStr"/>
-      <c r="E118" s="48" t="inlineStr"/>
+      <c r="C118" s="48" t="n"/>
+      <c r="D118" s="48" t="n"/>
+      <c r="E118" s="48" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="48" t="inlineStr">
@@ -62732,9 +63566,9 @@
           <t>产品经理</t>
         </is>
       </c>
-      <c r="C119" s="48" t="inlineStr"/>
-      <c r="D119" s="48" t="inlineStr"/>
-      <c r="E119" s="48" t="inlineStr"/>
+      <c r="C119" s="48" t="n"/>
+      <c r="D119" s="48" t="n"/>
+      <c r="E119" s="48" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="48" t="inlineStr">
@@ -62747,9 +63581,9 @@
           <t>大模型产品经理</t>
         </is>
       </c>
-      <c r="C120" s="48" t="inlineStr"/>
-      <c r="D120" s="48" t="inlineStr"/>
-      <c r="E120" s="48" t="inlineStr"/>
+      <c r="C120" s="48" t="n"/>
+      <c r="D120" s="48" t="n"/>
+      <c r="E120" s="48" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="48" t="inlineStr">
@@ -62762,9 +63596,9 @@
           <t>高级平台硬件产品经理（机器人）</t>
         </is>
       </c>
-      <c r="C121" s="48" t="inlineStr"/>
-      <c r="D121" s="48" t="inlineStr"/>
-      <c r="E121" s="48" t="inlineStr"/>
+      <c r="C121" s="48" t="n"/>
+      <c r="D121" s="48" t="n"/>
+      <c r="E121" s="48" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="48" t="inlineStr">
@@ -62777,9 +63611,9 @@
           <t>智能组网产品经理</t>
         </is>
       </c>
-      <c r="C122" s="48" t="inlineStr"/>
-      <c r="D122" s="48" t="inlineStr"/>
-      <c r="E122" s="48" t="inlineStr"/>
+      <c r="C122" s="48" t="n"/>
+      <c r="D122" s="48" t="n"/>
+      <c r="E122" s="48" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="48" t="inlineStr">
@@ -62792,9 +63626,9 @@
           <t>Product Manager - AI Rich Media Solution</t>
         </is>
       </c>
-      <c r="C123" s="48" t="inlineStr"/>
-      <c r="D123" s="48" t="inlineStr"/>
-      <c r="E123" s="48" t="inlineStr"/>
+      <c r="C123" s="48" t="n"/>
+      <c r="D123" s="48" t="n"/>
+      <c r="E123" s="48" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="48" t="inlineStr">
@@ -62807,9 +63641,9 @@
           <t>AI Product Manager / Owner (ERP project)</t>
         </is>
       </c>
-      <c r="C124" s="48" t="inlineStr"/>
-      <c r="D124" s="48" t="inlineStr"/>
-      <c r="E124" s="48" t="inlineStr"/>
+      <c r="C124" s="48" t="n"/>
+      <c r="D124" s="48" t="n"/>
+      <c r="E124" s="48" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="48" t="inlineStr">
@@ -62822,9 +63656,9 @@
           <t>AI Application Product Manager</t>
         </is>
       </c>
-      <c r="C125" s="48" t="inlineStr"/>
-      <c r="D125" s="48" t="inlineStr"/>
-      <c r="E125" s="48" t="inlineStr"/>
+      <c r="C125" s="48" t="n"/>
+      <c r="D125" s="48" t="n"/>
+      <c r="E125" s="48" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="48" t="inlineStr">
@@ -62837,9 +63671,9 @@
           <t>AI智能体产品设计师</t>
         </is>
       </c>
-      <c r="C126" s="48" t="inlineStr"/>
-      <c r="D126" s="48" t="inlineStr"/>
-      <c r="E126" s="48" t="inlineStr"/>
+      <c r="C126" s="48" t="n"/>
+      <c r="D126" s="48" t="n"/>
+      <c r="E126" s="48" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="48" t="inlineStr">
@@ -62852,9 +63686,9 @@
           <t>AI产品经理</t>
         </is>
       </c>
-      <c r="C127" s="48" t="inlineStr"/>
-      <c r="D127" s="48" t="inlineStr"/>
-      <c r="E127" s="48" t="inlineStr"/>
+      <c r="C127" s="48" t="n"/>
+      <c r="D127" s="48" t="n"/>
+      <c r="E127" s="48" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="48" t="inlineStr">
@@ -62867,9 +63701,9 @@
           <t>AI产品经理</t>
         </is>
       </c>
-      <c r="C128" s="48" t="inlineStr"/>
-      <c r="D128" s="48" t="inlineStr"/>
-      <c r="E128" s="48" t="inlineStr"/>
+      <c r="C128" s="48" t="n"/>
+      <c r="D128" s="48" t="n"/>
+      <c r="E128" s="48" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="48" t="inlineStr">
@@ -62882,9 +63716,9 @@
           <t>企业AI应用工程师</t>
         </is>
       </c>
-      <c r="C129" s="48" t="inlineStr"/>
-      <c r="D129" s="48" t="inlineStr"/>
-      <c r="E129" s="48" t="inlineStr"/>
+      <c r="C129" s="48" t="n"/>
+      <c r="D129" s="48" t="n"/>
+      <c r="E129" s="48" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="48" t="inlineStr">
@@ -62897,9 +63731,9 @@
           <t>AI硬件产品专员/工程师</t>
         </is>
       </c>
-      <c r="C130" s="48" t="inlineStr"/>
-      <c r="D130" s="48" t="inlineStr"/>
-      <c r="E130" s="48" t="inlineStr"/>
+      <c r="C130" s="48" t="n"/>
+      <c r="D130" s="48" t="n"/>
+      <c r="E130" s="48" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="48" t="inlineStr">
@@ -62912,9 +63746,9 @@
           <t>产品经理</t>
         </is>
       </c>
-      <c r="C131" s="48" t="inlineStr"/>
-      <c r="D131" s="48" t="inlineStr"/>
-      <c r="E131" s="48" t="inlineStr"/>
+      <c r="C131" s="48" t="n"/>
+      <c r="D131" s="48" t="n"/>
+      <c r="E131" s="48" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="48" t="inlineStr">
@@ -62927,9 +63761,9 @@
           <t>大模型产品经理</t>
         </is>
       </c>
-      <c r="C132" s="48" t="inlineStr"/>
-      <c r="D132" s="48" t="inlineStr"/>
-      <c r="E132" s="48" t="inlineStr"/>
+      <c r="C132" s="48" t="n"/>
+      <c r="D132" s="48" t="n"/>
+      <c r="E132" s="48" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="48" t="inlineStr">
@@ -62942,9 +63776,9 @@
           <t>工业AI产品经理</t>
         </is>
       </c>
-      <c r="C133" s="48" t="inlineStr"/>
-      <c r="D133" s="48" t="inlineStr"/>
-      <c r="E133" s="48" t="inlineStr"/>
+      <c r="C133" s="48" t="n"/>
+      <c r="D133" s="48" t="n"/>
+      <c r="E133" s="48" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="48" t="inlineStr">
@@ -62957,9 +63791,9 @@
           <t>高级平台硬件产品经理（机器人）</t>
         </is>
       </c>
-      <c r="C134" s="48" t="inlineStr"/>
-      <c r="D134" s="48" t="inlineStr"/>
-      <c r="E134" s="48" t="inlineStr"/>
+      <c r="C134" s="48" t="n"/>
+      <c r="D134" s="48" t="n"/>
+      <c r="E134" s="48" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="48" t="inlineStr">
@@ -62972,9 +63806,9 @@
           <t>智能组网产品经理</t>
         </is>
       </c>
-      <c r="C135" s="48" t="inlineStr"/>
-      <c r="D135" s="48" t="inlineStr"/>
-      <c r="E135" s="48" t="inlineStr"/>
+      <c r="C135" s="48" t="n"/>
+      <c r="D135" s="48" t="n"/>
+      <c r="E135" s="48" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="48" t="inlineStr">
@@ -62987,9 +63821,9 @@
           <t>Product Manager - AI Rich Media Solution</t>
         </is>
       </c>
-      <c r="C136" s="48" t="inlineStr"/>
-      <c r="D136" s="48" t="inlineStr"/>
-      <c r="E136" s="48" t="inlineStr"/>
+      <c r="C136" s="48" t="n"/>
+      <c r="D136" s="48" t="n"/>
+      <c r="E136" s="48" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="48" t="inlineStr">
@@ -63002,9 +63836,9 @@
           <t>AI Product Manager / Owner (ERP project)</t>
         </is>
       </c>
-      <c r="C137" s="48" t="inlineStr"/>
-      <c r="D137" s="48" t="inlineStr"/>
-      <c r="E137" s="48" t="inlineStr"/>
+      <c r="C137" s="48" t="n"/>
+      <c r="D137" s="48" t="n"/>
+      <c r="E137" s="48" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="48" t="inlineStr">
@@ -63017,9 +63851,9 @@
           <t>AI Application Product Manager</t>
         </is>
       </c>
-      <c r="C138" s="48" t="inlineStr"/>
-      <c r="D138" s="48" t="inlineStr"/>
-      <c r="E138" s="48" t="inlineStr"/>
+      <c r="C138" s="48" t="n"/>
+      <c r="D138" s="48" t="n"/>
+      <c r="E138" s="48" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="48" t="inlineStr">
@@ -63032,9 +63866,9 @@
           <t>AI智能体产品设计师</t>
         </is>
       </c>
-      <c r="C139" s="48" t="inlineStr"/>
-      <c r="D139" s="48" t="inlineStr"/>
-      <c r="E139" s="48" t="inlineStr"/>
+      <c r="C139" s="48" t="n"/>
+      <c r="D139" s="48" t="n"/>
+      <c r="E139" s="48" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="48" t="inlineStr">
@@ -63047,9 +63881,9 @@
           <t>AI产品经理</t>
         </is>
       </c>
-      <c r="C140" s="48" t="inlineStr"/>
-      <c r="D140" s="48" t="inlineStr"/>
-      <c r="E140" s="48" t="inlineStr"/>
+      <c r="C140" s="48" t="n"/>
+      <c r="D140" s="48" t="n"/>
+      <c r="E140" s="48" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="48" t="inlineStr">
@@ -63062,9 +63896,9 @@
           <t>AI产品经理</t>
         </is>
       </c>
-      <c r="C141" s="48" t="inlineStr"/>
-      <c r="D141" s="48" t="inlineStr"/>
-      <c r="E141" s="48" t="inlineStr"/>
+      <c r="C141" s="48" t="n"/>
+      <c r="D141" s="48" t="n"/>
+      <c r="E141" s="48" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="48" t="inlineStr">
@@ -63077,9 +63911,9 @@
           <t>企业AI应用工程师</t>
         </is>
       </c>
-      <c r="C142" s="48" t="inlineStr"/>
-      <c r="D142" s="48" t="inlineStr"/>
-      <c r="E142" s="48" t="inlineStr"/>
+      <c r="C142" s="48" t="n"/>
+      <c r="D142" s="48" t="n"/>
+      <c r="E142" s="48" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="48" t="inlineStr">
@@ -63092,9 +63926,9 @@
           <t>AI硬件产品专员/工程师</t>
         </is>
       </c>
-      <c r="C143" s="48" t="inlineStr"/>
-      <c r="D143" s="48" t="inlineStr"/>
-      <c r="E143" s="48" t="inlineStr"/>
+      <c r="C143" s="48" t="n"/>
+      <c r="D143" s="48" t="n"/>
+      <c r="E143" s="48" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="48" t="inlineStr">
@@ -63107,9 +63941,9 @@
           <t>产品经理</t>
         </is>
       </c>
-      <c r="C144" s="48" t="inlineStr"/>
-      <c r="D144" s="48" t="inlineStr"/>
-      <c r="E144" s="48" t="inlineStr"/>
+      <c r="C144" s="48" t="n"/>
+      <c r="D144" s="48" t="n"/>
+      <c r="E144" s="48" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="48" t="inlineStr">
@@ -63122,9 +63956,9 @@
           <t>大模型产品经理</t>
         </is>
       </c>
-      <c r="C145" s="48" t="inlineStr"/>
-      <c r="D145" s="48" t="inlineStr"/>
-      <c r="E145" s="48" t="inlineStr"/>
+      <c r="C145" s="48" t="n"/>
+      <c r="D145" s="48" t="n"/>
+      <c r="E145" s="48" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="48" t="inlineStr">
@@ -63137,9 +63971,9 @@
           <t>工业AI产品经理</t>
         </is>
       </c>
-      <c r="C146" s="48" t="inlineStr"/>
-      <c r="D146" s="48" t="inlineStr"/>
-      <c r="E146" s="48" t="inlineStr"/>
+      <c r="C146" s="48" t="n"/>
+      <c r="D146" s="48" t="n"/>
+      <c r="E146" s="48" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="48" t="inlineStr">
@@ -63152,9 +63986,9 @@
           <t>高级平台硬件产品经理（机器人）</t>
         </is>
       </c>
-      <c r="C147" s="48" t="inlineStr"/>
-      <c r="D147" s="48" t="inlineStr"/>
-      <c r="E147" s="48" t="inlineStr"/>
+      <c r="C147" s="48" t="n"/>
+      <c r="D147" s="48" t="n"/>
+      <c r="E147" s="48" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="48" t="inlineStr">
@@ -63167,9 +64001,9 @@
           <t>智能组网产品经理</t>
         </is>
       </c>
-      <c r="C148" s="48" t="inlineStr"/>
-      <c r="D148" s="48" t="inlineStr"/>
-      <c r="E148" s="48" t="inlineStr"/>
+      <c r="C148" s="48" t="n"/>
+      <c r="D148" s="48" t="n"/>
+      <c r="E148" s="48" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="48" t="inlineStr">
@@ -63182,9 +64016,9 @@
           <t>Product Manager - AI Rich Media Solution</t>
         </is>
       </c>
-      <c r="C149" s="48" t="inlineStr"/>
-      <c r="D149" s="48" t="inlineStr"/>
-      <c r="E149" s="48" t="inlineStr"/>
+      <c r="C149" s="48" t="n"/>
+      <c r="D149" s="48" t="n"/>
+      <c r="E149" s="48" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="48" t="inlineStr">
@@ -63197,9 +64031,9 @@
           <t>AI Product Manager / Owner (ERP project)</t>
         </is>
       </c>
-      <c r="C150" s="48" t="inlineStr"/>
-      <c r="D150" s="48" t="inlineStr"/>
-      <c r="E150" s="48" t="inlineStr"/>
+      <c r="C150" s="48" t="n"/>
+      <c r="D150" s="48" t="n"/>
+      <c r="E150" s="48" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="48" t="inlineStr">
@@ -63212,9 +64046,9 @@
           <t>AI Application Product Manager</t>
         </is>
       </c>
-      <c r="C151" s="48" t="inlineStr"/>
-      <c r="D151" s="48" t="inlineStr"/>
-      <c r="E151" s="48" t="inlineStr"/>
+      <c r="C151" s="48" t="n"/>
+      <c r="D151" s="48" t="n"/>
+      <c r="E151" s="48" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="48" t="inlineStr">
@@ -63227,9 +64061,9 @@
           <t>AI智能体产品设计师</t>
         </is>
       </c>
-      <c r="C152" s="48" t="inlineStr"/>
-      <c r="D152" s="48" t="inlineStr"/>
-      <c r="E152" s="48" t="inlineStr"/>
+      <c r="C152" s="48" t="n"/>
+      <c r="D152" s="48" t="n"/>
+      <c r="E152" s="48" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="48" t="inlineStr">
@@ -63242,9 +64076,9 @@
           <t>AI产品经理</t>
         </is>
       </c>
-      <c r="C153" s="48" t="inlineStr"/>
-      <c r="D153" s="48" t="inlineStr"/>
-      <c r="E153" s="48" t="inlineStr"/>
+      <c r="C153" s="48" t="n"/>
+      <c r="D153" s="48" t="n"/>
+      <c r="E153" s="48" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="48" t="inlineStr">
@@ -63257,9 +64091,9 @@
           <t>AI产品经理</t>
         </is>
       </c>
-      <c r="C154" s="48" t="inlineStr"/>
-      <c r="D154" s="48" t="inlineStr"/>
-      <c r="E154" s="48" t="inlineStr"/>
+      <c r="C154" s="48" t="n"/>
+      <c r="D154" s="48" t="n"/>
+      <c r="E154" s="48" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="48" t="inlineStr">
@@ -63272,9 +64106,9 @@
           <t>企业AI应用工程师</t>
         </is>
       </c>
-      <c r="C155" s="48" t="inlineStr"/>
-      <c r="D155" s="48" t="inlineStr"/>
-      <c r="E155" s="48" t="inlineStr"/>
+      <c r="C155" s="48" t="n"/>
+      <c r="D155" s="48" t="n"/>
+      <c r="E155" s="48" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="48" t="inlineStr">
@@ -63287,9 +64121,9 @@
           <t>AI硬件产品专员/工程师</t>
         </is>
       </c>
-      <c r="C156" s="48" t="inlineStr"/>
-      <c r="D156" s="48" t="inlineStr"/>
-      <c r="E156" s="48" t="inlineStr"/>
+      <c r="C156" s="48" t="n"/>
+      <c r="D156" s="48" t="n"/>
+      <c r="E156" s="48" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="48" t="inlineStr">
@@ -63302,9 +64136,9 @@
           <t>产品经理</t>
         </is>
       </c>
-      <c r="C157" s="48" t="inlineStr"/>
-      <c r="D157" s="48" t="inlineStr"/>
-      <c r="E157" s="48" t="inlineStr"/>
+      <c r="C157" s="48" t="n"/>
+      <c r="D157" s="48" t="n"/>
+      <c r="E157" s="48" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="48" t="inlineStr">
@@ -63317,9 +64151,9 @@
           <t>大模型产品经理</t>
         </is>
       </c>
-      <c r="C158" s="48" t="inlineStr"/>
-      <c r="D158" s="48" t="inlineStr"/>
-      <c r="E158" s="48" t="inlineStr"/>
+      <c r="C158" s="48" t="n"/>
+      <c r="D158" s="48" t="n"/>
+      <c r="E158" s="48" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="48" t="inlineStr">
@@ -63332,9 +64166,9 @@
           <t>工业AI产品经理</t>
         </is>
       </c>
-      <c r="C159" s="48" t="inlineStr"/>
-      <c r="D159" s="48" t="inlineStr"/>
-      <c r="E159" s="48" t="inlineStr"/>
+      <c r="C159" s="48" t="n"/>
+      <c r="D159" s="48" t="n"/>
+      <c r="E159" s="48" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="48" t="inlineStr">
@@ -63347,9 +64181,9 @@
           <t>高级平台硬件产品经理（机器人）</t>
         </is>
       </c>
-      <c r="C160" s="48" t="inlineStr"/>
-      <c r="D160" s="48" t="inlineStr"/>
-      <c r="E160" s="48" t="inlineStr"/>
+      <c r="C160" s="48" t="n"/>
+      <c r="D160" s="48" t="n"/>
+      <c r="E160" s="48" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="48" t="inlineStr">
@@ -63362,9 +64196,9 @@
           <t>智能组网产品经理</t>
         </is>
       </c>
-      <c r="C161" s="48" t="inlineStr"/>
-      <c r="D161" s="48" t="inlineStr"/>
-      <c r="E161" s="48" t="inlineStr"/>
+      <c r="C161" s="48" t="n"/>
+      <c r="D161" s="48" t="n"/>
+      <c r="E161" s="48" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="48" t="inlineStr">
@@ -63377,9 +64211,9 @@
           <t>Product Manager - AI Rich Media Solution</t>
         </is>
       </c>
-      <c r="C162" s="48" t="inlineStr"/>
-      <c r="D162" s="48" t="inlineStr"/>
-      <c r="E162" s="48" t="inlineStr"/>
+      <c r="C162" s="48" t="n"/>
+      <c r="D162" s="48" t="n"/>
+      <c r="E162" s="48" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="48" t="inlineStr">
@@ -63392,9 +64226,9 @@
           <t>AI Product Manager / Owner (ERP project)</t>
         </is>
       </c>
-      <c r="C163" s="48" t="inlineStr"/>
-      <c r="D163" s="48" t="inlineStr"/>
-      <c r="E163" s="48" t="inlineStr"/>
+      <c r="C163" s="48" t="n"/>
+      <c r="D163" s="48" t="n"/>
+      <c r="E163" s="48" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="48" t="inlineStr">
@@ -63407,9 +64241,9 @@
           <t>AI Application Product Manager</t>
         </is>
       </c>
-      <c r="C164" s="48" t="inlineStr"/>
-      <c r="D164" s="48" t="inlineStr"/>
-      <c r="E164" s="48" t="inlineStr"/>
+      <c r="C164" s="48" t="n"/>
+      <c r="D164" s="48" t="n"/>
+      <c r="E164" s="48" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="48" t="inlineStr">
@@ -63422,9 +64256,9 @@
           <t>AI智能体产品设计师</t>
         </is>
       </c>
-      <c r="C165" s="48" t="inlineStr"/>
-      <c r="D165" s="48" t="inlineStr"/>
-      <c r="E165" s="48" t="inlineStr"/>
+      <c r="C165" s="48" t="n"/>
+      <c r="D165" s="48" t="n"/>
+      <c r="E165" s="48" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="48" t="inlineStr">
@@ -63437,9 +64271,9 @@
           <t>AI产品经理</t>
         </is>
       </c>
-      <c r="C166" s="48" t="inlineStr"/>
-      <c r="D166" s="48" t="inlineStr"/>
-      <c r="E166" s="48" t="inlineStr"/>
+      <c r="C166" s="48" t="n"/>
+      <c r="D166" s="48" t="n"/>
+      <c r="E166" s="48" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="48" t="inlineStr">
@@ -63452,9 +64286,9 @@
           <t>AI产品经理</t>
         </is>
       </c>
-      <c r="C167" s="48" t="inlineStr"/>
-      <c r="D167" s="48" t="inlineStr"/>
-      <c r="E167" s="48" t="inlineStr"/>
+      <c r="C167" s="48" t="n"/>
+      <c r="D167" s="48" t="n"/>
+      <c r="E167" s="48" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="48" t="inlineStr">
@@ -63467,9 +64301,9 @@
           <t>企业AI应用工程师</t>
         </is>
       </c>
-      <c r="C168" s="48" t="inlineStr"/>
-      <c r="D168" s="48" t="inlineStr"/>
-      <c r="E168" s="48" t="inlineStr"/>
+      <c r="C168" s="48" t="n"/>
+      <c r="D168" s="48" t="n"/>
+      <c r="E168" s="48" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="48" t="inlineStr">
@@ -63482,9 +64316,9 @@
           <t>AI硬件产品专员/工程师</t>
         </is>
       </c>
-      <c r="C169" s="48" t="inlineStr"/>
-      <c r="D169" s="48" t="inlineStr"/>
-      <c r="E169" s="48" t="inlineStr"/>
+      <c r="C169" s="48" t="n"/>
+      <c r="D169" s="48" t="n"/>
+      <c r="E169" s="48" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="48" t="inlineStr">
@@ -63497,9 +64331,9 @@
           <t>产品经理</t>
         </is>
       </c>
-      <c r="C170" s="48" t="inlineStr"/>
-      <c r="D170" s="48" t="inlineStr"/>
-      <c r="E170" s="48" t="inlineStr"/>
+      <c r="C170" s="48" t="n"/>
+      <c r="D170" s="48" t="n"/>
+      <c r="E170" s="48" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="48" t="inlineStr">
@@ -63512,9 +64346,9 @@
           <t>大模型产品经理</t>
         </is>
       </c>
-      <c r="C171" s="48" t="inlineStr"/>
-      <c r="D171" s="48" t="inlineStr"/>
-      <c r="E171" s="48" t="inlineStr"/>
+      <c r="C171" s="48" t="n"/>
+      <c r="D171" s="48" t="n"/>
+      <c r="E171" s="48" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="48" t="inlineStr">
@@ -63527,9 +64361,9 @@
           <t>工业AI产品经理</t>
         </is>
       </c>
-      <c r="C172" s="48" t="inlineStr"/>
-      <c r="D172" s="48" t="inlineStr"/>
-      <c r="E172" s="48" t="inlineStr"/>
+      <c r="C172" s="48" t="n"/>
+      <c r="D172" s="48" t="n"/>
+      <c r="E172" s="48" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="48" t="inlineStr">
@@ -63569,9 +64403,9 @@
           <t>AI+机器人产品经理</t>
         </is>
       </c>
-      <c r="C174" s="48" t="inlineStr"/>
-      <c r="D174" s="48" t="inlineStr"/>
-      <c r="E174" s="48" t="inlineStr"/>
+      <c r="C174" s="48" t="n"/>
+      <c r="D174" s="48" t="n"/>
+      <c r="E174" s="48" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="48" t="inlineStr">
@@ -63584,9 +64418,9 @@
           <t>高级平台硬件产品经理（机器人）</t>
         </is>
       </c>
-      <c r="C175" s="48" t="inlineStr"/>
-      <c r="D175" s="48" t="inlineStr"/>
-      <c r="E175" s="48" t="inlineStr"/>
+      <c r="C175" s="48" t="n"/>
+      <c r="D175" s="48" t="n"/>
+      <c r="E175" s="48" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="48" t="inlineStr">
@@ -63599,9 +64433,9 @@
           <t>智能组网产品经理</t>
         </is>
       </c>
-      <c r="C176" s="48" t="inlineStr"/>
-      <c r="D176" s="48" t="inlineStr"/>
-      <c r="E176" s="48" t="inlineStr"/>
+      <c r="C176" s="48" t="n"/>
+      <c r="D176" s="48" t="n"/>
+      <c r="E176" s="48" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="48" t="inlineStr">
@@ -63614,9 +64448,9 @@
           <t>Product Manager - AI Rich Media Solution</t>
         </is>
       </c>
-      <c r="C177" s="48" t="inlineStr"/>
-      <c r="D177" s="48" t="inlineStr"/>
-      <c r="E177" s="48" t="inlineStr"/>
+      <c r="C177" s="48" t="n"/>
+      <c r="D177" s="48" t="n"/>
+      <c r="E177" s="48" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="48" t="inlineStr">
@@ -63629,9 +64463,9 @@
           <t>AI Product Manager / Owner (ERP project)</t>
         </is>
       </c>
-      <c r="C178" s="48" t="inlineStr"/>
-      <c r="D178" s="48" t="inlineStr"/>
-      <c r="E178" s="48" t="inlineStr"/>
+      <c r="C178" s="48" t="n"/>
+      <c r="D178" s="48" t="n"/>
+      <c r="E178" s="48" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="48" t="inlineStr">
@@ -63644,9 +64478,489 @@
           <t>AI Application Product Manager</t>
         </is>
       </c>
-      <c r="C179" s="48" t="inlineStr"/>
-      <c r="D179" s="48" t="inlineStr"/>
-      <c r="E179" s="48" t="inlineStr"/>
+      <c r="C179" s="48" t="n"/>
+      <c r="D179" s="48" t="n"/>
+      <c r="E179" s="48" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="48" t="inlineStr">
+        <is>
+          <t>新明珠集团</t>
+        </is>
+      </c>
+      <c r="B180" s="48" t="inlineStr">
+        <is>
+          <t>AI智能体产品设计师</t>
+        </is>
+      </c>
+      <c r="C180" s="48" t="n"/>
+      <c r="D180" s="48" t="n"/>
+      <c r="E180" s="48" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="48" t="inlineStr">
+        <is>
+          <t>玖龙纸业（控股）有限公司</t>
+        </is>
+      </c>
+      <c r="B181" s="48" t="inlineStr">
+        <is>
+          <t>AI产品经理</t>
+        </is>
+      </c>
+      <c r="C181" s="48" t="n"/>
+      <c r="D181" s="48" t="n"/>
+      <c r="E181" s="48" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="48" t="inlineStr">
+        <is>
+          <t>Seeed 矽递科技</t>
+        </is>
+      </c>
+      <c r="B182" s="48" t="inlineStr">
+        <is>
+          <t>AI产品经理</t>
+        </is>
+      </c>
+      <c r="C182" s="48" t="n"/>
+      <c r="D182" s="48" t="n"/>
+      <c r="E182" s="48" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="48" t="inlineStr">
+        <is>
+          <t>深圳欣盛商科技有限公司</t>
+        </is>
+      </c>
+      <c r="B183" s="48" t="inlineStr">
+        <is>
+          <t>企业AI应用工程师</t>
+        </is>
+      </c>
+      <c r="C183" s="48" t="n"/>
+      <c r="D183" s="48" t="n"/>
+      <c r="E183" s="48" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="48" t="inlineStr">
+        <is>
+          <t>美团</t>
+        </is>
+      </c>
+      <c r="B184" s="48" t="inlineStr">
+        <is>
+          <t>AI硬件产品专员/工程师</t>
+        </is>
+      </c>
+      <c r="C184" s="48" t="n"/>
+      <c r="D184" s="48" t="n"/>
+      <c r="E184" s="48" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="48" t="inlineStr">
+        <is>
+          <t>深圳启奥人工智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="B185" s="48" t="inlineStr">
+        <is>
+          <t>产品经理</t>
+        </is>
+      </c>
+      <c r="C185" s="48" t="n"/>
+      <c r="D185" s="48" t="n"/>
+      <c r="E185" s="48" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="48" t="inlineStr">
+        <is>
+          <t>深圳费曼智核机器人科技有限公司</t>
+        </is>
+      </c>
+      <c r="B186" s="48" t="inlineStr">
+        <is>
+          <t>大模型产品经理</t>
+        </is>
+      </c>
+      <c r="C186" s="48" t="n"/>
+      <c r="D186" s="48" t="n"/>
+      <c r="E186" s="48" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="48" t="inlineStr">
+        <is>
+          <t>鱼泡直聘线索/深圳宝安未核验雇主</t>
+        </is>
+      </c>
+      <c r="B187" s="48" t="inlineStr">
+        <is>
+          <t>工业AI产品经理</t>
+        </is>
+      </c>
+      <c r="C187" s="48" t="n"/>
+      <c r="D187" s="48" t="n"/>
+      <c r="E187" s="48" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="48" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="B188" s="48" t="inlineStr">
+        <is>
+          <t>Technical Product Manager, AI Platform</t>
+        </is>
+      </c>
+      <c r="C188" s="48" t="n"/>
+      <c r="D188" s="48" t="n"/>
+      <c r="E188" s="48" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="48" t="inlineStr">
+        <is>
+          <t>深圳中博纳网络科技有限公司（鱼泡直聘线索）</t>
+        </is>
+      </c>
+      <c r="B189" s="48" t="inlineStr">
+        <is>
+          <t>AI+机器人产品经理</t>
+        </is>
+      </c>
+      <c r="C189" s="48" t="n"/>
+      <c r="D189" s="48" t="n"/>
+      <c r="E189" s="48" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="48" t="inlineStr">
+        <is>
+          <t>科大讯飞硬件中心</t>
+        </is>
+      </c>
+      <c r="B190" s="48" t="inlineStr">
+        <is>
+          <t>高级平台硬件产品经理（机器人）</t>
+        </is>
+      </c>
+      <c r="C190" s="48" t="n"/>
+      <c r="D190" s="48" t="n"/>
+      <c r="E190" s="48" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="48" t="inlineStr">
+        <is>
+          <t>中电信数智科技(深圳)有限公司</t>
+        </is>
+      </c>
+      <c r="B191" s="48" t="inlineStr">
+        <is>
+          <t>智能组网产品经理</t>
+        </is>
+      </c>
+      <c r="C191" s="48" t="n"/>
+      <c r="D191" s="48" t="n"/>
+      <c r="E191" s="48" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="48" t="inlineStr">
+        <is>
+          <t>New Media Group Publishing Limited</t>
+        </is>
+      </c>
+      <c r="B192" s="48" t="inlineStr">
+        <is>
+          <t>Product Manager - AI Rich Media Solution</t>
+        </is>
+      </c>
+      <c r="C192" s="48" t="n"/>
+      <c r="D192" s="48" t="n"/>
+      <c r="E192" s="48" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="48" t="inlineStr">
+        <is>
+          <t>Galaxy Telecom (Hong Kong) Limited</t>
+        </is>
+      </c>
+      <c r="B193" s="48" t="inlineStr">
+        <is>
+          <t>AI Product Manager / Owner (ERP project)</t>
+        </is>
+      </c>
+      <c r="C193" s="48" t="n"/>
+      <c r="D193" s="48" t="n"/>
+      <c r="E193" s="48" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="48" t="inlineStr">
+        <is>
+          <t>HK01 Company Limited</t>
+        </is>
+      </c>
+      <c r="B194" s="48" t="inlineStr">
+        <is>
+          <t>AI Application Product Manager</t>
+        </is>
+      </c>
+      <c r="C194" s="48" t="n"/>
+      <c r="D194" s="48" t="n"/>
+      <c r="E194" s="48" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="48" t="inlineStr">
+        <is>
+          <t>新明珠集团</t>
+        </is>
+      </c>
+      <c r="B195" s="48" t="inlineStr">
+        <is>
+          <t>AI智能体产品设计师</t>
+        </is>
+      </c>
+      <c r="C195" s="48" t="n"/>
+      <c r="D195" s="48" t="n"/>
+      <c r="E195" s="48" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="48" t="inlineStr">
+        <is>
+          <t>玖龙纸业（控股）有限公司</t>
+        </is>
+      </c>
+      <c r="B196" s="48" t="inlineStr">
+        <is>
+          <t>AI产品经理</t>
+        </is>
+      </c>
+      <c r="C196" s="48" t="n"/>
+      <c r="D196" s="48" t="n"/>
+      <c r="E196" s="48" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="48" t="inlineStr">
+        <is>
+          <t>Seeed 矽递科技</t>
+        </is>
+      </c>
+      <c r="B197" s="48" t="inlineStr">
+        <is>
+          <t>AI产品经理</t>
+        </is>
+      </c>
+      <c r="C197" s="48" t="n"/>
+      <c r="D197" s="48" t="n"/>
+      <c r="E197" s="48" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="48" t="inlineStr">
+        <is>
+          <t>深圳欣盛商科技有限公司</t>
+        </is>
+      </c>
+      <c r="B198" s="48" t="inlineStr">
+        <is>
+          <t>企业AI应用工程师</t>
+        </is>
+      </c>
+      <c r="C198" s="48" t="n"/>
+      <c r="D198" s="48" t="n"/>
+      <c r="E198" s="48" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="48" t="inlineStr">
+        <is>
+          <t>美团</t>
+        </is>
+      </c>
+      <c r="B199" s="48" t="inlineStr">
+        <is>
+          <t>AI硬件产品专员/工程师</t>
+        </is>
+      </c>
+      <c r="C199" s="48" t="n"/>
+      <c r="D199" s="48" t="n"/>
+      <c r="E199" s="48" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="48" t="inlineStr">
+        <is>
+          <t>深圳启奥人工智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="B200" s="48" t="inlineStr">
+        <is>
+          <t>产品经理</t>
+        </is>
+      </c>
+      <c r="C200" s="48" t="n"/>
+      <c r="D200" s="48" t="n"/>
+      <c r="E200" s="48" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="48" t="inlineStr">
+        <is>
+          <t>深圳费曼智核机器人科技有限公司</t>
+        </is>
+      </c>
+      <c r="B201" s="48" t="inlineStr">
+        <is>
+          <t>大模型产品经理</t>
+        </is>
+      </c>
+      <c r="C201" s="48" t="n"/>
+      <c r="D201" s="48" t="n"/>
+      <c r="E201" s="48" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="48" t="inlineStr">
+        <is>
+          <t>鱼泡直聘线索/深圳宝安未核验雇主</t>
+        </is>
+      </c>
+      <c r="B202" s="48" t="inlineStr">
+        <is>
+          <t>工业AI产品经理</t>
+        </is>
+      </c>
+      <c r="C202" s="48" t="n"/>
+      <c r="D202" s="48" t="n"/>
+      <c r="E202" s="48" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="48" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B203" s="48" t="inlineStr">
+        <is>
+          <t>Subject Matter Expert - Automation &amp; AI/ML</t>
+        </is>
+      </c>
+      <c r="C203" s="48" t="n"/>
+      <c r="D203" s="48" t="n"/>
+      <c r="E203" s="48" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="48" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B204" s="48" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="C204" s="48" t="n"/>
+      <c r="D204" s="48" t="n"/>
+      <c r="E204" s="48" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="48" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="B205" s="48" t="inlineStr">
+        <is>
+          <t>Technical Product Manager, AI Platform</t>
+        </is>
+      </c>
+      <c r="C205" s="48" t="n"/>
+      <c r="D205" s="48" t="n"/>
+      <c r="E205" s="48" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="48" t="inlineStr">
+        <is>
+          <t>深圳中博纳网络科技有限公司（鱼泡直聘线索）</t>
+        </is>
+      </c>
+      <c r="B206" s="48" t="inlineStr">
+        <is>
+          <t>AI+机器人产品经理</t>
+        </is>
+      </c>
+      <c r="C206" s="48" t="n"/>
+      <c r="D206" s="48" t="n"/>
+      <c r="E206" s="48" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="48" t="inlineStr">
+        <is>
+          <t>科大讯飞硬件中心</t>
+        </is>
+      </c>
+      <c r="B207" s="48" t="inlineStr">
+        <is>
+          <t>高级平台硬件产品经理（机器人）</t>
+        </is>
+      </c>
+      <c r="C207" s="48" t="n"/>
+      <c r="D207" s="48" t="n"/>
+      <c r="E207" s="48" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="48" t="inlineStr">
+        <is>
+          <t>中电信数智科技(深圳)有限公司</t>
+        </is>
+      </c>
+      <c r="B208" s="48" t="inlineStr">
+        <is>
+          <t>智能组网产品经理</t>
+        </is>
+      </c>
+      <c r="C208" s="48" t="n"/>
+      <c r="D208" s="48" t="n"/>
+      <c r="E208" s="48" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="48" t="inlineStr">
+        <is>
+          <t>New Media Group Publishing Limited</t>
+        </is>
+      </c>
+      <c r="B209" s="48" t="inlineStr">
+        <is>
+          <t>Product Manager - AI Rich Media Solution</t>
+        </is>
+      </c>
+      <c r="C209" s="48" t="n"/>
+      <c r="D209" s="48" t="n"/>
+      <c r="E209" s="48" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="48" t="inlineStr">
+        <is>
+          <t>Galaxy Telecom (Hong Kong) Limited</t>
+        </is>
+      </c>
+      <c r="B210" s="48" t="inlineStr">
+        <is>
+          <t>AI Product Manager / Owner (ERP project)</t>
+        </is>
+      </c>
+      <c r="C210" s="48" t="n"/>
+      <c r="D210" s="48" t="n"/>
+      <c r="E210" s="48" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="48" t="inlineStr">
+        <is>
+          <t>HK01 Company Limited</t>
+        </is>
+      </c>
+      <c r="B211" s="48" t="inlineStr">
+        <is>
+          <t>AI Application Product Manager</t>
+        </is>
+      </c>
+      <c r="C211" s="48" t="n"/>
+      <c r="D211" s="48" t="n"/>
+      <c r="E211" s="48" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E16"/>
@@ -63696,7 +65010,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C:\Users\Yang\Documents\New project\daily_refresh_out\20260617\run_20260617_090826\jobroot\maps\prd_job_map_interactive.html</t>
+          <t>C:\Users\Yang\Desktop\job\maps\prd_job_map_interactive.html</t>
         </is>
       </c>
     </row>
@@ -65146,12 +66460,12 @@
           <t>????????????????????????</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="G20" s="62" t="inlineStr">
         <is>
           <t>https://nwd4iy9rd2s.jobs.feishu.cn/campusofSpiritAI/m/</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="H20" s="62" t="inlineStr">
         <is>
           <t>https://career.cuhk.edu.cn/en/job/view/id/468454</t>
         </is>
@@ -65166,7 +66480,7 @@
           <t>CUHK(SZ)???/????????</t>
         </is>
       </c>
-      <c r="K20" s="17" t="inlineStr">
+      <c r="K20" s="62" t="inlineStr">
         <is>
           <t>https://career.cuhk.edu.cn/en/job/view/id/468454</t>
         </is>
@@ -65223,7 +66537,7 @@
           <t>???</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="H21" s="62" t="inlineStr">
         <is>
           <t>https://m.liepin.com/job/1980980707.shtml</t>
         </is>
@@ -65238,7 +66552,7 @@
           <t>??????/?????????</t>
         </is>
       </c>
-      <c r="K21" s="17" t="inlineStr">
+      <c r="K21" s="62" t="inlineStr">
         <is>
           <t>https://m.liepin.com/job/1980980707.shtml</t>
         </is>

--- a/latest/job.xlsx
+++ b/latest/job.xlsx
@@ -2917,7 +2917,7 @@
       </c>
       <c r="V8" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="W8" s="48" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="V11" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W11" s="48" t="inlineStr">
@@ -3482,17 +3482,17 @@
       </c>
       <c r="AF11" s="2" t="inlineStr">
         <is>
-          <t>A档，100分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1主攻。城市/薪资为香港、HK$22,000-28,000/月，薪资匹配为部分达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港本地Agentic AI平台公司，主打企业客服与销售流程自动化；JD与可信度为中高、中高，入池岗位。关键风险：英文/粤语/IANG。</t>
+          <t>A档，100分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1主攻。城市/薪资为香港、HK$22,000-28,000/月，薪资匹配为部分达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港本地Agentic AI平台公司，主打企业客服与销售流程自动化；JD与可信度为中高、中高，入池岗位。关键风险：英文/粤语/IANG；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AG11" s="2" t="inlineStr">
         <is>
-          <t>重点准备后投</t>
+          <t>先核验再投</t>
         </is>
       </c>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>英文/粤语/IANG</t>
+          <t>英文/粤语/IANG；招聘状态不稳</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="V19" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="W19" s="48" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="V20" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="W20" s="48" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="V22" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="W22" s="48" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="V12" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W12" s="47" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="V14" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W14" s="47" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="V17" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W17" s="48" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="V18" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W18" s="48" t="inlineStr">
@@ -8599,21 +8599,21 @@
         </is>
       </c>
       <c r="AE18" s="2" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AF18" s="2" t="inlineStr">
         <is>
-          <t>A档，87分；字段显示主线为备线C-AI解决方案/数字化产品，匹配度中高，原申请优先级P3练手/备选实习。城市/薪资为深圳、未写，薪资匹配为实习可接受，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：腾讯云CSIG，中国头部云与产业互联网平台，做云、AI、安全和行业数字化；JD与可信度为精确JD、高，入池岗位。关键风险：出差/驻厂；招聘状态不稳。</t>
+          <t>A档，98分；字段显示主线为备线C-AI解决方案/数字化产品，匹配度中高，原申请优先级P3练手/备选实习。城市/薪资为深圳、未写，薪资匹配为实习可接受，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：腾讯云CSIG，中国头部云与产业互联网平台，做云、AI、安全和行业数字化；JD与可信度为精确JD、高，入池岗位。关键风险：出差/驻厂。</t>
         </is>
       </c>
       <c r="AG18" s="2" t="inlineStr">
         <is>
-          <t>先核验再投</t>
+          <t>定制简历后优先投</t>
         </is>
       </c>
       <c r="AH18" s="2" t="inlineStr">
         <is>
-          <t>出差/驻厂；招聘状态不稳</t>
+          <t>出差/驻厂</t>
         </is>
       </c>
       <c r="AI18" s="2" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="V26" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="W26" s="48" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="V29" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W29" s="47" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="AF29" s="2" t="inlineStr">
         <is>
-          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度高，原申请优先级P1主线实习。城市/薪资为深圳、400-500/天待确认，薪资匹配为实习可接受，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：深圳创客硬件和桌面激光加工设备出海品牌，软硬件结合和创作者生态强；JD与可信度为入口页/搜索页、中高，入池岗位。关键风险：薪资待确认；JD不精确；出差/驻厂；招聘状态不稳。</t>
+          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度高，原申请优先级P1主线实习。城市/薪资为深圳、400-500/天待确认，薪资匹配为实习可接受，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：深圳创客硬件和桌面激光加工设备出海品牌，软硬件结合和创作者生态强；JD与可信度为入口页/搜索页、中高，入池岗位。关键风险：薪资待确认；JD不精确；出差/驻厂。</t>
         </is>
       </c>
       <c r="AG29" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="AH29" s="2" t="inlineStr">
         <is>
-          <t>薪资待确认；JD不精确；出差/驻厂；招聘状态不稳</t>
+          <t>薪资待确认；JD不精确；出差/驻厂</t>
         </is>
       </c>
       <c r="AI29" s="2" t="inlineStr">
@@ -11152,7 +11152,7 @@
       </c>
       <c r="V33" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W33" s="48" t="inlineStr">
@@ -11194,11 +11194,11 @@
         </is>
       </c>
       <c r="AE33" s="2" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AF33" s="2" t="inlineStr">
         <is>
-          <t>B档，69分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度中高，原申请优先级P2AI应用实习。城市/薪资为香港/深圳、未公开，薪资匹配为实习可接受，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：移动设备管理、远程控制和跨设备协同工具公司，香港/深圳协同；JD与可信度为入口页/搜索页、中高，入池岗位。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
+          <t>B档，73分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度中高，原申请优先级P2AI应用实习。城市/薪资为香港/深圳、未公开，薪资匹配为实习可接受，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：移动设备管理、远程控制和跨设备协同工具公司，香港/深圳协同；JD与可信度为入口页/搜索页、中高，入池岗位。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂。</t>
         </is>
       </c>
       <c r="AG33" s="2" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="AH33" s="2" t="inlineStr">
         <is>
-          <t>薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
+          <t>薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂</t>
         </is>
       </c>
       <c r="AI33" s="2" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="V36" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="W36" s="47" t="inlineStr">
@@ -13750,7 +13750,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="AA48" s="17" t="inlineStr">
+      <c r="AA48" s="62" t="inlineStr">
         <is>
           <t>https://jobs.apple.com/en-us/details/200494847-3435/engineering-project-manager-intern-shanghai-shenzhen?team=HRDWR</t>
         </is>
@@ -13760,10 +13760,10 @@
       </c>
       <c r="AC48" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 Apple miss correction: official Jobs link grade fixed; promoted from expanded to internship.</t>
-        </is>
-      </c>
-      <c r="AD48" s="60" t="inlineStr">
+          <t>2026-06-17 Apple miss correction: official Jobs link grade fixed; promoted from expanded to internship.；首次入库日期=2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD48" s="59" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -13773,12 +13773,12 @@
       </c>
       <c r="AF48" s="47" t="inlineStr">
         <is>
-          <t>B档，79分；字段显示主线为主线A-AI终端/智能硬件/TPM/软硬件协同项目，匹配度高，原申请优先级P2今日可投。城市/薪资为深圳/上海、Apple官网未公开，薪资匹配为实习薪资未公开；Apple平台价值高，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球消费电子与软硬件一体化顶级外企，AI终端、硬件工程、供应链和产品体验平台价值极高；JD与可信度为Apple官方搜索页可核验标题、发…、中高，扩源入口需后置核验。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳。</t>
+          <t>B档，79分；字段显示主线为主线A-AI终端/智能硬件/TPM/软硬件协同项目，匹配度高，原申请优先级P2今日可投。城市/薪资为深圳/上海、Apple官网未公开，薪资匹配为实习薪资未公开；Apple平台价值高，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球消费电子与软硬件一体化顶级外企，AI终端、硬件工程、供应链和产品体验平台价值极高；JD与可信度为Apple官方搜索页可核验标题、发…、高，入池岗位。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AG48" s="47" t="inlineStr">
         <is>
-          <t>作为主投池，持续监控</t>
+          <t>二次核验后投</t>
         </is>
       </c>
       <c r="AH48" s="47" t="inlineStr">
@@ -14065,326 +14065,326 @@
       </c>
     </row>
     <row r="2" ht="56" customHeight="1">
-      <c r="A2" s="64" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="B2" s="64" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>实习岗</t>
         </is>
       </c>
-      <c r="C2" s="64" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="D2" s="64" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Engineering Project Manager Intern-Shanghai/ Shenzhen</t>
         </is>
       </c>
-      <c r="E2" s="64" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>深圳/上海</t>
         </is>
       </c>
-      <c r="F2" s="64" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Apple官网未公开</t>
         </is>
       </c>
-      <c r="G2" s="64" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H2" s="64" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>实习薪资未公开；Apple平台价值高</t>
         </is>
       </c>
-      <c r="I2" s="64" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>主线A-AI终端/智能硬件/TPM/软硬件协同项目</t>
         </is>
       </c>
-      <c r="J2" s="64" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>P2今日可投</t>
         </is>
       </c>
-      <c r="K2" s="64" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>中高</t>
         </is>
       </c>
-      <c r="L2" s="64" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>实习/硬件项目管理/EPM/外企</t>
         </is>
       </c>
-      <c r="M2" s="64" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>学生岗位，具体年级与专业以Apple JD为准</t>
         </is>
       </c>
-      <c r="N2" s="64" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Apple官网显示Intern岗位；完整JD为JS页面，需投前二次确认每周到岗、实习周期和技术要求</t>
         </is>
       </c>
-      <c r="O2" s="64" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>2026-06-11发布；2026-06-17官方搜索页可见</t>
         </is>
       </c>
-      <c r="P2" s="64" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Apple Jobs</t>
         </is>
       </c>
-      <c r="Q2" s="64" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>全球消费电子与软硬件一体化顶级外企，AI终端、硬件工程、供应链和产品体验平台价值极高</t>
         </is>
       </c>
-      <c r="R2" s="64" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>硬件工程项目管理实习，预计围绕跨职能协作、项目节奏、工程问题跟进、样机/量产节点沟通和供应链协同。</t>
         </is>
       </c>
-      <c r="S2" s="64" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>外企英文沟通与硬件工程语境；可能偏EPM/执行协同而非产品定义；完整JD需二次确认。</t>
         </is>
       </c>
-      <c r="T2" s="64" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>英文风险中；代码风险低；算法风险低；驻厂/供应链沟通风险中。</t>
         </is>
       </c>
-      <c r="U2" s="64" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Apple官方搜索页可核验标题、发布时间、地点和Role Number；详情页JS渲染，职责需二次确认</t>
         </is>
       </c>
-      <c r="V2" s="64" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
-      <c r="W2" s="64" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="X2" s="64" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="Y2" s="64" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Apple智能硬件/TPM版：突出工业设计、硬件产品、CMF、AI硕士、跨团队项目协作、英文沟通和软硬件结合项目。</t>
         </is>
       </c>
-      <c r="Z2" s="64" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="AA2" s="17" t="inlineStr">
+      <c r="AA2" s="50" t="inlineStr">
         <is>
           <t>https://jobs.apple.com/en-us/details/200494847-3435/engineering-project-manager-intern-shanghai-shenzhen?team=HRDWR</t>
         </is>
       </c>
-      <c r="AB2" s="64" t="inlineStr">
+      <c r="AB2" s="53" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="AC2" s="64" t="n">
+      <c r="AC2" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="AD2" s="64" t="inlineStr">
-        <is>
-          <t>B档，79分；字段显示主线为主线A-AI终端/智能硬件/TPM/软硬件协同项目，匹配度高，原申请优先级P2今日可投。城市/薪资为深圳/上海、Apple官网未公开，薪资匹配为实习薪资未公开；Apple平台价值高，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球消费电子与软硬件一体化顶级外企，AI终端、硬件工程、供应链和产品体验平台价值极高；JD与可信度为Apple官方搜索页可核验标题、发…、中高，扩源入口需后置核验。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳。</t>
-        </is>
-      </c>
-      <c r="AE2" s="64" t="inlineStr">
-        <is>
-          <t>作为主投池，持续监控</t>
-        </is>
-      </c>
-      <c r="AF2" s="64" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>B档，79分；字段显示主线为主线A-AI终端/智能硬件/TPM/软硬件协同项目，匹配度高，原申请优先级P2今日可投。城市/薪资为深圳/上海、Apple官网未公开，薪资匹配为实习薪资未公开；Apple平台价值高，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球消费电子与软硬件一体化顶级外企，AI终端、硬件工程、供应链和产品体验平台价值极高；JD与可信度为Apple官方搜索页可核验标题、发…、高，入池岗位。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳。</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>二次核验后投</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
         <is>
           <t>薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳</t>
         </is>
       </c>
-      <c r="AG2" s="64" t="inlineStr">
+      <c r="AG2" s="2" t="inlineStr">
         <is>
           <t>Apple智能硬件/TPM版：突出工业设计、硬件产品、CMF、AI硕士、跨团队项目协作、英文沟通和软硬件结合项目。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="56" customHeight="1">
-      <c r="A3" s="64" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="B3" s="64" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>次选_条件不完全符合</t>
         </is>
       </c>
-      <c r="C3" s="64" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="D3" s="64" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Technical Program Manager, iPad</t>
         </is>
       </c>
-      <c r="E3" s="64" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
       </c>
-      <c r="F3" s="64" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Apple官网未公开</t>
         </is>
       </c>
-      <c r="G3" s="64" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>中高</t>
         </is>
       </c>
-      <c r="H3" s="64" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>薪资未知；Apple平台价值高</t>
         </is>
       </c>
-      <c r="I3" s="64" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>主线A-AI终端/智能硬件/TPM/NPI</t>
         </is>
       </c>
-      <c r="J3" s="64" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>P3二次确认后投递</t>
         </is>
       </c>
-      <c r="K3" s="64" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>中高</t>
         </is>
       </c>
-      <c r="L3" s="64" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>正式/TPM/智能硬件/外企</t>
         </is>
       </c>
-      <c r="M3" s="64" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>未完整核验</t>
         </is>
       </c>
-      <c r="N3" s="64" t="n"/>
-      <c r="O3" s="64" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>Apple官方岗位页，2026-06-12发布</t>
         </is>
       </c>
-      <c r="P3" s="64" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Apple Jobs 官方</t>
         </is>
       </c>
-      <c r="Q3" s="64" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>全球消费电子与软硬件一体化顶级外企，iPad硬件与供应链平台价值高</t>
         </is>
       </c>
-      <c r="R3" s="64" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>iPad硬件/运营链路的技术项目管理，预计涉及跨职能工程协作、供应链/制造节点、风险跟踪和项目推进。</t>
         </is>
       </c>
-      <c r="S3" s="64" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>正式TPM可能要求多年经验；非纯产品经理；英文和硬件工程语境要求高，需二次确认。</t>
         </is>
       </c>
-      <c r="T3" s="64" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>英文风险中高；代码风险低；驻厂/供应链沟通风险中。</t>
         </is>
       </c>
-      <c r="U3" s="64" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Apple官方搜索页可核验标题、发布时间、地点和Role Number；详情页JS渲染，职责需二次确认</t>
         </is>
       </c>
-      <c r="V3" s="64" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
-      <c r="W3" s="64" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="X3" s="64" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="Y3" s="64" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Apple智能硬件/TPM版：突出硬件产品、项目协作、NPI/供应链理解、CMF与软硬件结合项目。</t>
         </is>
       </c>
-      <c r="Z3" s="64" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>中高</t>
         </is>
       </c>
-      <c r="AA3" s="17" t="inlineStr">
+      <c r="AA3" s="50" t="inlineStr">
         <is>
           <t>https://jobs.apple.com/en-us/details/200666248-3435/technical-program-manager-ipad?team=OPMFG</t>
         </is>
       </c>
-      <c r="AB3" s="64" t="inlineStr">
+      <c r="AB3" s="53" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="AC3" s="64" t="n">
+      <c r="AC3" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="AD3" s="64" t="inlineStr">
+      <c r="AD3" s="2" t="inlineStr">
         <is>
           <t>B档，79分；字段显示主线为主线A-AI终端/智能硬件/TPM/NPI，匹配度中高，原申请优先级P3二次确认后投递。城市/薪资为深圳、Apple官网未公开，薪资匹配为薪资未知；Apple平台价值高，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球消费电子与软硬件一体化顶级外企，iPad硬件与供应链平台价值高；JD与可信度为Apple官方搜索页可核验标题、发…、中高，次选表但仍按平台和方向重新排序。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳。</t>
         </is>
       </c>
-      <c r="AE3" s="64" t="inlineStr">
+      <c r="AE3" s="2" t="inlineStr">
         <is>
           <t>二次核验后投</t>
         </is>
       </c>
-      <c r="AF3" s="64" t="inlineStr">
+      <c r="AF3" s="2" t="inlineStr">
         <is>
           <t>薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳</t>
         </is>
       </c>
-      <c r="AG3" s="64" t="inlineStr">
+      <c r="AG3" s="2" t="inlineStr">
         <is>
           <t>Apple智能硬件/TPM版：突出硬件产品、项目协作、NPI/供应链理解、CMF与软硬件结合项目。</t>
         </is>
@@ -15095,7 +15095,7 @@
       </c>
       <c r="V4" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W4" s="48" t="inlineStr">
@@ -15142,11 +15142,11 @@
         </is>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AG4" s="2" t="inlineStr">
         <is>
-          <t>B档，71分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港线上生活服务与医疗预约平台；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
+          <t>B档，75分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港线上生活服务与医疗预约平台；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂。</t>
         </is>
       </c>
       <c r="AH4" s="2" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="AI4" s="2" t="inlineStr">
         <is>
-          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
+          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr">
@@ -15273,7 +15273,7 @@
       </c>
       <c r="V5" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W5" s="47" t="inlineStr">
@@ -15320,11 +15320,11 @@
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AG5" s="2" t="inlineStr">
         <is>
-          <t>B档，72分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、44k-53k 港币/月，薪资匹配为达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：世界500强与全球大型医疗健康集团；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：JD不精确；英文/粤语/IANG；出差/驻厂；销售化；招聘状态不稳。</t>
+          <t>B档，74分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、44k-53k 港币/月，薪资匹配为达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：世界500强与全球大型医疗健康集团；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：JD不精确；英文/粤语/IANG；出差/驻厂；销售化。</t>
         </is>
       </c>
       <c r="AH5" s="2" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>JD不精确；英文/粤语/IANG；出差/驻厂；销售化；招聘状态不稳</t>
+          <t>JD不精确；英文/粤语/IANG；出差/驻厂；销售化</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="V6" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W6" s="48" t="inlineStr">
@@ -15498,11 +15498,11 @@
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AG6" s="2" t="inlineStr">
         <is>
-          <t>B档，65分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球大型保险集团在港核心市场；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；销售化；招聘状态不稳。</t>
+          <t>B档，67分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球大型保险集团在港核心市场；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；销售化。</t>
         </is>
       </c>
       <c r="AH6" s="2" t="inlineStr">
@@ -15512,7 +15512,7 @@
       </c>
       <c r="AI6" s="2" t="inlineStr">
         <is>
-          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；销售化；招聘状态不稳</t>
+          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；销售化</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="inlineStr">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="V7" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W7" s="47" t="inlineStr">
@@ -15676,11 +15676,11 @@
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AG7" s="2" t="inlineStr">
         <is>
-          <t>B档，65分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港大型餐饮与零售集团；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
+          <t>B档，69分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港大型餐饮与零售集团；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂。</t>
         </is>
       </c>
       <c r="AH7" s="2" t="inlineStr">
@@ -15690,7 +15690,7 @@
       </c>
       <c r="AI7" s="2" t="inlineStr">
         <is>
-          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
+          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="V9" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W9" s="47" t="inlineStr">
@@ -16032,11 +16032,11 @@
         </is>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AG9" s="2" t="inlineStr">
         <is>
-          <t>B档，65分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港大型贸易分销与汽车消费品集团；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
+          <t>B档，69分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港大型贸易分销与汽车消费品集团；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂。</t>
         </is>
       </c>
       <c r="AH9" s="2" t="inlineStr">
@@ -16046,7 +16046,7 @@
       </c>
       <c r="AI9" s="2" t="inlineStr">
         <is>
-          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
+          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="V10" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W10" s="48" t="inlineStr">
@@ -16210,11 +16210,11 @@
         </is>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
-          <t>B档，71分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港快消外企与知名品牌集团；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
+          <t>B档，75分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港快消外企与知名品牌集团；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂。</t>
         </is>
       </c>
       <c r="AH10" s="2" t="inlineStr">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AI10" s="2" t="inlineStr">
         <is>
-          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
+          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="inlineStr">
@@ -16341,7 +16341,7 @@
       </c>
       <c r="V11" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W11" s="47" t="inlineStr">
@@ -16388,11 +16388,11 @@
         </is>
       </c>
       <c r="AF11" s="2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AG11" s="2" t="inlineStr">
         <is>
-          <t>B档，71分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港消费电子与电商零售品牌；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
+          <t>B档，75分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港消费电子与电商零售品牌；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂。</t>
         </is>
       </c>
       <c r="AH11" s="2" t="inlineStr">
@@ -16402,7 +16402,7 @@
       </c>
       <c r="AI11" s="2" t="inlineStr">
         <is>
-          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
+          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂</t>
         </is>
       </c>
       <c r="AJ11" s="2" t="inlineStr">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="V12" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W12" s="47" t="inlineStr">
@@ -16566,11 +16566,11 @@
         </is>
       </c>
       <c r="AF12" s="2" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AG12" s="2" t="inlineStr">
         <is>
-          <t>B档，65分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港持牌银行与台湾金控系机构；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
+          <t>B档，69分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港持牌银行与台湾金控系机构；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂。</t>
         </is>
       </c>
       <c r="AH12" s="2" t="inlineStr">
@@ -16580,7 +16580,7 @@
       </c>
       <c r="AI12" s="2" t="inlineStr">
         <is>
-          <t>薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
+          <t>薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂</t>
         </is>
       </c>
       <c r="AJ12" s="2" t="inlineStr">
@@ -16875,7 +16875,7 @@
       </c>
       <c r="V14" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W14" s="48" t="inlineStr">
@@ -16922,11 +16922,11 @@
         </is>
       </c>
       <c r="AF14" s="2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AG14" s="2" t="inlineStr">
         <is>
-          <t>B档，71分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球顶级学术出版机构；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
+          <t>B档，75分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球顶级学术出版机构；JD与可信度为转载/聚合线索、中，次选表但仍按平台和方向重新排序。关键风险：详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂。</t>
         </is>
       </c>
       <c r="AH14" s="2" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="AI14" s="2" t="inlineStr">
         <is>
-          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
+          <t>详情或任职要求含3年及以上/3-5年经验门槛，正式主表降为次选复核；薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂</t>
         </is>
       </c>
       <c r="AJ14" s="2" t="inlineStr">
@@ -22393,7 +22393,7 @@
       </c>
       <c r="V45" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W45" s="48" t="inlineStr">
@@ -22444,7 +22444,7 @@
       </c>
       <c r="AG45" s="2" t="inlineStr">
         <is>
-          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中高，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为不适用，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港商户收单与支付科技公司；JD与可信度为精确JD、高，次选表但仍按平台和方向重新排序。关键风险：英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
+          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中高，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为不适用，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港商户收单与支付科技公司；JD与可信度为精确JD、高，次选表但仍按平台和方向重新排序。关键风险：英文/粤语/IANG；出差/驻厂。</t>
         </is>
       </c>
       <c r="AH45" s="2" t="inlineStr">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="AI45" s="2" t="inlineStr">
         <is>
-          <t>英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
+          <t>英文/粤语/IANG；出差/驻厂</t>
         </is>
       </c>
       <c r="AJ45" s="2" t="inlineStr">
@@ -22749,7 +22749,7 @@
       </c>
       <c r="V47" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W47" s="48" t="inlineStr">
@@ -22800,7 +22800,7 @@
       </c>
       <c r="AG47" s="2" t="inlineStr">
         <is>
-          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中高，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为不适用，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：AI 产品创业公司；JD与可信度为精确JD、高，次选表但仍按平台和方向重新排序。关键风险：英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
+          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中高，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为不适用，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：AI 产品创业公司；JD与可信度为精确JD、高，次选表但仍按平台和方向重新排序。关键风险：英文/粤语/IANG；出差/驻厂。</t>
         </is>
       </c>
       <c r="AH47" s="2" t="inlineStr">
@@ -22810,7 +22810,7 @@
       </c>
       <c r="AI47" s="2" t="inlineStr">
         <is>
-          <t>英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
+          <t>英文/粤语/IANG；出差/驻厂</t>
         </is>
       </c>
       <c r="AJ47" s="2" t="inlineStr">
@@ -23105,7 +23105,7 @@
       </c>
       <c r="V49" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W49" s="48" t="inlineStr">
@@ -23156,7 +23156,7 @@
       </c>
       <c r="AG49" s="2" t="inlineStr">
         <is>
-          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为不适用，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球玩具与娱乐大厂；JD与可信度为精确JD、高，次选表但仍按平台和方向重新排序。关键风险：英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
+          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度中，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为不适用，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球玩具与娱乐大厂；JD与可信度为精确JD、高，次选表但仍按平台和方向重新排序。关键风险：英文/粤语/IANG；出差/驻厂。</t>
         </is>
       </c>
       <c r="AH49" s="2" t="inlineStr">
@@ -23166,7 +23166,7 @@
       </c>
       <c r="AI49" s="2" t="inlineStr">
         <is>
-          <t>英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
+          <t>英文/粤语/IANG；出差/驻厂</t>
         </is>
       </c>
       <c r="AJ49" s="2" t="inlineStr">
@@ -24018,7 +24018,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="AA54" s="17" t="inlineStr">
+      <c r="AA54" s="62" t="inlineStr">
         <is>
           <t>https://jobs.apple.com/en-us/details/200658508-3435/product-design-engineer-mechanical?team=HRDWR</t>
         </is>
@@ -24196,7 +24196,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="AA55" s="17" t="inlineStr">
+      <c r="AA55" s="62" t="inlineStr">
         <is>
           <t>https://jobs.apple.com/en-us/details/200644919-3435/manufacturing-design-engineer-intern-shenzhen-changsha?team=STDNT</t>
         </is>
@@ -25415,7 +25415,7 @@
       </c>
       <c r="V62" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="W62" s="48" t="inlineStr">
@@ -25462,7 +25462,7 @@
       </c>
       <c r="AG62" s="2" t="inlineStr">
         <is>
-          <t>B档，79分；字段显示主线为主线B-AI应用落地/FDE/GenAI部署，匹配度中高，原申请优先级P2验证（FDE上限岗位）。城市/薪资为香港（可选 Taipei；投前…、官方未公开，薪资匹配为待确认；平台/方向强，香港薪资上限…，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球云与AI平台头部公司；Google Cloud企业级AI与云服务；JD与可信度为精确JD（LinkedIn公共页完…、高，次选表但仍按平台和方向重新排序。关键风险：薪资待确认；英文/粤语/IANG；代码/技术面。</t>
+          <t>B档，79分；字段显示主线为主线B-AI应用落地/FDE/GenAI部署，匹配度中高，原申请优先级P2验证（FDE上限岗位）。城市/薪资为香港（可选 Taipei；投前…、官方未公开，薪资匹配为待确认；平台/方向强，香港薪资上限…，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球云与AI平台头部公司；Google Cloud企业级AI与云服务；JD与可信度为精确JD（LinkedIn公共页完…、高，次选表但仍按平台和方向重新排序。关键风险：薪资待确认；英文/粤语/IANG；代码/技术面；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AH62" s="2" t="inlineStr">
@@ -25472,7 +25472,7 @@
       </c>
       <c r="AI62" s="2" t="inlineStr">
         <is>
-          <t>薪资待确认；英文/粤语/IANG；代码/技术面</t>
+          <t>薪资待确认；英文/粤语/IANG；代码/技术面；招聘状态不稳</t>
         </is>
       </c>
       <c r="AJ62" s="2" t="inlineStr">
@@ -26301,7 +26301,7 @@
       </c>
       <c r="V67" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="W67" s="48" t="inlineStr">
@@ -26479,7 +26479,7 @@
       </c>
       <c r="V68" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="W68" s="48" t="inlineStr">
@@ -29144,7 +29144,7 @@
           <t>中高</t>
         </is>
       </c>
-      <c r="AA83" s="17" t="inlineStr">
+      <c r="AA83" s="62" t="inlineStr">
         <is>
           <t>https://jobs.apple.com/en-us/details/200666248-3435/technical-program-manager-ipad?team=OPMFG</t>
         </is>
@@ -29991,7 +29991,7 @@
       </c>
       <c r="V88" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；公开可见HR活跃状态：刚刚活跃</t>
         </is>
       </c>
       <c r="W88" s="47" t="inlineStr">
@@ -30821,7 +30821,7 @@
       </c>
       <c r="Q4" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="R4" s="47" t="inlineStr">
@@ -31151,7 +31151,7 @@
       </c>
       <c r="Q6" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="R6" s="47" t="inlineStr">
@@ -31811,7 +31811,7 @@
       </c>
       <c r="Q10" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R10" s="48" t="inlineStr">
@@ -31870,21 +31870,21 @@
         </is>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>A档，87分；字段显示主线为备线C-AI解决方案/数字化产品，匹配度中高，原申请优先级P3练手/备选实习。城市/薪资为深圳、未写，薪资匹配为实习可接受，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：腾讯云CSIG，中国头部云与产业互联网平台，做云、AI、安全和行业数字化；JD与可信度为精确JD、高，入池岗位。关键风险：出差/驻厂；招聘状态不稳。</t>
+          <t>A档，98分；字段显示主线为备线C-AI解决方案/数字化产品，匹配度中高，原申请优先级P3练手/备选实习。城市/薪资为深圳、未写，薪资匹配为实习可接受，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：腾讯云CSIG，中国头部云与产业互联网平台，做云、AI、安全和行业数字化；JD与可信度为精确JD、高，入池岗位。关键风险：出差/驻厂。</t>
         </is>
       </c>
       <c r="AE10" s="2" t="inlineStr">
         <is>
-          <t>先核验再投</t>
+          <t>定制简历后优先投</t>
         </is>
       </c>
       <c r="AF10" s="2" t="inlineStr">
         <is>
-          <t>出差/驻厂；招聘状态不稳</t>
+          <t>出差/驻厂</t>
         </is>
       </c>
       <c r="AG10" s="2" t="inlineStr">
@@ -32471,7 +32471,7 @@
       </c>
       <c r="Q14" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R14" s="47" t="inlineStr">
@@ -32801,7 +32801,7 @@
       </c>
       <c r="Q16" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R16" s="47" t="inlineStr">
@@ -33296,7 +33296,7 @@
       </c>
       <c r="Q19" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R19" s="48" t="inlineStr">
@@ -35276,7 +35276,7 @@
       </c>
       <c r="Q31" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R31" s="47" t="inlineStr">
@@ -35339,17 +35339,17 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>C档，50分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度高，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球外设龙头与瑞士国际品牌；JD与可信度为精确JD、高，入池岗位。关键风险：资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；薪资待确认；英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
+          <t>C档，50分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度高，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球外设龙头与瑞士国际品牌；JD与可信度为精确JD、高，入池岗位。关键风险：资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；薪资待确认；英文/粤语/IANG；出差/驻厂。</t>
         </is>
       </c>
       <c r="AE31" s="2" t="inlineStr">
         <is>
-          <t>观察</t>
+          <t>练手投/暂缓</t>
         </is>
       </c>
       <c r="AF31" s="2" t="inlineStr">
         <is>
-          <t>资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；薪资待确认；英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
+          <t>资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；薪资待确认；英文/粤语/IANG；出差/驻厂</t>
         </is>
       </c>
       <c r="AG31" s="2" t="inlineStr">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="Q49" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R49" s="47" t="inlineStr">
@@ -38305,11 +38305,11 @@
         </is>
       </c>
       <c r="AC49" s="2" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>B档，69分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度中高，原申请优先级P2AI应用实习。城市/薪资为香港/深圳、未公开，薪资匹配为实习可接受，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：移动设备管理、远程控制和跨设备协同工具公司，香港/深圳协同；JD与可信度为入口页/搜索页、中高，入池岗位。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
+          <t>B档，73分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度中高，原申请优先级P2AI应用实习。城市/薪资为香港/深圳、未公开，薪资匹配为实习可接受，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：移动设备管理、远程控制和跨设备协同工具公司，香港/深圳协同；JD与可信度为入口页/搜索页、中高，入池岗位。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂。</t>
         </is>
       </c>
       <c r="AE49" s="2" t="inlineStr">
@@ -38319,7 +38319,7 @@
       </c>
       <c r="AF49" s="2" t="inlineStr">
         <is>
-          <t>薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
+          <t>薪资待确认；JD不精确；英文/粤语/IANG；出差/驻厂</t>
         </is>
       </c>
       <c r="AG49" s="2" t="inlineStr">
@@ -39236,7 +39236,7 @@
       </c>
       <c r="Q55" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R55" s="48" t="inlineStr">
@@ -39299,7 +39299,7 @@
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度高，原申请优先级P1主线实习。城市/薪资为深圳、400-500/天待确认，薪资匹配为实习可接受，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：深圳创客硬件和桌面激光加工设备出海品牌，软硬件结合和创作者生态强；JD与可信度为入口页/搜索页、中高，入池岗位。关键风险：薪资待确认；JD不精确；出差/驻厂；招聘状态不稳。</t>
+          <t>B档，79分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度高，原申请优先级P1主线实习。城市/薪资为深圳、400-500/天待确认，薪资匹配为实习可接受，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：深圳创客硬件和桌面激光加工设备出海品牌，软硬件结合和创作者生态强；JD与可信度为入口页/搜索页、中高，入池岗位。关键风险：薪资待确认；JD不精确；出差/驻厂。</t>
         </is>
       </c>
       <c r="AE55" s="2" t="inlineStr">
@@ -39309,7 +39309,7 @@
       </c>
       <c r="AF55" s="2" t="inlineStr">
         <is>
-          <t>薪资待确认；JD不精确；出差/驻厂；招聘状态不稳</t>
+          <t>薪资待确认；JD不精确；出差/驻厂</t>
         </is>
       </c>
       <c r="AG55" s="2" t="inlineStr">
@@ -40721,7 +40721,7 @@
       </c>
       <c r="Q64" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="R64" s="47" t="inlineStr">
@@ -46146,7 +46146,7 @@
       </c>
       <c r="Q97" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R97" s="48" t="inlineStr">
@@ -46205,17 +46205,17 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>A档，100分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1主攻。城市/薪资为香港、HK$22,000-28,000/月，薪资匹配为部分达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港本地Agentic AI平台公司，主打企业客服与销售流程自动化；JD与可信度为中高、中高，入池岗位。关键风险：英文/粤语/IANG。</t>
+          <t>A档，100分；字段显示主线为主线B-AI应用落地/AI产品工程师，匹配度高，原申请优先级P1主攻。城市/薪资为香港、HK$22,000-28,000/月，薪资匹配为部分达标，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港本地Agentic AI平台公司，主打企业客服与销售流程自动化；JD与可信度为中高、中高，入池岗位。关键风险：英文/粤语/IANG；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AE97" s="2" t="inlineStr">
         <is>
-          <t>重点准备后投</t>
+          <t>先核验再投</t>
         </is>
       </c>
       <c r="AF97" s="2" t="inlineStr">
         <is>
-          <t>英文/粤语/IANG</t>
+          <t>英文/粤语/IANG；招聘状态不稳</t>
         </is>
       </c>
       <c r="AG97" s="2" t="inlineStr">
@@ -46464,7 +46464,7 @@
       </c>
       <c r="Q99" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R99" s="48" t="inlineStr">
@@ -46515,11 +46515,11 @@
         </is>
       </c>
       <c r="AC99" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>B档，73分；字段显示主线为备线C-AI解决方案/数字化产品，匹配度中高，原申请优先级P2验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港本地ERP/企业系统厂商，正在把AI/CRM/ERP打包为企业数字化方案；JD与可信度为搜索结果核验、中，扩源入口需后置核验。关键风险：薪资待确认；英文/粤语/IANG；招聘状态不稳。</t>
+          <t>B档，76分；字段显示主线为备线C-AI解决方案/数字化产品，匹配度中高，原申请优先级P2验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港本地ERP/企业系统厂商，正在把AI/CRM/ERP打包为企业数字化方案；JD与可信度为搜索结果核验、中，扩源入口需后置核验。关键风险：薪资待确认；英文/粤语/IANG。</t>
         </is>
       </c>
       <c r="AE99" s="2" t="inlineStr">
@@ -46529,7 +46529,7 @@
       </c>
       <c r="AF99" s="2" t="inlineStr">
         <is>
-          <t>薪资待确认；英文/粤语/IANG；招聘状态不稳</t>
+          <t>薪资待确认；英文/粤语/IANG</t>
         </is>
       </c>
       <c r="AG99" s="2" t="inlineStr">
@@ -47104,7 +47104,7 @@
       </c>
       <c r="Q103" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；公开可见HR活跃状态：刚刚活跃</t>
         </is>
       </c>
       <c r="R103" s="48" t="inlineStr">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="Q107" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R107" s="48" t="inlineStr">
@@ -47803,11 +47803,11 @@
         </is>
       </c>
       <c r="AC107" s="2" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>B档，72分；字段显示主线为主线B-AI应用落地/AI产品工程师（偏业务落地与原型实现），匹配度中高，原申请优先级P2验证。城市/薪资为香港-Kowloon Bay、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港数据中心与IT服务公司，业务覆盖AI Infrastructure、HPC与企…；JD与可信度为搜索结果核验，需二次确认、中，扩源入口需后置核验。关键风险：薪资待确认；英文/粤语/IANG；招聘状态不稳。</t>
+          <t>B档，76分；字段显示主线为主线B-AI应用落地/AI产品工程师（偏业务落地与原型实现），匹配度中高，原申请优先级P2验证。城市/薪资为香港-Kowloon Bay、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港数据中心与IT服务公司，业务覆盖AI Infrastructure、HPC与企…；JD与可信度为搜索结果核验，需二次确认、中，扩源入口需后置核验。关键风险：薪资待确认；英文/粤语/IANG；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AE107" s="2" t="inlineStr">
@@ -47909,7 +47909,7 @@
       </c>
       <c r="Q108" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R108" s="48" t="inlineStr">
@@ -48875,7 +48875,7 @@
       </c>
       <c r="Q114" s="48" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="R114" s="48" t="inlineStr">
@@ -52145,7 +52145,7 @@
       </c>
       <c r="Q134" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="R134" s="47" t="inlineStr">
@@ -52308,7 +52308,7 @@
       </c>
       <c r="Q135" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="R135" s="47" t="inlineStr">
@@ -52634,7 +52634,7 @@
       </c>
       <c r="Q137" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="R137" s="47" t="inlineStr">
@@ -52797,7 +52797,7 @@
       </c>
       <c r="Q138" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="R138" s="47" t="inlineStr">
@@ -52960,7 +52960,7 @@
       </c>
       <c r="Q139" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="R139" s="47" t="inlineStr">
@@ -54101,7 +54101,7 @@
       </c>
       <c r="Q146" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="R146" s="47" t="inlineStr">
@@ -54753,7 +54753,7 @@
       </c>
       <c r="Q150" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；非招聘软件或页面未公开HR活跃状态</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；非招聘软件或页面未公开HR活跃状态</t>
         </is>
       </c>
       <c r="R150" s="47" t="inlineStr">
@@ -56691,7 +56691,7 @@
           <t>中高</t>
         </is>
       </c>
-      <c r="U162" s="17" t="inlineStr">
+      <c r="U162" s="62" t="inlineStr">
         <is>
           <t>https://jobs.apple.com/en-us/details/200494847-3435/engineering-project-manager-intern-shanghai-shenzhen?team=HRDWR</t>
         </is>
@@ -56728,12 +56728,12 @@
       </c>
       <c r="AD162" s="47" t="inlineStr">
         <is>
-          <t>B档，79分；字段显示主线为主线A-AI终端/智能硬件/TPM/软硬件协同项目，匹配度高，原申请优先级P2今日可投。城市/薪资为深圳/上海、Apple官网未公开，薪资匹配为实习薪资未公开；Apple平台价值高，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球消费电子与软硬件一体化顶级外企，AI终端、硬件工程、供应链和产品体验平台价值极高；JD与可信度为Apple官方搜索页可核验标题、发…、中高，扩源入口需后置核验。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳。</t>
+          <t>B档，79分；字段显示主线为主线A-AI终端/智能硬件/TPM/软硬件协同项目，匹配度高，原申请优先级P2今日可投。城市/薪资为深圳/上海、Apple官网未公开，薪资匹配为实习薪资未公开；Apple平台价值高，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球消费电子与软硬件一体化顶级外企，AI终端、硬件工程、供应链和产品体验平台价值极高；JD与可信度为Apple官方搜索页可核验标题、发…、中高，入池岗位。关键风险：薪资待确认；JD不精确；英文/粤语/IANG；招聘状态不稳。</t>
         </is>
       </c>
       <c r="AE162" s="47" t="inlineStr">
         <is>
-          <t>作为主投池，持续监控</t>
+          <t>二次核验后投</t>
         </is>
       </c>
       <c r="AF162" s="47" t="inlineStr">
@@ -58197,7 +58197,7 @@
       </c>
       <c r="S7" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="T7" s="47" t="inlineStr">
@@ -58269,11 +58269,11 @@
         </is>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AI7" s="2" t="inlineStr">
         <is>
-          <t>B档，73分；字段显示主线为备线C-AI解决方案/数字化产品，匹配度中高，原申请优先级P2验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港本地ERP/企业系统厂商，正在把AI/CRM/ERP打包为企业数字化方案；JD与可信度为搜索结果核验、中，扩源入口需后置核验。关键风险：薪资待确认；英文/粤语/IANG；招聘状态不稳。</t>
+          <t>B档，76分；字段显示主线为备线C-AI解决方案/数字化产品，匹配度中高，原申请优先级P2验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：香港本地ERP/企业系统厂商，正在把AI/CRM/ERP打包为企业数字化方案；JD与可信度为搜索结果核验、中，扩源入口需后置核验。关键风险：薪资待确认；英文/粤语/IANG。</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr">
@@ -58283,7 +58283,7 @@
       </c>
       <c r="AK7" s="2" t="inlineStr">
         <is>
-          <t>薪资待确认；英文/粤语/IANG；招聘状态不稳</t>
+          <t>薪资待确认；英文/粤语/IANG</t>
         </is>
       </c>
       <c r="AL7" s="2" t="inlineStr">
@@ -58573,7 +58573,7 @@
       </c>
       <c r="S9" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="T9" s="47" t="inlineStr">
@@ -58745,7 +58745,7 @@
       </c>
       <c r="S10" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（403），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="T10" s="47" t="inlineStr">
@@ -59949,7 +59949,7 @@
       </c>
       <c r="S17" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接无法精确确认（429），需二次确认；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="T17" s="47" t="inlineStr">
@@ -60009,17 +60009,17 @@
       </c>
       <c r="AI17" s="2" t="inlineStr">
         <is>
-          <t>C档，50分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度高，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球外设龙头与瑞士国际品牌；JD与可信度为精确JD、高，扩源入口需后置核验。关键风险：资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；详情或任职要求含5年及以上/5+ years硬经验门槛；薪资待确认；经验偏高；英文/粤语/IANG；出差/驻厂；招聘状态不稳。</t>
+          <t>C档，50分；字段显示主线为主线A-AIoT/AI终端/软硬件产品，匹配度高，原申请优先级P3次选验证。城市/薪资为香港、未写，薪资匹配为待确认，对当前香港/深圳双线与现金流目标的支撑不同。公司/岗位价值：全球外设龙头与瑞士国际品牌；JD与可信度为精确JD、高，扩源入口需后置核验。关键风险：资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；详情或任职要求含5年及以上/5+ years硬经验门槛；薪资待确认；经验偏高；英文/粤语/IANG；出差/驻厂。</t>
         </is>
       </c>
       <c r="AJ17" s="2" t="inlineStr">
         <is>
-          <t>观察</t>
+          <t>练手投/暂缓</t>
         </is>
       </c>
       <c r="AK17" s="2" t="inlineStr">
         <is>
-          <t>资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；详情或任职要求含5年及以上/5+ years硬经验门槛；薪资待确认；经验偏高；英文/粤语/IANG；出差/驻厂；招聘状态不稳</t>
+          <t>资深/高年限硬门槛：标题含高级/资深/专家/负责人/Lead/Owner等资深信号；详情或任职要求含5年及以上/5+ years硬经验门槛；薪资待确认；经验偏高；英文/粤语/IANG；出差/驻厂</t>
         </is>
       </c>
       <c r="AL17" s="2" t="inlineStr">
@@ -60873,7 +60873,7 @@
       </c>
       <c r="S22" s="47" t="inlineStr">
         <is>
-          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面内容较上次有变化；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
+          <t>2026-06-17 自动复核：链接可打开，未识别下架关键词；页面未公开HR活跃/登录状态；不绕过登录或反爬抓取</t>
         </is>
       </c>
       <c r="T22" s="47" t="inlineStr">
@@ -61595,7 +61595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E211"/>
+  <dimension ref="A1:E228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -64961,6 +64961,261 @@
       <c r="C211" s="48" t="n"/>
       <c r="D211" s="48" t="n"/>
       <c r="E211" s="48" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="48" t="inlineStr">
+        <is>
+          <t>新明珠集团</t>
+        </is>
+      </c>
+      <c r="B212" s="48" t="inlineStr">
+        <is>
+          <t>AI智能体产品设计师</t>
+        </is>
+      </c>
+      <c r="C212" s="48" t="inlineStr"/>
+      <c r="D212" s="48" t="inlineStr"/>
+      <c r="E212" s="48" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="48" t="inlineStr">
+        <is>
+          <t>玖龙纸业（控股）有限公司</t>
+        </is>
+      </c>
+      <c r="B213" s="48" t="inlineStr">
+        <is>
+          <t>AI产品经理</t>
+        </is>
+      </c>
+      <c r="C213" s="48" t="inlineStr"/>
+      <c r="D213" s="48" t="inlineStr"/>
+      <c r="E213" s="48" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="48" t="inlineStr">
+        <is>
+          <t>Seeed 矽递科技</t>
+        </is>
+      </c>
+      <c r="B214" s="48" t="inlineStr">
+        <is>
+          <t>AI产品经理</t>
+        </is>
+      </c>
+      <c r="C214" s="48" t="inlineStr"/>
+      <c r="D214" s="48" t="inlineStr"/>
+      <c r="E214" s="48" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="48" t="inlineStr">
+        <is>
+          <t>深圳欣盛商科技有限公司</t>
+        </is>
+      </c>
+      <c r="B215" s="48" t="inlineStr">
+        <is>
+          <t>企业AI应用工程师</t>
+        </is>
+      </c>
+      <c r="C215" s="48" t="inlineStr"/>
+      <c r="D215" s="48" t="inlineStr"/>
+      <c r="E215" s="48" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="48" t="inlineStr">
+        <is>
+          <t>美团</t>
+        </is>
+      </c>
+      <c r="B216" s="48" t="inlineStr">
+        <is>
+          <t>AI硬件产品专员/工程师</t>
+        </is>
+      </c>
+      <c r="C216" s="48" t="inlineStr"/>
+      <c r="D216" s="48" t="inlineStr"/>
+      <c r="E216" s="48" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="48" t="inlineStr">
+        <is>
+          <t>深圳启奥人工智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="B217" s="48" t="inlineStr">
+        <is>
+          <t>产品经理</t>
+        </is>
+      </c>
+      <c r="C217" s="48" t="inlineStr"/>
+      <c r="D217" s="48" t="inlineStr"/>
+      <c r="E217" s="48" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="48" t="inlineStr">
+        <is>
+          <t>深圳费曼智核机器人科技有限公司</t>
+        </is>
+      </c>
+      <c r="B218" s="48" t="inlineStr">
+        <is>
+          <t>大模型产品经理</t>
+        </is>
+      </c>
+      <c r="C218" s="48" t="inlineStr"/>
+      <c r="D218" s="48" t="inlineStr"/>
+      <c r="E218" s="48" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="48" t="inlineStr">
+        <is>
+          <t>鱼泡直聘线索/深圳宝安未核验雇主</t>
+        </is>
+      </c>
+      <c r="B219" s="48" t="inlineStr">
+        <is>
+          <t>工业AI产品经理</t>
+        </is>
+      </c>
+      <c r="C219" s="48" t="inlineStr"/>
+      <c r="D219" s="48" t="inlineStr"/>
+      <c r="E219" s="48" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="48" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B220" s="48" t="inlineStr">
+        <is>
+          <t>Subject Matter Expert - Automation &amp; AI/ML</t>
+        </is>
+      </c>
+      <c r="C220" s="48" t="inlineStr"/>
+      <c r="D220" s="48" t="inlineStr"/>
+      <c r="E220" s="48" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="48" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B221" s="48" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="C221" s="48" t="inlineStr"/>
+      <c r="D221" s="48" t="inlineStr"/>
+      <c r="E221" s="48" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="48" t="inlineStr">
+        <is>
+          <t>Reap</t>
+        </is>
+      </c>
+      <c r="B222" s="48" t="inlineStr">
+        <is>
+          <t>Technical Product Manager, AI Platform</t>
+        </is>
+      </c>
+      <c r="C222" s="48" t="inlineStr"/>
+      <c r="D222" s="48" t="inlineStr"/>
+      <c r="E222" s="48" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="48" t="inlineStr">
+        <is>
+          <t>深圳中博纳网络科技有限公司（鱼泡直聘线索）</t>
+        </is>
+      </c>
+      <c r="B223" s="48" t="inlineStr">
+        <is>
+          <t>AI+机器人产品经理</t>
+        </is>
+      </c>
+      <c r="C223" s="48" t="inlineStr"/>
+      <c r="D223" s="48" t="inlineStr"/>
+      <c r="E223" s="48" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="48" t="inlineStr">
+        <is>
+          <t>科大讯飞硬件中心</t>
+        </is>
+      </c>
+      <c r="B224" s="48" t="inlineStr">
+        <is>
+          <t>高级平台硬件产品经理（机器人）</t>
+        </is>
+      </c>
+      <c r="C224" s="48" t="inlineStr"/>
+      <c r="D224" s="48" t="inlineStr"/>
+      <c r="E224" s="48" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="48" t="inlineStr">
+        <is>
+          <t>中电信数智科技(深圳)有限公司</t>
+        </is>
+      </c>
+      <c r="B225" s="48" t="inlineStr">
+        <is>
+          <t>智能组网产品经理</t>
+        </is>
+      </c>
+      <c r="C225" s="48" t="inlineStr"/>
+      <c r="D225" s="48" t="inlineStr"/>
+      <c r="E225" s="48" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="48" t="inlineStr">
+        <is>
+          <t>New Media Group Publishing Limited</t>
+        </is>
+      </c>
+      <c r="B226" s="48" t="inlineStr">
+        <is>
+          <t>Product Manager - AI Rich Media Solution</t>
+        </is>
+      </c>
+      <c r="C226" s="48" t="inlineStr"/>
+      <c r="D226" s="48" t="inlineStr"/>
+      <c r="E226" s="48" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="48" t="inlineStr">
+        <is>
+          <t>Galaxy Telecom (Hong Kong) Limited</t>
+        </is>
+      </c>
+      <c r="B227" s="48" t="inlineStr">
+        <is>
+          <t>AI Product Manager / Owner (ERP project)</t>
+        </is>
+      </c>
+      <c r="C227" s="48" t="inlineStr"/>
+      <c r="D227" s="48" t="inlineStr"/>
+      <c r="E227" s="48" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="48" t="inlineStr">
+        <is>
+          <t>HK01 Company Limited</t>
+        </is>
+      </c>
+      <c r="B228" s="48" t="inlineStr">
+        <is>
+          <t>AI Application Product Manager</t>
+        </is>
+      </c>
+      <c r="C228" s="48" t="inlineStr"/>
+      <c r="D228" s="48" t="inlineStr"/>
+      <c r="E228" s="48" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E16"/>
